--- a/research/traditional_assets/database/data/chile/chile_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_paper_forest_products.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0592</v>
+        <v>-0.01645000000000001</v>
       </c>
       <c r="E2">
         <v>0.191</v>
       </c>
       <c r="G2">
-        <v>0.1178599881781501</v>
+        <v>0.1144222189173111</v>
       </c>
       <c r="H2">
-        <v>0.1169206651075531</v>
+        <v>0.1135162601626016</v>
       </c>
       <c r="I2">
-        <v>0.06198761275731798</v>
+        <v>0.05868902439024389</v>
       </c>
       <c r="J2">
-        <v>0.04592961479734035</v>
+        <v>0.05108727791211101</v>
       </c>
       <c r="K2">
-        <v>515.6</v>
+        <v>475.4</v>
       </c>
       <c r="L2">
-        <v>0.06625375857726608</v>
+        <v>0.05891830259766013</v>
       </c>
       <c r="M2">
         <v>214.3</v>
       </c>
       <c r="N2">
-        <v>0.05458899049850983</v>
+        <v>0.05322636729422284</v>
       </c>
       <c r="O2">
-        <v>0.4156322730799069</v>
+        <v>0.4507782919646613</v>
       </c>
       <c r="P2">
         <v>214.3</v>
       </c>
       <c r="Q2">
-        <v>0.05458899049850983</v>
+        <v>0.05322636729422284</v>
       </c>
       <c r="R2">
-        <v>0.4156322730799069</v>
+        <v>0.4507782919646613</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -638,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>690</v>
+        <v>716.9</v>
       </c>
       <c r="V2">
-        <v>0.1757648317497516</v>
+        <v>0.1780587154140381</v>
       </c>
       <c r="W2">
-        <v>0.06275865426749111</v>
+        <v>-0.02123847391337487</v>
       </c>
       <c r="X2">
-        <v>0.1215927862494203</v>
+        <v>0.1194406107013577</v>
       </c>
       <c r="Y2">
-        <v>-0.05883413198192916</v>
+        <v>-0.1406790846147326</v>
       </c>
       <c r="Z2">
-        <v>0.6243741976893453</v>
+        <v>0.6222440207106205</v>
       </c>
       <c r="AA2">
-        <v>0.02867726638927006</v>
+        <v>0.005545961414640595</v>
       </c>
       <c r="AB2">
-        <v>0.07777348259264126</v>
+        <v>0.07734138397540044</v>
       </c>
       <c r="AC2">
-        <v>-0.0490962162033712</v>
+        <v>-0.07179542256075984</v>
       </c>
       <c r="AD2">
-        <v>5838.9</v>
+        <v>5972.299999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5838.9</v>
+        <v>5972.299999999999</v>
       </c>
       <c r="AG2">
-        <v>5148.9</v>
+        <v>5255.4</v>
       </c>
       <c r="AH2">
-        <v>0.5979661225242202</v>
+        <v>0.5973195979396909</v>
       </c>
       <c r="AI2">
-        <v>0.4203157280966332</v>
+        <v>0.4156551877731688</v>
       </c>
       <c r="AJ2">
-        <v>0.5673969100566416</v>
+        <v>0.5662170315462852</v>
       </c>
       <c r="AK2">
-        <v>0.3900179522334244</v>
+        <v>0.3849686847599165</v>
       </c>
       <c r="AL2">
-        <v>294.6</v>
+        <v>305.3</v>
       </c>
       <c r="AM2">
-        <v>234.1</v>
+        <v>243.44</v>
       </c>
       <c r="AN2">
-        <v>5.831319284929592</v>
+        <v>5.91680041213418</v>
       </c>
       <c r="AO2">
-        <v>1.637474541751527</v>
+        <v>1.551097281362594</v>
       </c>
       <c r="AP2">
-        <v>5.142215120343553</v>
+        <v>5.206562444272722</v>
       </c>
       <c r="AQ2">
-        <v>2.060657838530542</v>
+        <v>1.945243181071311</v>
       </c>
     </row>
     <row r="3">
@@ -781,10 +781,10 @@
         <v>0.06275865426749111</v>
       </c>
       <c r="X3">
-        <v>0.1215927862494203</v>
+        <v>0.1215617448925203</v>
       </c>
       <c r="Y3">
-        <v>-0.05883413198192916</v>
+        <v>-0.05880309062502923</v>
       </c>
       <c r="Z3">
         <v>0.6243741976893453</v>
@@ -793,10 +793,10 @@
         <v>0.02867726638927006</v>
       </c>
       <c r="AB3">
-        <v>0.07777348259264126</v>
+        <v>0.07776100291556468</v>
       </c>
       <c r="AC3">
-        <v>-0.0490962162033712</v>
+        <v>-0.04908373652629461</v>
       </c>
       <c r="AD3">
         <v>5838.9</v>
@@ -839,6 +839,134 @@
       </c>
       <c r="AQ3">
         <v>2.060657838530542</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Masisa S.A. (SNSE:MASISA)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Paper/Forest Products</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.09210000000000002</v>
+      </c>
+      <c r="G4">
+        <v>0.02107466852756455</v>
+      </c>
+      <c r="H4">
+        <v>0.02107466852756455</v>
+      </c>
+      <c r="I4">
+        <v>-0.03087927424982554</v>
+      </c>
+      <c r="J4">
+        <v>-0.03087927424982554</v>
+      </c>
+      <c r="K4">
+        <v>-40.2</v>
+      </c>
+      <c r="L4">
+        <v>-0.1402651779483601</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>26.9</v>
+      </c>
+      <c r="V4">
+        <v>0.2676616915422885</v>
+      </c>
+      <c r="W4">
+        <v>-0.1052356020942408</v>
+      </c>
+      <c r="X4">
+        <v>0.117319476510195</v>
+      </c>
+      <c r="Y4">
+        <v>-0.2225550786044359</v>
+      </c>
+      <c r="Z4">
+        <v>0.5694869451178318</v>
+      </c>
+      <c r="AA4">
+        <v>-0.01758534355998887</v>
+      </c>
+      <c r="AB4">
+        <v>0.07692176503523619</v>
+      </c>
+      <c r="AC4">
+        <v>-0.09450710859522507</v>
+      </c>
+      <c r="AD4">
+        <v>133.4</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>133.4</v>
+      </c>
+      <c r="AG4">
+        <v>106.5</v>
+      </c>
+      <c r="AH4">
+        <v>0.5703292005130398</v>
+      </c>
+      <c r="AI4">
+        <v>0.2798405705894693</v>
+      </c>
+      <c r="AJ4">
+        <v>0.5144927536231884</v>
+      </c>
+      <c r="AK4">
+        <v>0.2367718986216096</v>
+      </c>
+      <c r="AL4">
+        <v>10.7</v>
+      </c>
+      <c r="AM4">
+        <v>9.34</v>
+      </c>
+      <c r="AN4">
+        <v>16.50990099009901</v>
+      </c>
+      <c r="AO4">
+        <v>-0.8271028037383178</v>
+      </c>
+      <c r="AP4">
+        <v>13.18069306930693</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.9475374732334046</v>
       </c>
     </row>
   </sheetData>
@@ -1133,49 +1261,49 @@
         <v>1.63747454175153</v>
       </c>
       <c r="F2">
-        <v>4.50377430680187</v>
+        <v>4.52601304784222</v>
       </c>
       <c r="G2">
         <v>5.83131928492959</v>
       </c>
       <c r="H2">
-        <v>2.73053830020973</v>
+        <v>2.82805752521722</v>
       </c>
       <c r="I2">
         <v>0.59796612252422</v>
       </c>
       <c r="J2">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="K2">
         <v>3925.7</v>
       </c>
       <c r="L2">
-        <v>6411.35177232254</v>
+        <v>6470.11993667362</v>
       </c>
       <c r="M2">
         <v>9074.6</v>
       </c>
       <c r="N2">
-        <v>8455.439772322539</v>
+        <v>8611.85393667362</v>
       </c>
       <c r="O2">
         <v>5838.9</v>
       </c>
       <c r="P2">
-        <v>2734.088</v>
+        <v>2831.734</v>
       </c>
       <c r="Q2">
-        <v>0.0777734825926413</v>
+        <v>0.0777610029155647</v>
       </c>
       <c r="R2">
-        <v>0.0801147811288218</v>
+        <v>0.0794783832134536</v>
       </c>
       <c r="S2">
         <v>0.0483122072898587</v>
       </c>
       <c r="T2">
-        <v>0.0483852072898587</v>
+        <v>0.0464872072898587</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,16 +1316,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.12159278624942</v>
+        <v>0.12156174489252</v>
       </c>
       <c r="X2">
-        <v>0.0924540598439741</v>
+        <v>0.0929536522526684</v>
       </c>
       <c r="Y2">
         <v>1.38760296413234</v>
       </c>
       <c r="Z2">
-        <v>0.854135530989282</v>
+        <v>0.863635700686294</v>
       </c>
       <c r="AA2">
         <v>5838.9</v>
@@ -1230,7 +1358,7 @@
         <v>3925.7</v>
       </c>
       <c r="AK2">
-        <v>0.05462137816692637</v>
+        <v>0.05459900767788712</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08213808209396509</v>
+        <v>0.08212319963045955</v>
       </c>
       <c r="C2">
-        <v>8674.64168760764</v>
+        <v>8674.795392704607</v>
       </c>
       <c r="D2">
-        <v>7984.64168760764</v>
+        <v>7984.795392704608</v>
       </c>
       <c r="E2">
         <v>-5838.9</v>
@@ -1469,19 +1597,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08213808209396509</v>
+        <v>0.08212319963045955</v>
       </c>
       <c r="T2">
         <v>0.6652721574126821</v>
       </c>
       <c r="U2">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V2">
         <v>0.27</v>
       </c>
       <c r="W2">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1628,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08202056134520996</v>
+        <v>0.08199549906435591</v>
       </c>
       <c r="C3">
-        <v>8602.90254920279</v>
+        <v>8605.320378551693</v>
       </c>
       <c r="D3">
-        <v>8010.54854920279</v>
+        <v>8012.966378551692</v>
       </c>
       <c r="E3">
         <v>-5741.254</v>
@@ -1533,37 +1661,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M3">
-        <v>5.866679664418547</v>
+        <v>5.729975264418547</v>
       </c>
       <c r="N3">
-        <v>810.299987002248</v>
+        <v>810.4366914022481</v>
       </c>
       <c r="O3">
-        <v>218.780996490607</v>
+        <v>218.817906678607</v>
       </c>
       <c r="P3">
-        <v>591.5189905116411</v>
+        <v>591.6187847236411</v>
       </c>
       <c r="Q3">
-        <v>1110.418990511641</v>
+        <v>1110.518784723641</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08240602956799128</v>
+        <v>0.0823910373651084</v>
       </c>
       <c r="T3">
         <v>0.6701776995835029</v>
       </c>
       <c r="U3">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V3">
         <v>0.27</v>
       </c>
       <c r="W3">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>139.11900996005</v>
+        <v>142.4380785262408</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1710,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08190304059645484</v>
+        <v>0.08186779849825225</v>
       </c>
       <c r="C4">
-        <v>8531.332072147359</v>
+        <v>8536.044847094714</v>
       </c>
       <c r="D4">
-        <v>8036.62407214736</v>
+        <v>8041.336847094713</v>
       </c>
       <c r="E4">
         <v>-5643.607999999999</v>
@@ -1615,37 +1743,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M4">
-        <v>11.73335932883709</v>
+        <v>11.45995052883709</v>
       </c>
       <c r="N4">
-        <v>804.4333073378295</v>
+        <v>804.7067161378295</v>
       </c>
       <c r="O4">
-        <v>217.196992981214</v>
+        <v>217.270813357214</v>
       </c>
       <c r="P4">
-        <v>587.2363143566156</v>
+        <v>587.4359027806155</v>
       </c>
       <c r="Q4">
-        <v>1106.136314356615</v>
+        <v>1106.335902780615</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08267944535781395</v>
+        <v>0.08266434117597457</v>
       </c>
       <c r="T4">
         <v>0.6751833548598507</v>
       </c>
       <c r="U4">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V4">
         <v>0.27</v>
       </c>
       <c r="W4">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>69.559504980025</v>
+        <v>71.21903926312042</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1792,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08178551984769972</v>
+        <v>0.08174009793214859</v>
       </c>
       <c r="C5">
-        <v>8459.931908873337</v>
+        <v>8466.970924709605</v>
       </c>
       <c r="D5">
-        <v>8062.869908873338</v>
+        <v>8069.908924709605</v>
       </c>
       <c r="E5">
         <v>-5545.962</v>
@@ -1697,37 +1825,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M5">
-        <v>17.60003899325564</v>
+        <v>17.18992579325564</v>
       </c>
       <c r="N5">
-        <v>798.5666276734109</v>
+        <v>798.976740873411</v>
       </c>
       <c r="O5">
-        <v>215.612989471821</v>
+        <v>215.723720035821</v>
       </c>
       <c r="P5">
-        <v>582.9536382015899</v>
+        <v>583.25302083759</v>
       </c>
       <c r="Q5">
-        <v>1101.85363820159</v>
+        <v>1102.15302083759</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08295849858660202</v>
+        <v>0.08294328011696168</v>
       </c>
       <c r="T5">
         <v>0.6802922195233395</v>
       </c>
       <c r="U5">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V5">
         <v>0.27</v>
       </c>
       <c r="W5">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>46.37300332001667</v>
+        <v>47.47935950874695</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1874,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08166799909894461</v>
+        <v>0.08161239736604495</v>
       </c>
       <c r="C6">
-        <v>8388.70373346935</v>
+        <v>8398.100768101407</v>
       </c>
       <c r="D6">
-        <v>8089.28773346935</v>
+        <v>8098.684768101407</v>
       </c>
       <c r="E6">
         <v>-5448.316</v>
@@ -1779,37 +1907,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M6">
-        <v>23.46671865767419</v>
+        <v>22.91990105767419</v>
       </c>
       <c r="N6">
-        <v>792.6999480089925</v>
+        <v>793.2467656089924</v>
       </c>
       <c r="O6">
-        <v>214.028985962428</v>
+        <v>214.176626714428</v>
       </c>
       <c r="P6">
-        <v>578.6709620465645</v>
+        <v>579.0701388945645</v>
       </c>
       <c r="Q6">
-        <v>1097.570962046565</v>
+        <v>1097.970138894565</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08324336542432319</v>
+        <v>0.08322803028588605</v>
       </c>
       <c r="T6">
         <v>0.6855075188673179</v>
       </c>
       <c r="U6">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V6">
         <v>0.27</v>
       </c>
       <c r="W6">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>34.7797524900125</v>
+        <v>35.60951963156021</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1956,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08155047835018948</v>
+        <v>0.08148469679994129</v>
       </c>
       <c r="C7">
-        <v>8317.649242036619</v>
+        <v>8329.436564846932</v>
       </c>
       <c r="D7">
-        <v>8115.879242036618</v>
+        <v>8127.666564846932</v>
       </c>
       <c r="E7">
         <v>-5350.67</v>
@@ -1861,37 +1989,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M7">
-        <v>29.33339832209274</v>
+        <v>28.64987632209274</v>
       </c>
       <c r="N7">
-        <v>786.8332683445739</v>
+        <v>787.5167903445739</v>
       </c>
       <c r="O7">
-        <v>212.444982453035</v>
+        <v>212.629533393035</v>
       </c>
       <c r="P7">
-        <v>574.3882858915389</v>
+        <v>574.8872569515389</v>
       </c>
       <c r="Q7">
-        <v>1093.288285891539</v>
+        <v>1093.787256951539</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08353422945862796</v>
+        <v>0.0835187751952088</v>
       </c>
       <c r="T7">
         <v>0.6908326139869588</v>
       </c>
       <c r="U7">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V7">
         <v>0.27</v>
       </c>
       <c r="W7">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.82380199201</v>
+        <v>28.48761570524817</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +2038,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08143295760143436</v>
+        <v>0.08135699623383763</v>
       </c>
       <c r="C8">
-        <v>8246.770153051937</v>
+        <v>8260.980533949132</v>
       </c>
       <c r="D8">
-        <v>8142.646153051938</v>
+        <v>8156.856533949132</v>
       </c>
       <c r="E8">
         <v>-5253.023999999999</v>
@@ -1943,37 +2071,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M8">
-        <v>35.20007798651127</v>
+        <v>34.37985158651128</v>
       </c>
       <c r="N8">
-        <v>780.9665886801554</v>
+        <v>781.7868150801553</v>
       </c>
       <c r="O8">
-        <v>210.860978943642</v>
+        <v>211.0824400716419</v>
       </c>
       <c r="P8">
-        <v>570.1056097365134</v>
+        <v>570.7043750085134</v>
       </c>
       <c r="Q8">
-        <v>1089.005609736513</v>
+        <v>1089.604375008513</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08383128208940728</v>
+        <v>0.08381570616643204</v>
       </c>
       <c r="T8">
         <v>0.6962710090027624</v>
       </c>
       <c r="U8">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V8">
         <v>0.27</v>
       </c>
       <c r="W8">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.18650166000834</v>
+        <v>23.73967975437347</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +2120,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08131543685267925</v>
+        <v>0.08122929566773397</v>
       </c>
       <c r="C9">
-        <v>8176.068207737905</v>
+        <v>8192.734926403456</v>
       </c>
       <c r="D9">
-        <v>8169.590207737905</v>
+        <v>8186.256926403456</v>
       </c>
       <c r="E9">
         <v>-5155.378</v>
@@ -2025,37 +2153,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M9">
-        <v>41.06675765092983</v>
+        <v>40.10982685092983</v>
       </c>
       <c r="N9">
-        <v>775.0999090157368</v>
+        <v>776.0568398157368</v>
       </c>
       <c r="O9">
-        <v>209.276975434249</v>
+        <v>209.5353467502489</v>
       </c>
       <c r="P9">
-        <v>565.8229335814879</v>
+        <v>566.5214930654879</v>
       </c>
       <c r="Q9">
-        <v>1084.722933581488</v>
+        <v>1085.421493065488</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08413472294880553</v>
+        <v>0.08411902274993965</v>
       </c>
       <c r="T9">
         <v>0.7018263587500886</v>
       </c>
       <c r="U9">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V9">
         <v>0.27</v>
       </c>
       <c r="W9">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.87414428000714</v>
+        <v>20.34829693232012</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2202,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08119791610392413</v>
+        <v>0.08110159510163033</v>
       </c>
       <c r="C10">
-        <v>8105.545170440488</v>
+        <v>8124.702025776502</v>
       </c>
       <c r="D10">
-        <v>8196.713170440487</v>
+        <v>8215.870025776501</v>
       </c>
       <c r="E10">
         <v>-5057.732</v>
@@ -2107,37 +2235,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M10">
-        <v>46.93343731534838</v>
+        <v>45.83980211534838</v>
       </c>
       <c r="N10">
-        <v>769.2332293513183</v>
+        <v>770.3268645513183</v>
       </c>
       <c r="O10">
-        <v>207.692971924856</v>
+        <v>207.988253428856</v>
       </c>
       <c r="P10">
-        <v>561.5402574264624</v>
+        <v>562.3386111224623</v>
       </c>
       <c r="Q10">
-        <v>1080.440257426462</v>
+        <v>1081.238611122462</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08444476034862547</v>
+        <v>0.08442893317221917</v>
       </c>
       <c r="T10">
         <v>0.7075024769701828</v>
       </c>
       <c r="U10">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V10">
         <v>0.27</v>
       </c>
       <c r="W10">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.38987624500625</v>
+        <v>17.80475981578011</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2284,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.081080395355169</v>
+        <v>0.08097389453552667</v>
       </c>
       <c r="C11">
-        <v>8035.202829014142</v>
+        <v>8056.884148797284</v>
       </c>
       <c r="D11">
-        <v>8224.016829014143</v>
+        <v>8245.698148797284</v>
       </c>
       <c r="E11">
         <v>-4960.085999999999</v>
@@ -2189,37 +2317,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M11">
-        <v>52.80011697976692</v>
+        <v>51.56977737976693</v>
       </c>
       <c r="N11">
-        <v>763.3665496868997</v>
+        <v>764.5968892868997</v>
       </c>
       <c r="O11">
-        <v>206.1089684154629</v>
+        <v>206.4411601074629</v>
       </c>
       <c r="P11">
-        <v>557.2575812714367</v>
+        <v>558.1557291794368</v>
       </c>
       <c r="Q11">
-        <v>1076.157581271437</v>
+        <v>1077.055729179437</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08476161175723267</v>
+        <v>0.08474565481257076</v>
       </c>
       <c r="T11">
         <v>0.713303345041268</v>
       </c>
       <c r="U11">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V11">
         <v>0.27</v>
       </c>
       <c r="W11">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.45766777333889</v>
+        <v>15.82645316958232</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2366,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.0809628746064139</v>
+        <v>0.08084619396942301</v>
       </c>
       <c r="C12">
-        <v>7965.042995214676</v>
+        <v>7989.283645961398</v>
       </c>
       <c r="D12">
-        <v>8251.502995214676</v>
+        <v>8275.743645961398</v>
       </c>
       <c r="E12">
         <v>-4862.44</v>
@@ -2271,37 +2399,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M12">
-        <v>58.66679664418547</v>
+        <v>57.29975264418547</v>
       </c>
       <c r="N12">
-        <v>757.4998700224811</v>
+        <v>758.8669140224812</v>
       </c>
       <c r="O12">
-        <v>204.5249649060699</v>
+        <v>204.8940667860699</v>
       </c>
       <c r="P12">
-        <v>552.9749051164112</v>
+        <v>553.9728472364112</v>
       </c>
       <c r="Q12">
-        <v>1071.874905116411</v>
+        <v>1072.872847236411</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08508550430825336</v>
+        <v>0.08506941471159683</v>
       </c>
       <c r="T12">
         <v>0.7192331212917108</v>
       </c>
       <c r="U12">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V12">
         <v>0.27</v>
       </c>
       <c r="W12">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>13.911900996005</v>
+        <v>14.24380785262408</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2448,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08093368385765877</v>
+        <v>0.08071849340331935</v>
       </c>
       <c r="C13">
-        <v>7874.252739456053</v>
+        <v>7921.902902148469</v>
       </c>
       <c r="D13">
-        <v>8258.358739456053</v>
+        <v>8306.008902148469</v>
       </c>
       <c r="E13">
         <v>-4764.794</v>
@@ -2353,45 +2481,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M13">
-        <v>65.714992908604</v>
+        <v>63.02972790860402</v>
       </c>
       <c r="N13">
-        <v>750.4516737580626</v>
+        <v>753.1369387580626</v>
       </c>
       <c r="O13">
-        <v>202.6219519146769</v>
+        <v>203.3469734646769</v>
       </c>
       <c r="P13">
-        <v>547.8297218433856</v>
+        <v>549.7899652933856</v>
       </c>
       <c r="Q13">
-        <v>1066.729721843386</v>
+        <v>1068.689965293386</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08541667534356664</v>
+        <v>0.08540045011397181</v>
       </c>
       <c r="T13">
         <v>0.7252961509410398</v>
       </c>
       <c r="U13">
-        <v>0.06118110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V13">
         <v>0.27</v>
       </c>
       <c r="W13">
-        <v>0.04466220728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>12.41979387872393</v>
+        <v>12.94891622965826</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2530,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08082419310890367</v>
+        <v>0.08072219283721571</v>
       </c>
       <c r="C14">
-        <v>7802.423576379596</v>
+        <v>7823.377016655045</v>
       </c>
       <c r="D14">
-        <v>8284.175576379595</v>
+        <v>8305.129016655044</v>
       </c>
       <c r="E14">
         <v>-4667.148</v>
@@ -2435,37 +2563,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M14">
-        <v>71.68908317302255</v>
+        <v>70.51733117302255</v>
       </c>
       <c r="N14">
-        <v>744.477583493644</v>
+        <v>745.6493354936441</v>
       </c>
       <c r="O14">
-        <v>201.0089475432839</v>
+        <v>201.3253205832839</v>
       </c>
       <c r="P14">
-        <v>543.4686359503601</v>
+        <v>544.3240149103602</v>
       </c>
       <c r="Q14">
-        <v>1062.36863595036</v>
+        <v>1063.22401491036</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08575537299331888</v>
+        <v>0.08573900904821895</v>
       </c>
       <c r="T14">
         <v>0.7314969767187628</v>
       </c>
       <c r="U14">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V14">
         <v>0.27</v>
       </c>
       <c r="W14">
-        <v>0.04466220728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.38481105549694</v>
+        <v>11.57398689215997</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2612,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08071470236014854</v>
+        <v>0.08060544227111206</v>
       </c>
       <c r="C15">
-        <v>7730.756333904738</v>
+        <v>7753.589548280804</v>
       </c>
       <c r="D15">
-        <v>8310.154333904738</v>
+        <v>8332.987548280804</v>
       </c>
       <c r="E15">
         <v>-4569.501999999999</v>
@@ -2517,37 +2645,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M15">
-        <v>77.66317343744112</v>
+        <v>76.39377543744111</v>
       </c>
       <c r="N15">
-        <v>738.5034932292256</v>
+        <v>739.7728912292255</v>
       </c>
       <c r="O15">
-        <v>199.3959431718909</v>
+        <v>199.7386806318909</v>
       </c>
       <c r="P15">
-        <v>539.1075500573347</v>
+        <v>540.0342105973345</v>
       </c>
       <c r="Q15">
-        <v>1058.007550057335</v>
+        <v>1058.934210597335</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08610185679593897</v>
+        <v>0.08608535094647177</v>
       </c>
       <c r="T15">
         <v>0.7378403502155138</v>
       </c>
       <c r="U15">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V15">
         <v>0.27</v>
       </c>
       <c r="W15">
-        <v>0.04466220728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.50905635892025</v>
+        <v>10.68368020814766</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2694,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08083005161139342</v>
+        <v>0.0804886917050084</v>
       </c>
       <c r="C16">
-        <v>7605.746112727467</v>
+        <v>7683.989604957427</v>
       </c>
       <c r="D16">
-        <v>8282.790112727467</v>
+        <v>8361.033604957427</v>
       </c>
       <c r="E16">
         <v>-4471.856</v>
@@ -2599,45 +2727,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M16">
-        <v>86.64476050185965</v>
+        <v>82.27021970185966</v>
       </c>
       <c r="N16">
-        <v>729.521906164807</v>
+        <v>733.896446964807</v>
       </c>
       <c r="O16">
-        <v>196.9709146644979</v>
+        <v>198.1520406804979</v>
       </c>
       <c r="P16">
-        <v>532.5509915003091</v>
+        <v>535.7444062843091</v>
       </c>
       <c r="Q16">
-        <v>1051.450991500309</v>
+        <v>1054.644406284309</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.0864563983614107</v>
+        <v>0.08643974730747464</v>
       </c>
       <c r="T16">
         <v>0.7443312440261427</v>
       </c>
       <c r="U16">
-        <v>0.06338110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V16">
         <v>0.27</v>
       </c>
       <c r="W16">
-        <v>0.04626820728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>9.419688645214148</v>
+        <v>9.920560193279972</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2776,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08073662086263829</v>
+        <v>0.08055809113890475</v>
       </c>
       <c r="C17">
-        <v>7530.250717534281</v>
+        <v>7569.649621485966</v>
       </c>
       <c r="D17">
-        <v>8304.94071753428</v>
+        <v>8344.339621485966</v>
       </c>
       <c r="E17">
         <v>-4374.21</v>
@@ -2681,37 +2809,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M17">
-        <v>92.8336719662782</v>
+        <v>90.6366369662782</v>
       </c>
       <c r="N17">
-        <v>723.3329947003884</v>
+        <v>725.5300297003885</v>
       </c>
       <c r="O17">
-        <v>195.2999085691049</v>
+        <v>195.8931080191049</v>
       </c>
       <c r="P17">
-        <v>528.0330861312835</v>
+        <v>529.6369216812836</v>
       </c>
       <c r="Q17">
-        <v>1046.933086131284</v>
+        <v>1048.536921681284</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08681928208136411</v>
+        <v>0.08680248240638347</v>
       </c>
       <c r="T17">
         <v>0.750974864749963</v>
       </c>
       <c r="U17">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V17">
         <v>0.27</v>
       </c>
       <c r="W17">
-        <v>0.04626820728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.791709402199871</v>
+        <v>9.004820721341696</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2858,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08064319011388317</v>
+        <v>0.08045375057280109</v>
       </c>
       <c r="C18">
-        <v>7454.874114425611</v>
+        <v>7497.127976151069</v>
       </c>
       <c r="D18">
-        <v>8327.21011442561</v>
+        <v>8369.463976151068</v>
       </c>
       <c r="E18">
         <v>-4276.564</v>
@@ -2763,37 +2891,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M18">
-        <v>99.02258343069674</v>
+        <v>96.67907943069675</v>
       </c>
       <c r="N18">
-        <v>717.1440832359699</v>
+        <v>719.4875872359698</v>
       </c>
       <c r="O18">
-        <v>193.6289024737119</v>
+        <v>194.2616485537119</v>
       </c>
       <c r="P18">
-        <v>523.5151807622581</v>
+        <v>525.2259386822579</v>
       </c>
       <c r="Q18">
-        <v>1042.415180762258</v>
+        <v>1044.125938682258</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08719080588988784</v>
+        <v>0.08717385405526631</v>
       </c>
       <c r="T18">
         <v>0.7577766669195883</v>
       </c>
       <c r="U18">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V18">
         <v>0.27</v>
       </c>
       <c r="W18">
-        <v>0.04626820728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.242227564562381</v>
+        <v>8.44201942625784</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2940,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08054975936512807</v>
+        <v>0.08034941000669742</v>
       </c>
       <c r="C19">
-        <v>7379.617261580759</v>
+        <v>7424.758083878714</v>
       </c>
       <c r="D19">
-        <v>8349.599261580759</v>
+        <v>8394.740083878714</v>
       </c>
       <c r="E19">
         <v>-4178.918</v>
@@ -2845,37 +2973,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M19">
-        <v>105.2114948951153</v>
+        <v>102.7215218951153</v>
       </c>
       <c r="N19">
-        <v>710.9551717715514</v>
+        <v>713.4451447715513</v>
       </c>
       <c r="O19">
-        <v>191.9578963783189</v>
+        <v>192.6301890883189</v>
       </c>
       <c r="P19">
-        <v>518.9972753932325</v>
+        <v>520.8149556832325</v>
       </c>
       <c r="Q19">
-        <v>1037.897275393233</v>
+        <v>1039.714955683232</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08757128207933987</v>
+        <v>0.08755417441858007</v>
       </c>
       <c r="T19">
         <v>0.7647423679366747</v>
       </c>
       <c r="U19">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V19">
         <v>0.27</v>
       </c>
       <c r="W19">
-        <v>0.04626820728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.757390648999886</v>
+        <v>7.945430048242672</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +3022,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08065342861637294</v>
+        <v>0.08035018944059377</v>
       </c>
       <c r="C20">
-        <v>7257.135922906612</v>
+        <v>7326.922703007628</v>
       </c>
       <c r="D20">
-        <v>8324.763922906612</v>
+        <v>8394.550703007628</v>
       </c>
       <c r="E20">
         <v>-4081.272</v>
@@ -2927,37 +3055,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M20">
-        <v>114.0368483595338</v>
+        <v>110.1700667595339</v>
       </c>
       <c r="N20">
-        <v>702.1298183071328</v>
+        <v>705.9965999071328</v>
       </c>
       <c r="O20">
-        <v>189.5750509429259</v>
+        <v>190.6190819749259</v>
       </c>
       <c r="P20">
-        <v>512.554767364207</v>
+        <v>515.377517932207</v>
       </c>
       <c r="Q20">
-        <v>1031.454767364207</v>
+        <v>1034.277517932207</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.08796103817585167</v>
+        <v>0.08794377088831612</v>
       </c>
       <c r="T20">
         <v>0.7718779641005191</v>
       </c>
       <c r="U20">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V20">
         <v>0.27</v>
       </c>
       <c r="W20">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.157043345265624</v>
+        <v>7.408243370207793</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +3104,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08057094786761781</v>
+        <v>0.08025168887449013</v>
       </c>
       <c r="C21">
-        <v>7179.2372350646</v>
+        <v>7253.277500165766</v>
       </c>
       <c r="D21">
-        <v>8344.5112350646</v>
+        <v>8418.551500165766</v>
       </c>
       <c r="E21">
         <v>-3983.626</v>
@@ -3009,37 +3137,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M21">
-        <v>120.3722288239524</v>
+        <v>116.2906260239524</v>
       </c>
       <c r="N21">
-        <v>695.7944378427143</v>
+        <v>699.8760406427142</v>
       </c>
       <c r="O21">
-        <v>187.8644982175329</v>
+        <v>188.9665309735329</v>
       </c>
       <c r="P21">
-        <v>507.9299396251814</v>
+        <v>510.9095096691814</v>
       </c>
       <c r="Q21">
-        <v>1026.829939625181</v>
+        <v>1029.809509669181</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.08836041787968478</v>
+        <v>0.08834298702397159</v>
       </c>
       <c r="T21">
         <v>0.7791897478239648</v>
       </c>
       <c r="U21">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V21">
         <v>0.27</v>
       </c>
       <c r="W21">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.780356853409538</v>
+        <v>7.018335824407383</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3186,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08048846711886271</v>
+        <v>0.08015318830838648</v>
       </c>
       <c r="C22">
-        <v>7101.432455845708</v>
+        <v>7179.769931833158</v>
       </c>
       <c r="D22">
-        <v>8364.352455845708</v>
+        <v>8442.689931833158</v>
       </c>
       <c r="E22">
         <v>-3885.98</v>
@@ -3091,37 +3219,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M22">
-        <v>126.7076092883709</v>
+        <v>122.411185288371</v>
       </c>
       <c r="N22">
-        <v>689.4590573782957</v>
+        <v>693.7554813782957</v>
       </c>
       <c r="O22">
-        <v>186.1539454921399</v>
+        <v>187.3139799721399</v>
       </c>
       <c r="P22">
-        <v>503.3051118861558</v>
+        <v>506.4415014061559</v>
       </c>
       <c r="Q22">
-        <v>1022.205111886156</v>
+        <v>1025.341501406156</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08876978207611372</v>
+        <v>0.08875218356301842</v>
       </c>
       <c r="T22">
         <v>0.7866843261404967</v>
       </c>
       <c r="U22">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V22">
         <v>0.27</v>
       </c>
       <c r="W22">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.44133901073906</v>
+        <v>6.667419033187014</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3268,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08040598637010758</v>
+        <v>0.08005468774228282</v>
       </c>
       <c r="C23">
-        <v>7023.722256722224</v>
+        <v>7106.401185328504</v>
       </c>
       <c r="D23">
-        <v>8384.288256722224</v>
+        <v>8466.967185328504</v>
       </c>
       <c r="E23">
         <v>-3788.334</v>
@@ -3173,37 +3301,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M23">
-        <v>133.0429897527895</v>
+        <v>128.5317445527895</v>
       </c>
       <c r="N23">
-        <v>683.1236769138771</v>
+        <v>687.6349221138771</v>
       </c>
       <c r="O23">
-        <v>184.4433927667469</v>
+        <v>185.6614289707468</v>
       </c>
       <c r="P23">
-        <v>498.6802841471303</v>
+        <v>501.9734931431303</v>
       </c>
       <c r="Q23">
-        <v>1017.58028414713</v>
+        <v>1020.87349314313</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.08918950992308514</v>
+        <v>0.08917173950811709</v>
       </c>
       <c r="T23">
         <v>0.7943686406169406</v>
       </c>
       <c r="U23">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V23">
         <v>0.27</v>
       </c>
       <c r="W23">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.134608581656248</v>
+        <v>6.349922888749537</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3350,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08054834562135246</v>
+        <v>0.08011678717617916</v>
       </c>
       <c r="C24">
-        <v>6891.726966788985</v>
+        <v>6993.433416821201</v>
       </c>
       <c r="D24">
-        <v>8349.938966788985</v>
+        <v>8451.6454168212</v>
       </c>
       <c r="E24">
         <v>-3690.688</v>
@@ -3255,37 +3383,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M24">
-        <v>142.385867017208</v>
+        <v>136.800515817208</v>
       </c>
       <c r="N24">
-        <v>673.7807996494587</v>
+        <v>679.3661508494586</v>
       </c>
       <c r="O24">
-        <v>181.9208159053539</v>
+        <v>183.4288607293538</v>
       </c>
       <c r="P24">
-        <v>491.8599837441049</v>
+        <v>495.9372901201048</v>
       </c>
       <c r="Q24">
-        <v>1010.759983744105</v>
+        <v>1014.837290120105</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.08962000002254301</v>
+        <v>0.08960205329796186</v>
       </c>
       <c r="T24">
         <v>0.8022499887979087</v>
       </c>
       <c r="U24">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V24">
         <v>0.27</v>
       </c>
       <c r="W24">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.73207639047511</v>
+        <v>5.966108108519292</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3432,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08047608487259734</v>
+        <v>0.08002558661007551</v>
       </c>
       <c r="C25">
-        <v>6811.481225324991</v>
+        <v>6918.308428814447</v>
       </c>
       <c r="D25">
-        <v>8367.339225324991</v>
+        <v>8474.166428814447</v>
       </c>
       <c r="E25">
         <v>-3593.042</v>
@@ -3337,37 +3465,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M25">
-        <v>148.8579518816266</v>
+        <v>143.0187210816266</v>
       </c>
       <c r="N25">
-        <v>667.30871478504</v>
+        <v>673.14794558504</v>
       </c>
       <c r="O25">
-        <v>180.1733529919608</v>
+        <v>181.7499453079608</v>
       </c>
       <c r="P25">
-        <v>487.1353617930792</v>
+        <v>491.3980002770792</v>
       </c>
       <c r="Q25">
-        <v>1006.035361793079</v>
+        <v>1010.298000277079</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09006167168302578</v>
+        <v>0.09004354406936106</v>
       </c>
       <c r="T25">
         <v>0.8103360473212396</v>
       </c>
       <c r="U25">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V25">
         <v>0.27</v>
       </c>
       <c r="W25">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.482855677845756</v>
+        <v>5.706712103801062</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3514,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08040382412384223</v>
+        <v>0.07993438604397186</v>
       </c>
       <c r="C26">
-        <v>6731.3081553499</v>
+        <v>6843.303784501022</v>
       </c>
       <c r="D26">
-        <v>8384.812155349899</v>
+        <v>8496.807784501021</v>
       </c>
       <c r="E26">
         <v>-3495.396</v>
@@ -3419,37 +3547,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M26">
-        <v>155.3300367460451</v>
+        <v>149.2369263460451</v>
       </c>
       <c r="N26">
-        <v>660.8366299206216</v>
+        <v>666.9297403206215</v>
       </c>
       <c r="O26">
-        <v>178.4258900785678</v>
+        <v>180.0710298865678</v>
       </c>
       <c r="P26">
-        <v>482.4107398420538</v>
+        <v>486.8587104340537</v>
       </c>
       <c r="Q26">
-        <v>1001.310739842054</v>
+        <v>1005.758710434054</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09051496628194229</v>
+        <v>0.09049665301895497</v>
       </c>
       <c r="T26">
         <v>0.8186348968583425</v>
       </c>
       <c r="U26">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V26">
         <v>0.27</v>
       </c>
       <c r="W26">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.254403357935518</v>
+        <v>5.468932432809352</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3596,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08033156337508711</v>
+        <v>0.0798431854778682</v>
       </c>
       <c r="C27">
-        <v>6651.208213080772</v>
+        <v>6768.420451071232</v>
       </c>
       <c r="D27">
-        <v>8402.358213080772</v>
+        <v>8519.570451071231</v>
       </c>
       <c r="E27">
         <v>-3397.75</v>
@@ -3501,37 +3629,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M27">
-        <v>161.8021216104637</v>
+        <v>155.4551316104637</v>
       </c>
       <c r="N27">
-        <v>654.3645450562029</v>
+        <v>660.7115350562029</v>
       </c>
       <c r="O27">
-        <v>176.6784271651748</v>
+        <v>178.3921144651748</v>
       </c>
       <c r="P27">
-        <v>477.6861178910281</v>
+        <v>482.3194205910281</v>
       </c>
       <c r="Q27">
-        <v>996.5861178910282</v>
+        <v>1001.219420591028</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09098034873682992</v>
+        <v>0.09096184487387138</v>
       </c>
       <c r="T27">
         <v>0.8271550490497681</v>
       </c>
       <c r="U27">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V27">
         <v>0.27</v>
       </c>
       <c r="W27">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.044227223618095</v>
+        <v>5.250175135496977</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3678,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08025930262633198</v>
+        <v>0.07975198491176455</v>
       </c>
       <c r="C28">
-        <v>6571.181858561411</v>
+        <v>6693.659406107494</v>
       </c>
       <c r="D28">
-        <v>8419.977858561411</v>
+        <v>8542.455406107494</v>
       </c>
       <c r="E28">
         <v>-3300.104</v>
@@ -3583,37 +3711,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M28">
-        <v>168.2742064748822</v>
+        <v>161.6733368748822</v>
       </c>
       <c r="N28">
-        <v>647.8924601917844</v>
+        <v>654.4933297917844</v>
       </c>
       <c r="O28">
-        <v>174.9309642517818</v>
+        <v>176.7131990437818</v>
       </c>
       <c r="P28">
-        <v>472.9614959400026</v>
+        <v>477.7801307480026</v>
       </c>
       <c r="Q28">
-        <v>991.8614959400026</v>
+        <v>996.6801307480025</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09145830909590369</v>
+        <v>0.09143960948162337</v>
       </c>
       <c r="T28">
         <v>0.8359054756247456</v>
       </c>
       <c r="U28">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V28">
         <v>0.27</v>
       </c>
       <c r="W28">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.850218484248169</v>
+        <v>5.048245322593247</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3760,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08018704187757686</v>
+        <v>0.0796607843456609</v>
       </c>
       <c r="C29">
-        <v>6491.22955570254</v>
+        <v>6619.021637724315</v>
       </c>
       <c r="D29">
-        <v>8437.67155570254</v>
+        <v>8565.463637724315</v>
       </c>
       <c r="E29">
         <v>-3202.458</v>
@@ -3665,37 +3793,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M29">
-        <v>174.7462913393008</v>
+        <v>167.8915421393008</v>
       </c>
       <c r="N29">
-        <v>641.4203753273658</v>
+        <v>648.2751245273658</v>
       </c>
       <c r="O29">
-        <v>173.1835013383888</v>
+        <v>175.0342836223888</v>
       </c>
       <c r="P29">
-        <v>468.236873988977</v>
+        <v>473.2408409049771</v>
       </c>
       <c r="Q29">
-        <v>987.136873988977</v>
+        <v>992.140840904977</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09194936425933564</v>
+        <v>0.09193046353068364</v>
       </c>
       <c r="T29">
         <v>0.8448956399141062</v>
       </c>
       <c r="U29">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V29">
         <v>0.27</v>
       </c>
       <c r="W29">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.670580762609347</v>
+        <v>4.861273273608312</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3842,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08011478112882175</v>
+        <v>0.07956958377955724</v>
       </c>
       <c r="C30">
-        <v>6411.351772322538</v>
+        <v>6544.508144710489</v>
       </c>
       <c r="D30">
-        <v>8455.439772322537</v>
+        <v>8588.596144710489</v>
       </c>
       <c r="E30">
         <v>-3104.812</v>
@@ -3747,37 +3875,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M30">
-        <v>181.2183762037193</v>
+        <v>174.1097474037193</v>
       </c>
       <c r="N30">
-        <v>634.9482904629473</v>
+        <v>642.0569192629473</v>
       </c>
       <c r="O30">
-        <v>171.4360384249958</v>
+        <v>173.3553682009958</v>
       </c>
       <c r="P30">
-        <v>463.5122520379515</v>
+        <v>468.7015510619515</v>
       </c>
       <c r="Q30">
-        <v>982.4122520379515</v>
+        <v>987.6015510619516</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09245405984397406</v>
+        <v>0.09243495241444002</v>
       </c>
       <c r="T30">
         <v>0.8541355309892824</v>
       </c>
       <c r="U30">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V30">
         <v>0.27</v>
       </c>
       <c r="W30">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.503774306801871</v>
+        <v>4.687656370979444</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3924,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08059294038006662</v>
+        <v>0.07947838321345359</v>
       </c>
       <c r="C31">
-        <v>6197.502694735106</v>
+        <v>6470.119936673625</v>
       </c>
       <c r="D31">
-        <v>8339.236694735106</v>
+        <v>8611.853936673624</v>
       </c>
       <c r="E31">
         <v>-3007.166</v>
@@ -3829,45 +3957,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M31">
-        <v>195.0529694681378</v>
+        <v>180.3279526681379</v>
       </c>
       <c r="N31">
-        <v>621.1136971985288</v>
+        <v>635.8387139985288</v>
       </c>
       <c r="O31">
-        <v>167.7006982436028</v>
+        <v>171.6764527796028</v>
       </c>
       <c r="P31">
-        <v>453.412998954926</v>
+        <v>464.162261218926</v>
       </c>
       <c r="Q31">
-        <v>972.312998954926</v>
+        <v>983.062261218926</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09297297220564452</v>
+        <v>0.09295365225266841</v>
       </c>
       <c r="T31">
         <v>0.8636357006862945</v>
       </c>
       <c r="U31">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V31">
         <v>0.27</v>
       </c>
       <c r="W31">
-        <v>0.05028320728985866</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.184333460250082</v>
+        <v>4.526013047842222</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +4006,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.0805396596313115</v>
+        <v>0.07993468264734993</v>
       </c>
       <c r="C32">
-        <v>6112.646709947032</v>
+        <v>6257.353953965736</v>
       </c>
       <c r="D32">
-        <v>8352.026709947031</v>
+        <v>8496.733953965735</v>
       </c>
       <c r="E32">
         <v>-2909.52</v>
@@ -3911,37 +4039,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M32">
-        <v>201.7789339325564</v>
+        <v>193.8696079325564</v>
       </c>
       <c r="N32">
-        <v>614.3877327341103</v>
+        <v>622.2970587341102</v>
       </c>
       <c r="O32">
-        <v>165.8846878382098</v>
+        <v>168.0202058582098</v>
       </c>
       <c r="P32">
-        <v>448.5030448959005</v>
+        <v>454.2768528759004</v>
       </c>
       <c r="Q32">
-        <v>967.4030448959005</v>
+        <v>973.1768528759004</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.0935067106347913</v>
+        <v>0.09348717208627477</v>
       </c>
       <c r="T32">
         <v>0.8734073038032213</v>
       </c>
       <c r="U32">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V32">
         <v>0.27</v>
       </c>
       <c r="W32">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.044855678241746</v>
+        <v>4.209874231295685</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +4088,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.0810973888825564</v>
+        <v>0.07986173208124628</v>
       </c>
       <c r="C33">
-        <v>5883.031469422895</v>
+        <v>6177.905547396846</v>
       </c>
       <c r="D33">
-        <v>8220.057469422894</v>
+        <v>8514.931547396845</v>
       </c>
       <c r="E33">
         <v>-2811.874</v>
@@ -3993,45 +4121,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M33">
-        <v>216.6778685969749</v>
+        <v>200.3319281969749</v>
       </c>
       <c r="N33">
-        <v>599.4887980696917</v>
+        <v>615.8347384696917</v>
       </c>
       <c r="O33">
-        <v>161.8619754788168</v>
+        <v>166.2753793868168</v>
       </c>
       <c r="P33">
-        <v>437.626822590875</v>
+        <v>449.5593590828749</v>
       </c>
       <c r="Q33">
-        <v>956.5268225908749</v>
+        <v>968.4593590828749</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09405591974304378</v>
+        <v>0.0940361562628842</v>
       </c>
       <c r="T33">
         <v>0.8834621417931023</v>
       </c>
       <c r="U33">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V33">
         <v>0.27</v>
       </c>
       <c r="W33">
-        <v>0.05225420728985867</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.766728332484905</v>
+        <v>4.07407183673776</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4170,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08106381813380126</v>
+        <v>0.08060638151514263</v>
       </c>
       <c r="C34">
-        <v>5793.210869469246</v>
+        <v>5898.090684090078</v>
       </c>
       <c r="D34">
-        <v>8227.882869469246</v>
+        <v>8332.762684090078</v>
       </c>
       <c r="E34">
         <v>-2714.228</v>
@@ -4075,37 +4203,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M34">
-        <v>223.6674772613935</v>
+        <v>217.7306004613935</v>
       </c>
       <c r="N34">
-        <v>592.4991894052731</v>
+        <v>598.4360662052732</v>
       </c>
       <c r="O34">
-        <v>159.9747811394238</v>
+        <v>161.5777378754238</v>
       </c>
       <c r="P34">
-        <v>432.5244082658494</v>
+        <v>436.8583283298494</v>
       </c>
       <c r="Q34">
-        <v>951.4244082658494</v>
+        <v>955.7583283298494</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.09462128206036249</v>
+        <v>0.09460128703292331</v>
       </c>
       <c r="T34">
         <v>0.8938127103120975</v>
       </c>
       <c r="U34">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V34">
         <v>0.27</v>
       </c>
       <c r="W34">
-        <v>0.05225420728985867</v>
+        <v>0.05086720728985867</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.649018072094751</v>
+        <v>3.748516124684016</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4252,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08103024738504613</v>
+        <v>0.08055898094903896</v>
       </c>
       <c r="C35">
-        <v>5703.405183094599</v>
+        <v>5811.808011139639</v>
       </c>
       <c r="D35">
-        <v>8235.723183094598</v>
+        <v>8344.126011139639</v>
       </c>
       <c r="E35">
         <v>-2616.582</v>
@@ -4157,37 +4285,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M35">
-        <v>230.6570859258121</v>
+        <v>224.534681725812</v>
       </c>
       <c r="N35">
-        <v>585.5095807408545</v>
+        <v>591.6319849408546</v>
       </c>
       <c r="O35">
-        <v>158.0875868000307</v>
+        <v>159.7406359340308</v>
       </c>
       <c r="P35">
-        <v>427.4219939408238</v>
+        <v>431.8913490068239</v>
       </c>
       <c r="Q35">
-        <v>946.3219939408237</v>
+        <v>950.7913490068238</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.09520352086476536</v>
+        <v>0.09518328737818749</v>
       </c>
       <c r="T35">
         <v>0.9044722510256897</v>
       </c>
       <c r="U35">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V35">
         <v>0.27</v>
       </c>
       <c r="W35">
-        <v>0.05225420728985867</v>
+        <v>0.05086720728985867</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.538441766879758</v>
+        <v>3.634924726966319</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4334,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08216321663629103</v>
+        <v>0.08051158038293531</v>
       </c>
       <c r="C36">
-        <v>5349.158640256521</v>
+        <v>5725.556372681376</v>
       </c>
       <c r="D36">
-        <v>7979.122640256521</v>
+        <v>8355.520372681376</v>
       </c>
       <c r="E36">
         <v>-2518.936</v>
@@ -4239,45 +4367,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M36">
-        <v>253.2505253902306</v>
+        <v>231.3387629902306</v>
       </c>
       <c r="N36">
-        <v>562.916141276436</v>
+        <v>584.827903676436</v>
       </c>
       <c r="O36">
-        <v>151.9873581446377</v>
+        <v>157.9035339926377</v>
       </c>
       <c r="P36">
-        <v>410.9287831317982</v>
+        <v>426.9243696837983</v>
       </c>
       <c r="Q36">
-        <v>929.8287831317982</v>
+        <v>945.8243696837983</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.09580340326930165</v>
+        <v>0.09578292409755056</v>
       </c>
       <c r="T36">
         <v>0.9154548081245422</v>
       </c>
       <c r="U36">
-        <v>0.07628110587651873</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V36">
         <v>0.27</v>
       </c>
       <c r="W36">
-        <v>0.05568520728985867</v>
+        <v>0.05086720728985867</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.222763962321679</v>
+        <v>3.528015176173191</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4416,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08216395588753592</v>
+        <v>0.08117957981683166</v>
       </c>
       <c r="C37">
-        <v>5251.350430832355</v>
+        <v>5470.150362309369</v>
       </c>
       <c r="D37">
-        <v>7978.960430832355</v>
+        <v>8197.760362309369</v>
       </c>
       <c r="E37">
         <v>-2421.29</v>
@@ -4321,37 +4449,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M37">
-        <v>260.6990702546491</v>
+        <v>247.7121522546491</v>
       </c>
       <c r="N37">
-        <v>555.4675964120174</v>
+        <v>568.4545144120175</v>
       </c>
       <c r="O37">
-        <v>149.9762510312447</v>
+        <v>153.4827188912447</v>
       </c>
       <c r="P37">
-        <v>405.4913453807727</v>
+        <v>414.9717955207727</v>
       </c>
       <c r="Q37">
-        <v>924.3913453807727</v>
+        <v>933.8717955207727</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.09642174359397751</v>
+        <v>0.09640101117750943</v>
       </c>
       <c r="T37">
         <v>0.9267752900572056</v>
       </c>
       <c r="U37">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V37">
         <v>0.27</v>
       </c>
       <c r="W37">
-        <v>0.05568520728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.130684991969631</v>
+        <v>3.294818842103652</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4498,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.0821646951387808</v>
+        <v>0.081152619250728</v>
       </c>
       <c r="C38">
-        <v>5153.542228003242</v>
+        <v>5378.756127096089</v>
       </c>
       <c r="D38">
-        <v>7978.798228003241</v>
+        <v>8204.012127096088</v>
       </c>
       <c r="E38">
         <v>-2323.644</v>
@@ -4403,37 +4531,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M38">
-        <v>268.1476151190677</v>
+        <v>254.7896423190677</v>
       </c>
       <c r="N38">
-        <v>548.0190515475989</v>
+        <v>561.377024347599</v>
       </c>
       <c r="O38">
-        <v>147.9651439178517</v>
+        <v>151.5717965738517</v>
       </c>
       <c r="P38">
-        <v>400.0539076297472</v>
+        <v>409.8052277737472</v>
       </c>
       <c r="Q38">
-        <v>918.9539076297472</v>
+        <v>928.7052277737472</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.09705940705379949</v>
+        <v>0.09703841347871701</v>
       </c>
       <c r="T38">
         <v>0.9384495370502647</v>
       </c>
       <c r="U38">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V38">
         <v>0.27</v>
       </c>
       <c r="W38">
-        <v>0.05568520728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.043721519970475</v>
+        <v>3.203296096489662</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4580,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08467736439002567</v>
+        <v>0.08112565868462435</v>
       </c>
       <c r="C39">
-        <v>4540.221328638554</v>
+        <v>5287.371434584858</v>
       </c>
       <c r="D39">
-        <v>7463.123328638553</v>
+        <v>8210.273434584858</v>
       </c>
       <c r="E39">
         <v>-2225.998</v>
@@ -4485,45 +4613,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M39">
-        <v>309.1961485834862</v>
+        <v>261.8671323834862</v>
       </c>
       <c r="N39">
-        <v>506.9705180831804</v>
+        <v>554.2995342831805</v>
       </c>
       <c r="O39">
-        <v>136.8820398824587</v>
+        <v>149.6608742564588</v>
       </c>
       <c r="P39">
-        <v>370.0884782007217</v>
+        <v>404.6386600267217</v>
       </c>
       <c r="Q39">
-        <v>888.9884782007217</v>
+        <v>923.5386600267217</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.09771731379806026</v>
+        <v>0.09769605077361372</v>
       </c>
       <c r="T39">
         <v>0.9504943950589764</v>
       </c>
       <c r="U39">
-        <v>0.08558110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V39">
         <v>0.27</v>
       </c>
       <c r="W39">
-        <v>0.06247420728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.639640469021861</v>
+        <v>3.116720526314266</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4662,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08474599364127056</v>
+        <v>0.08109869811852069</v>
       </c>
       <c r="C40">
-        <v>4429.424076915195</v>
+        <v>5195.996306641358</v>
       </c>
       <c r="D40">
-        <v>7449.972076915195</v>
+        <v>8216.544306641357</v>
       </c>
       <c r="E40">
         <v>-2128.352</v>
@@ -4567,45 +4695,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M40">
-        <v>317.5528012479047</v>
+        <v>268.9446224479047</v>
       </c>
       <c r="N40">
-        <v>498.6138654187619</v>
+        <v>547.2220442187619</v>
       </c>
       <c r="O40">
-        <v>134.6257436630657</v>
+        <v>147.7499519390657</v>
       </c>
       <c r="P40">
-        <v>363.9881217556962</v>
+        <v>399.4720922796962</v>
       </c>
       <c r="Q40">
-        <v>882.8881217556961</v>
+        <v>918.3720922796962</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.098396443340523</v>
+        <v>0.09837490217479743</v>
       </c>
       <c r="T40">
         <v>0.9629277968744208</v>
       </c>
       <c r="U40">
-        <v>0.08558110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V40">
         <v>0.27</v>
       </c>
       <c r="W40">
-        <v>0.06247420728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.570176246152865</v>
+        <v>3.034701565095469</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4744,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08481462289251544</v>
+        <v>0.08329239755241705</v>
       </c>
       <c r="C41">
-        <v>4318.673093000763</v>
+        <v>4617.596079898089</v>
       </c>
       <c r="D41">
-        <v>7436.867093000763</v>
+        <v>7735.790079898088</v>
       </c>
       <c r="E41">
         <v>-2030.706</v>
@@ -4649,37 +4777,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M41">
-        <v>325.9094539123233</v>
+        <v>305.7260257123233</v>
       </c>
       <c r="N41">
-        <v>490.2572127543434</v>
+        <v>510.4406409543433</v>
       </c>
       <c r="O41">
-        <v>132.3694474436727</v>
+        <v>137.8189730576727</v>
       </c>
       <c r="P41">
-        <v>357.8877653106706</v>
+        <v>372.6216678966706</v>
       </c>
       <c r="Q41">
-        <v>876.7877653106706</v>
+        <v>891.5216678966706</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.09909783942536157</v>
+        <v>0.09907601099897076</v>
       </c>
       <c r="T41">
         <v>0.9757688512084044</v>
       </c>
       <c r="U41">
-        <v>0.08558110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V41">
         <v>0.27</v>
       </c>
       <c r="W41">
-        <v>0.06247420728985867</v>
+        <v>0.05860520728985868</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.504274291123305</v>
+        <v>2.669601532172628</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4826,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08625565214376031</v>
+        <v>0.0833223769863134</v>
       </c>
       <c r="C42">
-        <v>3956.126085335574</v>
+        <v>4513.769378514993</v>
       </c>
       <c r="D42">
-        <v>7171.966085335574</v>
+        <v>7729.609378514993</v>
       </c>
       <c r="E42">
         <v>-1933.06</v>
@@ -4731,45 +4859,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M42">
-        <v>352.6235545767419</v>
+        <v>313.5651545767419</v>
       </c>
       <c r="N42">
-        <v>463.5431120899248</v>
+        <v>502.6015120899247</v>
       </c>
       <c r="O42">
-        <v>125.1566402642797</v>
+        <v>135.7024082642797</v>
       </c>
       <c r="P42">
-        <v>338.3864718256451</v>
+        <v>366.8991038256451</v>
       </c>
       <c r="Q42">
-        <v>857.2864718256451</v>
+        <v>885.799103825645</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.09982261537969475</v>
+        <v>0.09980049011728322</v>
       </c>
       <c r="T42">
         <v>0.9890379406868541</v>
       </c>
       <c r="U42">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V42">
         <v>0.27</v>
       </c>
       <c r="W42">
-        <v>0.06590520728985866</v>
+        <v>0.05860520728985868</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.314555156833811</v>
+        <v>2.602861493868312</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4908,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08635859139500521</v>
+        <v>0.08335235642020974</v>
       </c>
       <c r="C43">
-        <v>3840.277361981894</v>
+        <v>4409.952545696547</v>
       </c>
       <c r="D43">
-        <v>7153.763361981893</v>
+        <v>7723.438545696547</v>
       </c>
       <c r="E43">
         <v>-1835.414</v>
@@ -4813,45 +4941,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M43">
-        <v>361.4391434411604</v>
+        <v>321.4042834411605</v>
       </c>
       <c r="N43">
-        <v>454.7275232255062</v>
+        <v>494.7623832255061</v>
       </c>
       <c r="O43">
-        <v>122.7764312708867</v>
+        <v>133.5858434708867</v>
       </c>
       <c r="P43">
-        <v>331.9510919546195</v>
+        <v>361.1765397546195</v>
       </c>
       <c r="Q43">
-        <v>850.8510919546195</v>
+        <v>880.0765397546195</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.100571960010446</v>
+        <v>0.1005495278497757</v>
       </c>
       <c r="T43">
         <v>1.002756829808641</v>
       </c>
       <c r="U43">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V43">
         <v>0.27</v>
       </c>
       <c r="W43">
-        <v>0.06590520728985866</v>
+        <v>0.05860520728985868</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.258102592032986</v>
+        <v>2.539377067188597</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4990,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08646153064625009</v>
+        <v>0.08457807585410609</v>
       </c>
       <c r="C44">
-        <v>3724.520803122905</v>
+        <v>4068.179715949218</v>
       </c>
       <c r="D44">
-        <v>7135.652803122905</v>
+        <v>7479.311715949218</v>
       </c>
       <c r="E44">
         <v>-1737.768</v>
@@ -4895,37 +5023,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M44">
-        <v>370.254732305579</v>
+        <v>345.237827105579</v>
       </c>
       <c r="N44">
-        <v>445.9119343610877</v>
+        <v>470.9288395610877</v>
       </c>
       <c r="O44">
-        <v>120.3962222774937</v>
+        <v>127.1507866814937</v>
       </c>
       <c r="P44">
-        <v>325.515712083594</v>
+        <v>343.778052879594</v>
       </c>
       <c r="Q44">
-        <v>844.4157120835939</v>
+        <v>862.6780528795939</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1013471441112232</v>
+        <v>0.1013243944695956</v>
       </c>
       <c r="T44">
         <v>1.016948784072558</v>
       </c>
       <c r="U44">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V44">
         <v>0.27</v>
       </c>
       <c r="W44">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.20433824460363</v>
+        <v>2.364070801595767</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +5072,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08656446989749496</v>
+        <v>0.08463652528800245</v>
       </c>
       <c r="C45">
-        <v>3608.855710551756</v>
+        <v>3959.277262585028</v>
       </c>
       <c r="D45">
-        <v>7117.633710551755</v>
+        <v>7468.055262585027</v>
       </c>
       <c r="E45">
         <v>-1640.122</v>
@@ -4977,37 +5105,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M45">
-        <v>379.0703211699974</v>
+        <v>353.4577753699975</v>
       </c>
       <c r="N45">
-        <v>437.0963454966692</v>
+        <v>462.7088912966692</v>
       </c>
       <c r="O45">
-        <v>118.0160132841007</v>
+        <v>124.9314006501007</v>
       </c>
       <c r="P45">
-        <v>319.0803322125685</v>
+        <v>337.7774906465685</v>
       </c>
       <c r="Q45">
-        <v>837.9803322125684</v>
+        <v>856.6774906465685</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1021495276541329</v>
+        <v>0.1021264493918653</v>
       </c>
       <c r="T45">
         <v>1.031638701643982</v>
       </c>
       <c r="U45">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V45">
         <v>0.27</v>
       </c>
       <c r="W45">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.153074564496569</v>
+        <v>2.309092410860981</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5154,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08666740914873984</v>
+        <v>0.08469497472189877</v>
       </c>
       <c r="C46">
-        <v>3493.281393096327</v>
+        <v>3850.408640497584</v>
       </c>
       <c r="D46">
-        <v>7099.705393096326</v>
+        <v>7456.832640497583</v>
       </c>
       <c r="E46">
         <v>-1542.476000000001</v>
@@ -5059,37 +5187,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M46">
-        <v>387.885910034416</v>
+        <v>361.677723634416</v>
       </c>
       <c r="N46">
-        <v>428.2807566322506</v>
+        <v>454.4889430322506</v>
       </c>
       <c r="O46">
-        <v>115.6358042907077</v>
+        <v>122.7120146187077</v>
       </c>
       <c r="P46">
-        <v>312.644952341543</v>
+        <v>331.7769284135429</v>
       </c>
       <c r="Q46">
-        <v>831.544952341543</v>
+        <v>850.6769284135429</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1029805677521465</v>
+        <v>0.1029571491327874</v>
       </c>
       <c r="T46">
         <v>1.04685325912867</v>
       </c>
       <c r="U46">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V46">
         <v>0.27</v>
       </c>
       <c r="W46">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.104141051667101</v>
+        <v>2.256613037886869</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5236,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08677034839998472</v>
+        <v>0.08475342415579513</v>
       </c>
       <c r="C47">
-        <v>3377.797166530869</v>
+        <v>3741.573697395846</v>
       </c>
       <c r="D47">
-        <v>7081.867166530868</v>
+        <v>7445.643697395846</v>
       </c>
       <c r="E47">
         <v>-1444.83</v>
@@ -5141,37 +5269,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M47">
-        <v>396.7014988988346</v>
+        <v>369.8976718988346</v>
       </c>
       <c r="N47">
-        <v>419.465167767832</v>
+        <v>446.268994767832</v>
       </c>
       <c r="O47">
-        <v>113.2555952973147</v>
+        <v>120.4926285873146</v>
       </c>
       <c r="P47">
-        <v>306.2095724705174</v>
+        <v>325.7763661805174</v>
       </c>
       <c r="Q47">
-        <v>825.1095724705174</v>
+        <v>844.6763661805173</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1038418274900879</v>
+        <v>0.1038180561370159</v>
       </c>
       <c r="T47">
         <v>1.062621073249166</v>
       </c>
       <c r="U47">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V47">
         <v>0.27</v>
       </c>
       <c r="W47">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.057382361630054</v>
+        <v>2.206466081489382</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5318,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08687328765122962</v>
+        <v>0.08481187358969147</v>
       </c>
       <c r="C48">
-        <v>3262.402353488954</v>
+        <v>3632.772281901483</v>
       </c>
       <c r="D48">
-        <v>7064.118353488953</v>
+        <v>7434.488281901482</v>
       </c>
       <c r="E48">
         <v>-1347.184</v>
@@ -5223,37 +5351,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M48">
-        <v>405.5170877632531</v>
+        <v>378.1176201632532</v>
       </c>
       <c r="N48">
-        <v>410.6495789034135</v>
+        <v>438.0490465034135</v>
       </c>
       <c r="O48">
-        <v>110.8753863039217</v>
+        <v>118.2732425559216</v>
       </c>
       <c r="P48">
-        <v>299.7741925994918</v>
+        <v>319.7758039474919</v>
       </c>
       <c r="Q48">
-        <v>818.6741925994918</v>
+        <v>838.6758039474919</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1047349857368419</v>
+        <v>0.1047108485858453</v>
       </c>
       <c r="T48">
         <v>1.078972880485235</v>
       </c>
       <c r="U48">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V48">
         <v>0.27</v>
       </c>
       <c r="W48">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.012656658116358</v>
+        <v>2.158499427543961</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5400,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.09256875690247449</v>
+        <v>0.08487032302358782</v>
       </c>
       <c r="C49">
-        <v>2304.492546320665</v>
+        <v>3524.004243541988</v>
       </c>
       <c r="D49">
-        <v>6203.854546320665</v>
+        <v>7423.366243541987</v>
       </c>
       <c r="E49">
         <v>-1249.538</v>
@@ -5305,45 +5433,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M49">
-        <v>489.1392772276716</v>
+        <v>386.3375684276717</v>
       </c>
       <c r="N49">
-        <v>327.027389438995</v>
+        <v>429.829098238995</v>
       </c>
       <c r="O49">
-        <v>88.29739514852865</v>
+        <v>116.0538565245286</v>
       </c>
       <c r="P49">
-        <v>238.7299942904663</v>
+        <v>313.7752417144663</v>
       </c>
       <c r="Q49">
-        <v>757.6299942904664</v>
+        <v>832.6752417144663</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1056618480683791</v>
+        <v>0.1056373313157627</v>
       </c>
       <c r="T49">
         <v>1.095941737050967</v>
       </c>
       <c r="U49">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V49">
         <v>0.27</v>
       </c>
       <c r="W49">
-        <v>0.07780420728985867</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.668577243055415</v>
+        <v>2.112573907808983</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5482,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.09279068615371935</v>
+        <v>0.08492877245748416</v>
       </c>
       <c r="C50">
-        <v>2177.546765725995</v>
+        <v>3415.269432743959</v>
       </c>
       <c r="D50">
-        <v>6174.554765725994</v>
+        <v>7412.277432743957</v>
       </c>
       <c r="E50">
         <v>-1151.892000000001</v>
@@ -5387,45 +5515,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M50">
-        <v>499.5464958920901</v>
+        <v>394.5575166920902</v>
       </c>
       <c r="N50">
-        <v>316.6201707745765</v>
+        <v>421.6091499745764</v>
       </c>
       <c r="O50">
-        <v>85.48744610913566</v>
+        <v>113.8344704931356</v>
       </c>
       <c r="P50">
-        <v>231.1327246654408</v>
+        <v>307.7746794814408</v>
       </c>
       <c r="Q50">
-        <v>750.0327246654408</v>
+        <v>826.6746794814408</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1066243589511292</v>
+        <v>0.1065994479968308</v>
       </c>
       <c r="T50">
         <v>1.113563241946151</v>
       </c>
       <c r="U50">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V50">
         <v>0.27</v>
       </c>
       <c r="W50">
-        <v>0.07780420728985867</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.633815217158427</v>
+        <v>2.068561951396296</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5564,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.09301261540496424</v>
+        <v>0.0849872218913805</v>
       </c>
       <c r="C51">
-        <v>2050.876440253359</v>
+        <v>3306.567700826361</v>
       </c>
       <c r="D51">
-        <v>6145.530440253358</v>
+        <v>7401.221700826361</v>
       </c>
       <c r="E51">
         <v>-1054.246</v>
@@ -5469,45 +5597,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M51">
-        <v>509.9537145565088</v>
+        <v>402.7774649565088</v>
       </c>
       <c r="N51">
-        <v>306.2129521101579</v>
+        <v>413.3892017101579</v>
       </c>
       <c r="O51">
-        <v>82.67749706974263</v>
+        <v>111.6150844617426</v>
       </c>
       <c r="P51">
-        <v>223.5354550404152</v>
+        <v>301.7741172484152</v>
       </c>
       <c r="Q51">
-        <v>742.4354550404153</v>
+        <v>820.6741172484152</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1076246153586931</v>
+        <v>0.107599294743823</v>
       </c>
       <c r="T51">
         <v>1.131875786248989</v>
       </c>
       <c r="U51">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V51">
         <v>0.27</v>
       </c>
       <c r="W51">
-        <v>0.07780420728985867</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.600472049461316</v>
+        <v>2.0263464013678</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5646,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.09323454465620912</v>
+        <v>0.09022867132527684</v>
       </c>
       <c r="C52">
-        <v>1924.477703635078</v>
+        <v>2335.766413108651</v>
       </c>
       <c r="D52">
-        <v>6116.777703635077</v>
+        <v>6528.066413108651</v>
       </c>
       <c r="E52">
         <v>-956.6000000000004</v>
@@ -5551,37 +5679,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M52">
-        <v>520.3609332209273</v>
+        <v>480.3260732209273</v>
       </c>
       <c r="N52">
-        <v>295.8057334457393</v>
+        <v>335.8405934457393</v>
       </c>
       <c r="O52">
-        <v>79.86754803034961</v>
+        <v>90.67696023034962</v>
       </c>
       <c r="P52">
-        <v>215.9381854153897</v>
+        <v>245.1636332153897</v>
       </c>
       <c r="Q52">
-        <v>734.8381854153897</v>
+        <v>764.0636332153897</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1086648820225596</v>
+        <v>0.108639135360695</v>
       </c>
       <c r="T52">
         <v>1.15092083232394</v>
       </c>
       <c r="U52">
-        <v>0.1065811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V52">
         <v>0.27</v>
       </c>
       <c r="W52">
-        <v>0.07780420728985867</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.56846260847209</v>
+        <v>1.699192927824404</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5728,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.09345647390745401</v>
+        <v>0.0903907807591732</v>
       </c>
       <c r="C53">
-        <v>1798.346761622051</v>
+        <v>2214.387678838257</v>
       </c>
       <c r="D53">
-        <v>6088.29276162205</v>
+        <v>6504.333678838256</v>
       </c>
       <c r="E53">
         <v>-858.9540000000006</v>
@@ -5633,37 +5761,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M53">
-        <v>530.7681518853458</v>
+        <v>489.9325946853459</v>
       </c>
       <c r="N53">
-        <v>285.3985147813208</v>
+        <v>326.2340719813208</v>
       </c>
       <c r="O53">
-        <v>77.05759899095663</v>
+        <v>88.08319943495661</v>
       </c>
       <c r="P53">
-        <v>208.3409157903642</v>
+        <v>238.1508725463642</v>
       </c>
       <c r="Q53">
-        <v>727.2409157903642</v>
+        <v>757.0508725463642</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1097476085502573</v>
+        <v>0.1097214184517251</v>
       </c>
       <c r="T53">
         <v>1.170743227218277</v>
       </c>
       <c r="U53">
-        <v>0.1065811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V53">
         <v>0.27</v>
       </c>
       <c r="W53">
-        <v>0.07780420728985867</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.53770843967852</v>
+        <v>1.66587541943569</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5810,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.09367840315869889</v>
+        <v>0.09055289019306956</v>
       </c>
       <c r="C54">
-        <v>1672.47989031463</v>
+        <v>2093.180879837329</v>
       </c>
       <c r="D54">
-        <v>6060.07189031463</v>
+        <v>6480.772879837329</v>
       </c>
       <c r="E54">
         <v>-761.308</v>
@@ -5715,37 +5843,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M54">
-        <v>541.1753705497645</v>
+        <v>499.5391161497644</v>
       </c>
       <c r="N54">
-        <v>274.9912961169022</v>
+        <v>316.6275505169022</v>
       </c>
       <c r="O54">
-        <v>74.24764995156359</v>
+        <v>85.4894386395636</v>
       </c>
       <c r="P54">
-        <v>200.7436461653386</v>
+        <v>231.1381118773386</v>
       </c>
       <c r="Q54">
-        <v>719.6436461653386</v>
+        <v>750.0381118773386</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1108754486832758</v>
+        <v>0.110848796671548</v>
       </c>
       <c r="T54">
         <v>1.191391555233212</v>
       </c>
       <c r="U54">
-        <v>0.1065811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V54">
         <v>0.27</v>
       </c>
       <c r="W54">
-        <v>0.07780420728985867</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.508137123530855</v>
+        <v>1.633839353677312</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5892,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1216779592304275</v>
+        <v>0.09071499962696589</v>
       </c>
       <c r="C55">
-        <v>-661.3796875477619</v>
+        <v>1972.144154434087</v>
       </c>
       <c r="D55">
-        <v>3823.858312452237</v>
+        <v>6457.382154434086</v>
       </c>
       <c r="E55">
         <v>-663.6620000000003</v>
@@ -5797,45 +5925,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M55">
-        <v>890.0431544141829</v>
+        <v>509.145637614183</v>
       </c>
       <c r="N55">
-        <v>-73.87648774751631</v>
+        <v>307.0210290524836</v>
       </c>
       <c r="O55">
-        <v>-19.94665169182941</v>
+        <v>82.89567784417059</v>
       </c>
       <c r="P55">
-        <v>-53.92983605568691</v>
+        <v>224.125351208313</v>
       </c>
       <c r="Q55">
-        <v>464.9701639443131</v>
+        <v>743.0253512083131</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1129696123965051</v>
+        <v>0.11202414843264</v>
       </c>
       <c r="T55">
-        <v>1.229731190436656</v>
+        <v>1.212918535504101</v>
       </c>
       <c r="U55">
-        <v>0.1719811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V55">
-        <v>0.2475891184681286</v>
+        <v>0.27</v>
       </c>
       <c r="W55">
-        <v>0.1294004554793776</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.9169967350671429</v>
+        <v>1.603012196060758</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5974,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1229397702891927</v>
+        <v>0.09087710906086224</v>
       </c>
       <c r="C56">
-        <v>-821.5743143807795</v>
+        <v>1851.275667737027</v>
       </c>
       <c r="D56">
-        <v>3761.309685619221</v>
+        <v>6434.159667737027</v>
       </c>
       <c r="E56">
         <v>-566.0159999999996</v>
@@ -5879,45 +6007,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M56">
-        <v>906.8364214786017</v>
+        <v>518.7521590786016</v>
       </c>
       <c r="N56">
-        <v>-90.66975481193504</v>
+        <v>297.414507588065</v>
       </c>
       <c r="O56">
-        <v>-24.48083379922246</v>
+        <v>80.30191704877755</v>
       </c>
       <c r="P56">
-        <v>-66.18892101271257</v>
+        <v>217.1125905392875</v>
       </c>
       <c r="Q56">
-        <v>452.7110789872874</v>
+        <v>736.0125905392874</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1144298213616466</v>
+        <v>0.1132506024442143</v>
       </c>
       <c r="T56">
-        <v>1.256464477185279</v>
+        <v>1.235381471438941</v>
       </c>
       <c r="U56">
-        <v>0.1719811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V56">
-        <v>0.2430041347927928</v>
+        <v>0.27</v>
       </c>
       <c r="W56">
-        <v>0.1301889860422876</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.9000153140473808</v>
+        <v>1.573326785022596</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +6056,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1242015813479579</v>
+        <v>0.09103921849475859</v>
       </c>
       <c r="C57">
-        <v>-979.7556004701146</v>
+        <v>1730.57361115514</v>
       </c>
       <c r="D57">
-        <v>3700.774399529885</v>
+        <v>6411.103611155139</v>
       </c>
       <c r="E57">
         <v>-468.3699999999999</v>
@@ -5961,45 +6089,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M57">
-        <v>923.6296885430202</v>
+        <v>528.3586805430201</v>
       </c>
       <c r="N57">
-        <v>-107.4630218763535</v>
+        <v>287.8079861236465</v>
       </c>
       <c r="O57">
-        <v>-29.01501590661546</v>
+        <v>77.70815625338456</v>
       </c>
       <c r="P57">
-        <v>-78.44800596973808</v>
+        <v>210.0998298702619</v>
       </c>
       <c r="Q57">
-        <v>440.4519940302619</v>
+        <v>728.9998298702619</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1159549285030165</v>
+        <v>0.1145315655229696</v>
       </c>
       <c r="T57">
-        <v>1.284385910011618</v>
+        <v>1.258842760081998</v>
       </c>
       <c r="U57">
-        <v>0.1719811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V57">
-        <v>0.2385858777965602</v>
+        <v>0.27</v>
       </c>
       <c r="W57">
-        <v>0.1309488427665463</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.8836513992465194</v>
+        <v>1.544720843476731</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6138,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1254633924067231</v>
+        <v>0.09120132792865493</v>
       </c>
       <c r="C58">
-        <v>-1136.019215440374</v>
+        <v>1610.036201928336</v>
       </c>
       <c r="D58">
-        <v>3642.156784559625</v>
+        <v>6388.212201928335</v>
       </c>
       <c r="E58">
         <v>-370.7240000000002</v>
@@ -6043,45 +6171,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M58">
-        <v>940.4229556074387</v>
+        <v>537.9652020074386</v>
       </c>
       <c r="N58">
-        <v>-124.256288940772</v>
+        <v>278.201464659228</v>
       </c>
       <c r="O58">
-        <v>-33.54919801400845</v>
+        <v>75.11439545799156</v>
       </c>
       <c r="P58">
-        <v>-90.70709092676358</v>
+        <v>203.0870692012364</v>
       </c>
       <c r="Q58">
-        <v>428.1929090732364</v>
+        <v>721.9870692012364</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1175493586962668</v>
+        <v>0.1158707541962138</v>
       </c>
       <c r="T58">
-        <v>1.313576498875519</v>
+        <v>1.283370470936101</v>
       </c>
       <c r="U58">
-        <v>0.1719811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V58">
-        <v>0.2343254156930502</v>
+        <v>0.27</v>
       </c>
       <c r="W58">
-        <v>0.131681561750653</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.8678719099742601</v>
+        <v>1.517136542700361</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6220,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1267252034654883</v>
+        <v>0.1166202593473234</v>
       </c>
       <c r="C59">
-        <v>-1290.45486207344</v>
+        <v>-780.4781008033824</v>
       </c>
       <c r="D59">
-        <v>3585.36713792656</v>
+        <v>4095.343899196618</v>
       </c>
       <c r="E59">
         <v>-273.0779999999995</v>
@@ -6125,37 +6253,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M59">
-        <v>957.2162226718573</v>
+        <v>863.7104130718573</v>
       </c>
       <c r="N59">
-        <v>-141.0495560051907</v>
+        <v>-47.54374640519063</v>
       </c>
       <c r="O59">
-        <v>-38.08338012140148</v>
+        <v>-12.83681152940147</v>
       </c>
       <c r="P59">
-        <v>-102.9661758837892</v>
+        <v>-34.70693487578916</v>
       </c>
       <c r="Q59">
-        <v>415.9338241162108</v>
+        <v>484.1930651242108</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1192179484333893</v>
+        <v>0.1179878458330059</v>
       </c>
       <c r="T59">
-        <v>1.344124789547043</v>
+        <v>1.322145747755821</v>
       </c>
       <c r="U59">
-        <v>0.1719811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V59">
-        <v>0.230214443487909</v>
+        <v>0.2551375978162099</v>
       </c>
       <c r="W59">
-        <v>0.1323885712967208</v>
+        <v>0.1155885712967208</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8526460869922555</v>
+        <v>0.9449540659859623</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6302,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1279870145242535</v>
+        <v>0.1177140704060886</v>
       </c>
       <c r="C60">
-        <v>-1443.146734350913</v>
+        <v>-940.4141703418236</v>
       </c>
       <c r="D60">
-        <v>3530.321265649086</v>
+        <v>4033.053829658175</v>
       </c>
       <c r="E60">
         <v>-175.4320000000007</v>
@@ -6207,37 +6335,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M60">
-        <v>974.0094897362757</v>
+        <v>878.8632273362756</v>
       </c>
       <c r="N60">
-        <v>-157.842823069609</v>
+        <v>-62.69656066960897</v>
       </c>
       <c r="O60">
-        <v>-42.61756222879444</v>
+        <v>-16.92807138079442</v>
       </c>
       <c r="P60">
-        <v>-115.2252608408146</v>
+        <v>-45.76848928881455</v>
       </c>
       <c r="Q60">
-        <v>403.6747391591854</v>
+        <v>473.1315107111855</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1209659948246605</v>
+        <v>0.119706604067125</v>
       </c>
       <c r="T60">
-        <v>1.376127760726733</v>
+        <v>1.353625408416674</v>
       </c>
       <c r="U60">
-        <v>0.1719811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V60">
-        <v>0.2262452289450141</v>
+        <v>0.2507386737159304</v>
       </c>
       <c r="W60">
-        <v>0.133071201203269</v>
+        <v>0.116271201203269</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8379452923889409</v>
+        <v>0.928661754503446</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6384,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1292488255830186</v>
+        <v>0.1188078814648537</v>
       </c>
       <c r="C61">
-        <v>-1594.173933940813</v>
+        <v>-1098.483768328282</v>
       </c>
       <c r="D61">
-        <v>3476.940066059185</v>
+        <v>3972.630231671717</v>
       </c>
       <c r="E61">
         <v>-77.78600000000097</v>
@@ -6289,37 +6417,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M61">
-        <v>990.8027568006942</v>
+        <v>894.0160416006942</v>
       </c>
       <c r="N61">
-        <v>-174.6360901340275</v>
+        <v>-77.84937493402754</v>
       </c>
       <c r="O61">
-        <v>-47.15174433618744</v>
+        <v>-21.01933123218744</v>
       </c>
       <c r="P61">
-        <v>-127.4843457978401</v>
+        <v>-56.8300437018401</v>
       </c>
       <c r="Q61">
-        <v>391.4156542021599</v>
+        <v>462.0699562981599</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1227993117716034</v>
+        <v>0.1215092041663232</v>
       </c>
       <c r="T61">
-        <v>1.409691852451776</v>
+        <v>1.386640662280495</v>
       </c>
       <c r="U61">
-        <v>0.1719811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V61">
-        <v>0.2224105640476409</v>
+        <v>0.2464888656868469</v>
       </c>
       <c r="W61">
-        <v>0.1337306911129852</v>
+        <v>0.1169306911129851</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8237428298060775</v>
+        <v>0.9129217247660995</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6466,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1305106366417838</v>
+        <v>0.119901692523619</v>
       </c>
       <c r="C62">
-        <v>-1743.610849461489</v>
+        <v>-1254.769547418383</v>
       </c>
       <c r="D62">
-        <v>3425.14915053851</v>
+        <v>3913.990452581616</v>
       </c>
       <c r="E62">
         <v>19.85999999999967</v>
@@ -6371,37 +6499,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M62">
-        <v>1007.596023865113</v>
+        <v>909.1688558651127</v>
       </c>
       <c r="N62">
-        <v>-191.4293571984462</v>
+        <v>-93.0021891984461</v>
       </c>
       <c r="O62">
-        <v>-51.68592644358046</v>
+        <v>-25.11059108358045</v>
       </c>
       <c r="P62">
-        <v>-139.7434307548657</v>
+        <v>-67.89159811486566</v>
       </c>
       <c r="Q62">
-        <v>379.1565692451343</v>
+        <v>451.0084018851343</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1247242945658935</v>
+        <v>0.1234019342704813</v>
       </c>
       <c r="T62">
-        <v>1.44493414876307</v>
+        <v>1.421306678837507</v>
       </c>
       <c r="U62">
-        <v>0.1719811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V62">
-        <v>0.2187037213135136</v>
+        <v>0.2423807179253994</v>
       </c>
       <c r="W62">
-        <v>0.1343681980257107</v>
+        <v>0.1175681980257107</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8100137826426428</v>
+        <v>0.8977063626866644</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6548,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1647247491855734</v>
+        <v>0.1209955035823841</v>
       </c>
       <c r="C63">
-        <v>-2826.65677099444</v>
+        <v>-1409.349351129726</v>
       </c>
       <c r="D63">
-        <v>2439.749229005559</v>
+        <v>3857.056648870273</v>
       </c>
       <c r="E63">
         <v>117.5059999999994</v>
@@ -6453,45 +6581,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M63">
-        <v>1335.313684129531</v>
+        <v>924.3216701295313</v>
       </c>
       <c r="N63">
-        <v>-519.1470174628647</v>
+        <v>-108.1550034628647</v>
       </c>
       <c r="O63">
-        <v>-140.1696947149735</v>
+        <v>-29.20185093497346</v>
       </c>
       <c r="P63">
-        <v>-378.9773227478912</v>
+        <v>-78.95315252789121</v>
       </c>
       <c r="Q63">
-        <v>139.9226772521088</v>
+        <v>439.9468474721087</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1295949213112355</v>
+        <v>0.1253917274569039</v>
       </c>
       <c r="T63">
-        <v>1.534104852776745</v>
+        <v>1.457750439833341</v>
       </c>
       <c r="U63">
-        <v>0.2241811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V63">
-        <v>0.1650286390524428</v>
+        <v>0.2384072635331798</v>
       </c>
       <c r="W63">
-        <v>0.1871848030724453</v>
+        <v>0.1181848030724453</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.6112171816757139</v>
+        <v>0.8829898649377027</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6630,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1665085602443386</v>
+        <v>0.1220893146411493</v>
       </c>
       <c r="C64">
-        <v>-2960.356979962756</v>
+        <v>-1562.296558601086</v>
       </c>
       <c r="D64">
-        <v>2403.695020037243</v>
+        <v>3801.755441398913</v>
       </c>
       <c r="E64">
         <v>215.1519999999991</v>
@@ -6535,45 +6663,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M64">
-        <v>1357.20407239395</v>
+        <v>939.4744843939498</v>
       </c>
       <c r="N64">
-        <v>-541.037405727283</v>
+        <v>-123.3078177272831</v>
       </c>
       <c r="O64">
-        <v>-146.0800995463664</v>
+        <v>-33.29311078636645</v>
       </c>
       <c r="P64">
-        <v>-394.9573061809166</v>
+        <v>-90.01470694091668</v>
       </c>
       <c r="Q64">
-        <v>123.9426938190834</v>
+        <v>428.8852930590833</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1318000508194259</v>
+        <v>0.1274862466005066</v>
       </c>
       <c r="T64">
-        <v>1.574476033112975</v>
+        <v>1.496112293513165</v>
       </c>
       <c r="U64">
-        <v>0.2241811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V64">
-        <v>0.1623668868096614</v>
+        <v>0.2345619850890962</v>
       </c>
       <c r="W64">
-        <v>0.1877815176338013</v>
+        <v>0.1187815176338013</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.6013588400357832</v>
+        <v>0.8687480929225786</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6712,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1682923713031038</v>
+        <v>0.1231831256999145</v>
       </c>
       <c r="C65">
-        <v>-3093.00710073393</v>
+        <v>-1713.680400112539</v>
       </c>
       <c r="D65">
-        <v>2368.69089926607</v>
+        <v>3748.01759988746</v>
       </c>
       <c r="E65">
         <v>312.7979999999998</v>
@@ -6617,45 +6745,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M65">
-        <v>1379.094460658368</v>
+        <v>954.6272986583684</v>
       </c>
       <c r="N65">
-        <v>-562.9277939917018</v>
+        <v>-138.4606319917018</v>
       </c>
       <c r="O65">
-        <v>-151.9905043777595</v>
+        <v>-37.38437063775949</v>
       </c>
       <c r="P65">
-        <v>-410.9372896139423</v>
+        <v>-101.0762613539423</v>
       </c>
       <c r="Q65">
-        <v>107.9627103860577</v>
+        <v>417.8237386460577</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1341243765172482</v>
+        <v>0.1296939829951149</v>
       </c>
       <c r="T65">
-        <v>1.617029439413326</v>
+        <v>1.536547760905413</v>
       </c>
       <c r="U65">
-        <v>0.2241811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V65">
-        <v>0.1597896346380795</v>
+        <v>0.2308387789765708</v>
       </c>
       <c r="W65">
-        <v>0.1883592888757492</v>
+        <v>0.1193592888757492</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.5918134616225166</v>
+        <v>0.8549584406539661</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6794,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1700761823618691</v>
+        <v>0.1242769367586797</v>
       </c>
       <c r="C66">
-        <v>-3224.652350957147</v>
+        <v>-1863.566246219301</v>
       </c>
       <c r="D66">
-        <v>2334.691649042852</v>
+        <v>3695.777753780697</v>
       </c>
       <c r="E66">
         <v>410.4439999999995</v>
@@ -6699,45 +6827,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M66">
-        <v>1400.984848922787</v>
+        <v>969.780112922787</v>
       </c>
       <c r="N66">
-        <v>-584.8181822561204</v>
+        <v>-153.6134462561204</v>
       </c>
       <c r="O66">
-        <v>-157.9009092091525</v>
+        <v>-41.4756304891525</v>
       </c>
       <c r="P66">
-        <v>-426.9172730469679</v>
+        <v>-112.1378157669679</v>
       </c>
       <c r="Q66">
-        <v>91.98272695303211</v>
+        <v>406.7621842330321</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1365778314205052</v>
+        <v>0.1320243714116459</v>
       </c>
       <c r="T66">
-        <v>1.661946923841474</v>
+        <v>1.579229643152786</v>
       </c>
       <c r="U66">
-        <v>0.2241811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V66">
-        <v>0.1572929215968595</v>
+        <v>0.2272319230550619</v>
       </c>
       <c r="W66">
-        <v>0.1889190047663862</v>
+        <v>0.1199190047663862</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.5825663762846648</v>
+        <v>0.8415997150187479</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6876,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1718599934206342</v>
+        <v>0.1253707478174449</v>
       </c>
       <c r="C67">
-        <v>-3355.335388873474</v>
+        <v>-2012.01587303827</v>
       </c>
       <c r="D67">
-        <v>2301.654611126525</v>
+        <v>3644.974126961729</v>
       </c>
       <c r="E67">
         <v>508.0899999999992</v>
@@ -6781,45 +6909,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M67">
-        <v>1422.875237187205</v>
+        <v>984.9329271872055</v>
       </c>
       <c r="N67">
-        <v>-606.7085705205387</v>
+        <v>-168.7662605205388</v>
       </c>
       <c r="O67">
-        <v>-163.8113140405455</v>
+        <v>-45.56689034054548</v>
       </c>
       <c r="P67">
-        <v>-442.8972564799933</v>
+        <v>-123.1993701799933</v>
       </c>
       <c r="Q67">
-        <v>76.00274352000667</v>
+        <v>395.7006298200066</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1391714837468053</v>
+        <v>0.1344879248805501</v>
       </c>
       <c r="T67">
-        <v>1.709431121665516</v>
+        <v>1.624350490100009</v>
       </c>
       <c r="U67">
-        <v>0.2241811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V67">
-        <v>0.1548730304953694</v>
+        <v>0.2237360473157533</v>
       </c>
       <c r="W67">
-        <v>0.189461498629619</v>
+        <v>0.120461498629619</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.5736038166495162</v>
+        <v>0.8286520270953825</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6958,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1736438044793994</v>
+        <v>0.1264645588762101</v>
       </c>
       <c r="C68">
-        <v>-3485.096491873611</v>
+        <v>-2159.087705950865</v>
       </c>
       <c r="D68">
-        <v>2269.539508126388</v>
+        <v>3595.548294049135</v>
       </c>
       <c r="E68">
         <v>605.7359999999999</v>
@@ -6863,45 +6991,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M68">
-        <v>1444.765625451624</v>
+        <v>1000.085741451624</v>
       </c>
       <c r="N68">
-        <v>-628.5989587849575</v>
+        <v>-183.9190747849575</v>
       </c>
       <c r="O68">
-        <v>-169.7217188719385</v>
+        <v>-49.65815019193853</v>
       </c>
       <c r="P68">
-        <v>-458.877239913019</v>
+        <v>-134.260924593019</v>
       </c>
       <c r="Q68">
-        <v>60.02276008698101</v>
+        <v>384.639075406981</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1419177038570055</v>
+        <v>0.1370963932593898</v>
       </c>
       <c r="T68">
-        <v>1.759708507596855</v>
+        <v>1.672125504514715</v>
       </c>
       <c r="U68">
-        <v>0.2241811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V68">
-        <v>0.1525264694272577</v>
+        <v>0.2203461072049085</v>
       </c>
       <c r="W68">
-        <v>0.1899875532848751</v>
+        <v>0.1209875532848751</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.564912849730584</v>
+        <v>0.816096693351513</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +7040,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1754276155381646</v>
+        <v>0.1275583699349753</v>
       </c>
       <c r="C69">
-        <v>-3613.973720312805</v>
+        <v>-2304.837043743475</v>
       </c>
       <c r="D69">
-        <v>2238.308279687194</v>
+        <v>3547.444956256525</v>
       </c>
       <c r="E69">
         <v>703.3819999999996</v>
@@ -6945,45 +7073,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M69">
-        <v>1466.656013716042</v>
+        <v>1015.238555716043</v>
       </c>
       <c r="N69">
-        <v>-650.4893470493759</v>
+        <v>-199.071889049376</v>
       </c>
       <c r="O69">
-        <v>-175.6321237033315</v>
+        <v>-53.74941004333151</v>
       </c>
       <c r="P69">
-        <v>-474.8572233460443</v>
+        <v>-145.3224790060444</v>
       </c>
       <c r="Q69">
-        <v>44.04277665395563</v>
+        <v>373.5775209939555</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.144830361549642</v>
+        <v>0.1398629506308865</v>
       </c>
       <c r="T69">
-        <v>1.813033007827063</v>
+        <v>1.722795974348494</v>
       </c>
       <c r="U69">
-        <v>0.2241811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V69">
-        <v>0.1502499549581942</v>
+        <v>0.2170573593361786</v>
       </c>
       <c r="W69">
-        <v>0.1904979048160936</v>
+        <v>0.1214979048160936</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.5564813146599784</v>
+        <v>0.8039161456895503</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +7122,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1772114265969298</v>
+        <v>0.1667358366576072</v>
       </c>
       <c r="C70">
-        <v>-3742.003067983767</v>
+        <v>-3551.686708804209</v>
       </c>
       <c r="D70">
-        <v>2207.924932016233</v>
+        <v>2398.241291195791</v>
       </c>
       <c r="E70">
         <v>801.0280000000002</v>
@@ -7027,37 +7155,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M70">
-        <v>1488.546401980461</v>
+        <v>1388.947481980461</v>
       </c>
       <c r="N70">
-        <v>-672.3797353137946</v>
+        <v>-572.7808153137945</v>
       </c>
       <c r="O70">
-        <v>-181.5425285347246</v>
+        <v>-154.6508201347245</v>
       </c>
       <c r="P70">
-        <v>-490.8372067790701</v>
+        <v>-418.12999517907</v>
       </c>
       <c r="Q70">
-        <v>28.0627932209299</v>
+        <v>100.77000482093</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1479250603480683</v>
+        <v>0.1470638417876852</v>
       </c>
       <c r="T70">
-        <v>1.869690289321659</v>
+        <v>1.854682824733783</v>
       </c>
       <c r="U70">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V70">
-        <v>0.1480403967970442</v>
+        <v>0.1586561067707094</v>
       </c>
       <c r="W70">
-        <v>0.1909932460081587</v>
+        <v>0.1759932460081587</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5482977659149786</v>
+        <v>0.5876152102618866</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7204,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.178995237655695</v>
+        <v>0.1683696477163724</v>
       </c>
       <c r="C71">
-        <v>-3869.218600498398</v>
+        <v>-3681.300436672775</v>
       </c>
       <c r="D71">
-        <v>2178.355399501602</v>
+        <v>2366.273563327225</v>
       </c>
       <c r="E71">
         <v>898.674</v>
@@ -7109,37 +7237,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M71">
-        <v>1510.43679024488</v>
+        <v>1409.37318024488</v>
       </c>
       <c r="N71">
-        <v>-694.2701235782132</v>
+        <v>-593.206513578213</v>
       </c>
       <c r="O71">
-        <v>-187.4529333661176</v>
+        <v>-160.1657586661175</v>
       </c>
       <c r="P71">
-        <v>-506.8171902120956</v>
+        <v>-433.0407549120955</v>
       </c>
       <c r="Q71">
-        <v>12.08280978790435</v>
+        <v>85.85924508790447</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1512194171334899</v>
+        <v>0.1503304173292234</v>
       </c>
       <c r="T71">
-        <v>1.930002879299777</v>
+        <v>1.914511302951002</v>
       </c>
       <c r="U71">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V71">
-        <v>0.1458948837999856</v>
+        <v>0.1563567429044672</v>
       </c>
       <c r="W71">
-        <v>0.1914742294845118</v>
+        <v>0.1764742294845117</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5403514214814282</v>
+        <v>0.579099047794323</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7286,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1807790487144602</v>
+        <v>0.1700034587751376</v>
       </c>
       <c r="C72">
-        <v>-3995.652582696819</v>
+        <v>-3810.073137603278</v>
       </c>
       <c r="D72">
-        <v>2149.56741730318</v>
+        <v>2335.146862396722</v>
       </c>
       <c r="E72">
         <v>996.3199999999997</v>
@@ -7191,37 +7319,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M72">
-        <v>1532.327178509298</v>
+        <v>1429.798878509298</v>
       </c>
       <c r="N72">
-        <v>-716.1605118426315</v>
+        <v>-613.6322118426316</v>
       </c>
       <c r="O72">
-        <v>-193.3633381975105</v>
+        <v>-165.6806971975105</v>
       </c>
       <c r="P72">
-        <v>-522.797173645121</v>
+        <v>-447.9515146451211</v>
       </c>
       <c r="Q72">
-        <v>-3.897173645121029</v>
+        <v>70.94848535487893</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1547333977046062</v>
+        <v>0.1538147645735309</v>
       </c>
       <c r="T72">
-        <v>1.994336308609769</v>
+        <v>1.978328346382702</v>
       </c>
       <c r="U72">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V72">
-        <v>0.1438106711742716</v>
+        <v>0.1541230751486891</v>
       </c>
       <c r="W72">
-        <v>0.1919414705758261</v>
+        <v>0.1769414705758262</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.532632115460265</v>
+        <v>0.5708262042544041</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7368,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1825628597732253</v>
+        <v>0.1716372698339027</v>
       </c>
       <c r="C73">
-        <v>-4121.335596085575</v>
+        <v>-3938.037570072927</v>
       </c>
       <c r="D73">
-        <v>2121.530403914423</v>
+        <v>2304.828429927071</v>
       </c>
       <c r="E73">
         <v>1093.965999999999</v>
@@ -7273,37 +7401,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M73">
-        <v>1554.217566773716</v>
+        <v>1450.224576773717</v>
       </c>
       <c r="N73">
-        <v>-738.0509001070499</v>
+        <v>-634.0579101070499</v>
       </c>
       <c r="O73">
-        <v>-199.2737430289035</v>
+        <v>-171.1956357289035</v>
       </c>
       <c r="P73">
-        <v>-538.7771570781464</v>
+        <v>-462.8622743781464</v>
       </c>
       <c r="Q73">
-        <v>-19.87715707814641</v>
+        <v>56.03772562185355</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1584897217633857</v>
+        <v>0.1575394116277905</v>
       </c>
       <c r="T73">
-        <v>2.063106526148037</v>
+        <v>2.046546565223484</v>
       </c>
       <c r="U73">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V73">
-        <v>0.1417851687633663</v>
+        <v>0.1519523276113837</v>
       </c>
       <c r="W73">
-        <v>0.1923955499462584</v>
+        <v>0.1773955499462584</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5251302546791345</v>
+        <v>0.5627863985606802</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7450,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1843466708319905</v>
+        <v>0.1732710808926679</v>
       </c>
       <c r="C74">
-        <v>-4246.29664720361</v>
+        <v>-4065.224813082721</v>
       </c>
       <c r="D74">
-        <v>2094.21535279639</v>
+        <v>2275.287186917278</v>
       </c>
       <c r="E74">
         <v>1191.611999999999</v>
@@ -7355,37 +7483,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M74">
-        <v>1576.107955038135</v>
+        <v>1470.650275038135</v>
       </c>
       <c r="N74">
-        <v>-759.9412883714687</v>
+        <v>-654.4836083714684</v>
       </c>
       <c r="O74">
-        <v>-205.1841478602965</v>
+        <v>-176.7105742602965</v>
       </c>
       <c r="P74">
-        <v>-554.7571405111721</v>
+        <v>-477.773034111172</v>
       </c>
       <c r="Q74">
-        <v>-35.85714051117213</v>
+        <v>41.12696588882801</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1625143546835066</v>
+        <v>0.1615301049002116</v>
       </c>
       <c r="T74">
-        <v>2.136788902081895</v>
+        <v>2.119637513981465</v>
       </c>
       <c r="U74">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V74">
-        <v>0.1398159303083196</v>
+        <v>0.1498418786167811</v>
       </c>
       <c r="W74">
-        <v>0.1928370160008454</v>
+        <v>0.1778370160008454</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.517836778919702</v>
+        <v>0.554969920802893</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7532,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1861304818907557</v>
+        <v>0.1749048919514331</v>
       </c>
       <c r="C75">
-        <v>-4370.563267723263</v>
+        <v>-4191.664372425543</v>
       </c>
       <c r="D75">
-        <v>2067.594732276735</v>
+        <v>2246.493627574456</v>
       </c>
       <c r="E75">
         <v>1289.257999999999</v>
@@ -7437,37 +7565,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M75">
-        <v>1597.998343302554</v>
+        <v>1491.075973302554</v>
       </c>
       <c r="N75">
-        <v>-781.831676635887</v>
+        <v>-674.909306635887</v>
       </c>
       <c r="O75">
-        <v>-211.0945526916895</v>
+        <v>-182.2255127916895</v>
       </c>
       <c r="P75">
-        <v>-570.7371239441975</v>
+        <v>-492.6837938441975</v>
       </c>
       <c r="Q75">
-        <v>-51.83712394419751</v>
+        <v>26.21620615580252</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1668371085606735</v>
+        <v>0.1658164050817009</v>
       </c>
       <c r="T75">
-        <v>2.215929231788632</v>
+        <v>2.19814260709189</v>
       </c>
       <c r="U75">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V75">
-        <v>0.1379006435917673</v>
+        <v>0.1477892501425787</v>
       </c>
       <c r="W75">
-        <v>0.1932663870950327</v>
+        <v>0.1782663870950327</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5107431244139529</v>
+        <v>0.5473675931206616</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7614,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1879142929495209</v>
+        <v>0.1765387030101983</v>
       </c>
       <c r="C76">
-        <v>-4494.161607012528</v>
+        <v>-4317.384278986254</v>
       </c>
       <c r="D76">
-        <v>2041.642392987471</v>
+        <v>2218.419721013746</v>
       </c>
       <c r="E76">
         <v>1386.904</v>
@@ -7519,37 +7647,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M76">
-        <v>1619.888731566972</v>
+        <v>1511.501671566972</v>
       </c>
       <c r="N76">
-        <v>-803.7220649003058</v>
+        <v>-695.3350049003058</v>
       </c>
       <c r="O76">
-        <v>-217.0049575230826</v>
+        <v>-187.7404513230826</v>
       </c>
       <c r="P76">
-        <v>-586.7171073772232</v>
+        <v>-507.5945535772232</v>
       </c>
       <c r="Q76">
-        <v>-67.81710737722324</v>
+        <v>11.30544642277675</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1714923819668533</v>
+        <v>0.1704324206617663</v>
       </c>
       <c r="T76">
-        <v>2.301157279165118</v>
+        <v>2.282686553518501</v>
       </c>
       <c r="U76">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V76">
-        <v>0.1360371213810677</v>
+        <v>0.1457920981136248</v>
       </c>
       <c r="W76">
-        <v>0.1936841535650528</v>
+        <v>0.1786841535650528</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5038411903002507</v>
+        <v>0.5399707337541662</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7696,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2126298508255763</v>
+        <v>0.1781725140689635</v>
       </c>
       <c r="C77">
-        <v>-4894.273445568287</v>
+        <v>-4442.411179762125</v>
       </c>
       <c r="D77">
-        <v>1739.176554431712</v>
+        <v>2191.038820237874</v>
       </c>
       <c r="E77">
         <v>1484.549999999999</v>
@@ -7601,45 +7729,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M77">
-        <v>1861.482619831391</v>
+        <v>1531.927369831391</v>
       </c>
       <c r="N77">
-        <v>-1045.315953164724</v>
+        <v>-715.7607031647243</v>
       </c>
       <c r="O77">
-        <v>-282.2353073544755</v>
+        <v>-193.2553898544756</v>
       </c>
       <c r="P77">
-        <v>-763.0806458102484</v>
+        <v>-522.5053133102488</v>
       </c>
       <c r="Q77">
-        <v>-244.1806458102484</v>
+        <v>-3.605313310248789</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1782470645146883</v>
+        <v>0.175417717488237</v>
       </c>
       <c r="T77">
-        <v>2.424820994262022</v>
+        <v>2.373994015659241</v>
       </c>
       <c r="U77">
-        <v>0.2541811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V77">
-        <v>0.1183814437225099</v>
+        <v>0.1438482034721099</v>
       </c>
       <c r="W77">
-        <v>0.2240907795958723</v>
+        <v>0.1790907795958723</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.4384497915648514</v>
+        <v>0.5327711239707772</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7778,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2147136618843415</v>
+        <v>0.1798063251277287</v>
       </c>
       <c r="C78">
-        <v>-5013.374876093209</v>
+        <v>-4566.770422224945</v>
       </c>
       <c r="D78">
-        <v>1717.721123906789</v>
+        <v>2164.325577775054</v>
       </c>
       <c r="E78">
         <v>1582.195999999999</v>
@@ -7683,45 +7811,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M78">
-        <v>1886.302388095809</v>
+        <v>1552.353068095809</v>
       </c>
       <c r="N78">
-        <v>-1070.135721429142</v>
+        <v>-736.1864014291426</v>
       </c>
       <c r="O78">
-        <v>-288.9366447858685</v>
+        <v>-198.7703283858685</v>
       </c>
       <c r="P78">
-        <v>-781.199076643274</v>
+        <v>-537.4160730432741</v>
       </c>
       <c r="Q78">
-        <v>-262.299076643274</v>
+        <v>-18.5160730432741</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1837656922028003</v>
+        <v>0.1808184557169135</v>
       </c>
       <c r="T78">
-        <v>2.525855202356273</v>
+        <v>2.472910432978376</v>
       </c>
       <c r="U78">
-        <v>0.2541811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V78">
-        <v>0.1168237931472137</v>
+        <v>0.14195546395274</v>
       </c>
       <c r="W78">
-        <v>0.2244867049416703</v>
+        <v>0.1794867049416703</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.4326807153600507</v>
+        <v>0.5257609776027408</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7860,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2167974729431067</v>
+        <v>0.1814401361864939</v>
       </c>
       <c r="C79">
-        <v>-5131.953385868152</v>
+        <v>-4690.486132586157</v>
       </c>
       <c r="D79">
-        <v>1696.788614131848</v>
+        <v>2138.255867413842</v>
       </c>
       <c r="E79">
         <v>1679.842</v>
@@ -7765,45 +7893,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M79">
-        <v>1911.122156360228</v>
+        <v>1572.778766360228</v>
       </c>
       <c r="N79">
-        <v>-1094.955489693561</v>
+        <v>-756.6120996935614</v>
       </c>
       <c r="O79">
-        <v>-295.6379822172615</v>
+        <v>-204.2852669172616</v>
       </c>
       <c r="P79">
-        <v>-799.3175074762996</v>
+        <v>-552.3268327762999</v>
       </c>
       <c r="Q79">
-        <v>-280.4175074762996</v>
+        <v>-33.42683277629988</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1897642005594438</v>
+        <v>0.1866888233567794</v>
       </c>
       <c r="T79">
-        <v>2.635674993763067</v>
+        <v>2.58042827789048</v>
       </c>
       <c r="U79">
-        <v>0.2541811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V79">
-        <v>0.1153066010284187</v>
+        <v>0.1401118864988083</v>
       </c>
       <c r="W79">
-        <v>0.2248723465122527</v>
+        <v>0.1798723465122527</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.4270614852904396</v>
+        <v>0.5189329129585492</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7942,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2188812840018718</v>
+        <v>0.183073947245259</v>
       </c>
       <c r="C80">
-        <v>-5250.027861996606</v>
+        <v>-4813.581288473025</v>
       </c>
       <c r="D80">
-        <v>1676.360138003393</v>
+        <v>2112.806711526974</v>
       </c>
       <c r="E80">
         <v>1777.487999999999</v>
@@ -7847,45 +7975,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M80">
-        <v>1935.941924624646</v>
+        <v>1593.204464624647</v>
       </c>
       <c r="N80">
-        <v>-1119.77525795798</v>
+        <v>-777.0377979579799</v>
       </c>
       <c r="O80">
-        <v>-302.3393196486545</v>
+        <v>-209.8002054486546</v>
       </c>
       <c r="P80">
-        <v>-817.4359383093251</v>
+        <v>-567.2375925093254</v>
       </c>
       <c r="Q80">
-        <v>-298.5359383093252</v>
+        <v>-48.33759250932542</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1963080278576004</v>
+        <v>0.1930928607820875</v>
       </c>
       <c r="T80">
-        <v>2.75547840257048</v>
+        <v>2.697720472340047</v>
       </c>
       <c r="U80">
-        <v>0.2541811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V80">
-        <v>0.1138283112716441</v>
+        <v>0.1383155802616441</v>
       </c>
       <c r="W80">
-        <v>0.2252480998374356</v>
+        <v>0.1802480998374356</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.4215863380431263</v>
+        <v>0.512279926894978</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +8024,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2209650950606371</v>
+        <v>0.1847077583040242</v>
       </c>
       <c r="C81">
-        <v>-5367.616292837838</v>
+        <v>-4936.077786475958</v>
       </c>
       <c r="D81">
-        <v>1656.417707162161</v>
+        <v>2087.956213524041</v>
       </c>
       <c r="E81">
         <v>1875.134</v>
@@ -7929,45 +8057,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M81">
-        <v>1960.761692889065</v>
+        <v>1613.630162889065</v>
       </c>
       <c r="N81">
-        <v>-1144.595026222398</v>
+        <v>-797.4634962223985</v>
       </c>
       <c r="O81">
-        <v>-309.0406570800475</v>
+        <v>-215.3151439800476</v>
       </c>
       <c r="P81">
-        <v>-835.5543691423507</v>
+        <v>-582.1483522423509</v>
       </c>
       <c r="Q81">
-        <v>-316.6543691423507</v>
+        <v>-63.24835224235096</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2034750768032004</v>
+        <v>0.2001068065336155</v>
       </c>
       <c r="T81">
-        <v>2.886691659835741</v>
+        <v>2.826183351975288</v>
       </c>
       <c r="U81">
-        <v>0.2541811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V81">
-        <v>0.112387446572003</v>
+        <v>0.1365647501317499</v>
       </c>
       <c r="W81">
-        <v>0.2256143404202088</v>
+        <v>0.1806143404202088</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.4162498021185298</v>
+        <v>0.5057953708583327</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +8106,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2230489061194023</v>
+        <v>0.2149032711314487</v>
       </c>
       <c r="C82">
-        <v>-5484.735820836899</v>
+        <v>-5406.554591029453</v>
       </c>
       <c r="D82">
-        <v>1636.944179163101</v>
+        <v>1715.125408970546</v>
       </c>
       <c r="E82">
         <v>1972.78</v>
@@ -8011,37 +8139,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M82">
-        <v>1985.581461153484</v>
+        <v>1907.464661153484</v>
       </c>
       <c r="N82">
-        <v>-1169.414794486817</v>
+        <v>-1091.297994486817</v>
       </c>
       <c r="O82">
-        <v>-315.7419945114406</v>
+        <v>-294.6504585114406</v>
       </c>
       <c r="P82">
-        <v>-853.6727999753763</v>
+        <v>-796.6475359753765</v>
       </c>
       <c r="Q82">
-        <v>-334.7727999753763</v>
+        <v>-277.7475359753765</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2113588306433604</v>
+        <v>0.2106306557035925</v>
       </c>
       <c r="T82">
-        <v>3.031026242827528</v>
+        <v>3.018931345346589</v>
       </c>
       <c r="U82">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V82">
-        <v>0.110982603489853</v>
+        <v>0.1155276973082902</v>
       </c>
       <c r="W82">
-        <v>0.2259714249884127</v>
+        <v>0.2159714249884127</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4110466795920481</v>
+        <v>0.4278803604010748</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8188,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2251327171781674</v>
+        <v>0.2168870821902139</v>
       </c>
       <c r="C83">
-        <v>-5601.402791671421</v>
+        <v>-5524.088034955243</v>
       </c>
       <c r="D83">
-        <v>1617.923208328578</v>
+        <v>1695.237965044756</v>
       </c>
       <c r="E83">
         <v>2070.425999999999</v>
@@ -8093,37 +8221,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M83">
-        <v>2010.401229417902</v>
+        <v>1931.307969417902</v>
       </c>
       <c r="N83">
-        <v>-1194.234562751235</v>
+        <v>-1115.141302751235</v>
       </c>
       <c r="O83">
-        <v>-322.4433319428336</v>
+        <v>-301.0881517428336</v>
       </c>
       <c r="P83">
-        <v>-871.7912308084019</v>
+        <v>-814.0531510084018</v>
       </c>
       <c r="Q83">
-        <v>-352.8912308084019</v>
+        <v>-295.1531510084018</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2200724533088005</v>
+        <v>0.2193059533722026</v>
       </c>
       <c r="T83">
-        <v>3.190553939818451</v>
+        <v>3.177822468785883</v>
       </c>
       <c r="U83">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V83">
-        <v>0.1096124478912128</v>
+        <v>0.1141014294402866</v>
       </c>
       <c r="W83">
-        <v>0.2263196926536979</v>
+        <v>0.216319692653698</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4059720292267142</v>
+        <v>0.4225978868158764</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8270,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2272165282369326</v>
+        <v>0.2188708932489791</v>
       </c>
       <c r="C84">
-        <v>-5717.632800011304</v>
+        <v>-5641.165562459157</v>
       </c>
       <c r="D84">
-        <v>1599.339199988696</v>
+        <v>1675.806437540843</v>
       </c>
       <c r="E84">
         <v>2168.072</v>
@@ -8175,37 +8303,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M84">
-        <v>2035.220997682321</v>
+        <v>1955.151277682321</v>
       </c>
       <c r="N84">
-        <v>-1219.054331015654</v>
+        <v>-1138.984611015654</v>
       </c>
       <c r="O84">
-        <v>-329.1446693742266</v>
+        <v>-307.5258449742266</v>
       </c>
       <c r="P84">
-        <v>-889.9096616414274</v>
+        <v>-831.4587660414275</v>
       </c>
       <c r="Q84">
-        <v>-371.0096616414274</v>
+        <v>-312.5587660414275</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2297542562704005</v>
+        <v>0.2289451730039917</v>
       </c>
       <c r="T84">
-        <v>3.367806936475032</v>
+        <v>3.354368161496211</v>
       </c>
       <c r="U84">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V84">
-        <v>0.1082757107218078</v>
+        <v>0.1127099485934538</v>
       </c>
       <c r="W84">
-        <v>0.2266594659856836</v>
+        <v>0.2166594659856836</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4010211508215104</v>
+        <v>0.4174442540498291</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8352,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2293003392956978</v>
+        <v>0.2208547043077442</v>
       </c>
       <c r="C85">
-        <v>-5833.440732160558</v>
+        <v>-5757.802673588047</v>
       </c>
       <c r="D85">
-        <v>1581.177267839442</v>
+        <v>1656.815326411953</v>
       </c>
       <c r="E85">
         <v>2265.718</v>
@@ -8257,37 +8385,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M85">
-        <v>2060.040765946739</v>
+        <v>1978.994585946739</v>
       </c>
       <c r="N85">
-        <v>-1243.874099280073</v>
+        <v>-1162.827919280073</v>
       </c>
       <c r="O85">
-        <v>-335.8460068056197</v>
+        <v>-313.9635382056197</v>
       </c>
       <c r="P85">
-        <v>-908.0280924744529</v>
+        <v>-848.8643810744531</v>
       </c>
       <c r="Q85">
-        <v>-389.128092474453</v>
+        <v>-329.9643810744532</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2405750948745417</v>
+        <v>0.2397184184748147</v>
       </c>
       <c r="T85">
-        <v>3.565913226855916</v>
+        <v>3.55168393570187</v>
       </c>
       <c r="U85">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V85">
-        <v>0.1069711840866053</v>
+        <v>0.1113519974055809</v>
       </c>
       <c r="W85">
-        <v>0.2269910520084647</v>
+        <v>0.2169910520084647</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3961895706911306</v>
+        <v>0.4124148052058552</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8434,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.231384150354463</v>
+        <v>0.2228385153665094</v>
       </c>
       <c r="C86">
-        <v>-5948.840805826322</v>
+        <v>-5874.014173643575</v>
       </c>
       <c r="D86">
-        <v>1563.423194173677</v>
+        <v>1638.249826356424</v>
       </c>
       <c r="E86">
         <v>2363.364</v>
@@ -8339,37 +8467,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M86">
-        <v>2084.860534211158</v>
+        <v>2002.837894211158</v>
       </c>
       <c r="N86">
-        <v>-1268.693867544491</v>
+        <v>-1186.671227544491</v>
       </c>
       <c r="O86">
-        <v>-342.5473442370127</v>
+        <v>-320.4012314370126</v>
       </c>
       <c r="P86">
-        <v>-926.1465233074786</v>
+        <v>-866.2699961074785</v>
       </c>
       <c r="Q86">
-        <v>-407.2465233074786</v>
+        <v>-347.3699961074785</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2527485383042005</v>
+        <v>0.2518383196294905</v>
       </c>
       <c r="T86">
-        <v>3.788782803534409</v>
+        <v>3.773664181683235</v>
       </c>
       <c r="U86">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V86">
-        <v>0.1056977176093838</v>
+        <v>0.1100263783888478</v>
       </c>
       <c r="W86">
-        <v>0.2273147431259415</v>
+        <v>0.2173147431259416</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3914730281829029</v>
+        <v>0.4075051051438808</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8516,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2334679614132281</v>
+        <v>0.2248223264252746</v>
       </c>
       <c r="C87">
-        <v>-6063.846607238433</v>
+        <v>-5989.814211675823</v>
       </c>
       <c r="D87">
-        <v>1546.063392761566</v>
+        <v>1620.095788324175</v>
       </c>
       <c r="E87">
         <v>2461.009999999998</v>
@@ -8421,37 +8549,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M87">
-        <v>2109.680302475576</v>
+        <v>2026.681202475576</v>
       </c>
       <c r="N87">
-        <v>-1293.513635808909</v>
+        <v>-1210.514535808909</v>
       </c>
       <c r="O87">
-        <v>-349.2486816684055</v>
+        <v>-326.8389246684056</v>
       </c>
       <c r="P87">
-        <v>-944.2649541405038</v>
+        <v>-883.6756111405039</v>
       </c>
       <c r="Q87">
-        <v>-425.3649541405039</v>
+        <v>-364.7756111405039</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2665451075244805</v>
+        <v>0.2655742076047899</v>
       </c>
       <c r="T87">
-        <v>4.041368323770036</v>
+        <v>4.02524179379545</v>
       </c>
       <c r="U87">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V87">
-        <v>0.1044542150492734</v>
+        <v>0.1087319504078026</v>
       </c>
       <c r="W87">
-        <v>0.2276308179818307</v>
+        <v>0.2176308179818307</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3868674631454571</v>
+        <v>0.4027109274363058</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8598,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2355517724719933</v>
+        <v>0.2268061374840398</v>
       </c>
       <c r="C88">
-        <v>-6178.471125823095</v>
+        <v>-6105.216316445584</v>
       </c>
       <c r="D88">
-        <v>1529.084874176904</v>
+        <v>1602.339683554414</v>
       </c>
       <c r="E88">
         <v>2558.655999999999</v>
@@ -8503,37 +8631,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M88">
-        <v>2134.500070739994</v>
+        <v>2050.524510739995</v>
       </c>
       <c r="N88">
-        <v>-1318.333404073328</v>
+        <v>-1234.357844073328</v>
       </c>
       <c r="O88">
-        <v>-355.9500190997986</v>
+        <v>-333.2766178997986</v>
       </c>
       <c r="P88">
-        <v>-962.3833849735295</v>
+        <v>-901.0812261735296</v>
       </c>
       <c r="Q88">
-        <v>-443.4833849735295</v>
+        <v>-382.1812261735296</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2823126152048005</v>
+        <v>0.2812723652908464</v>
       </c>
       <c r="T88">
-        <v>4.33003748975361</v>
+        <v>4.31275906478084</v>
       </c>
       <c r="U88">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V88">
-        <v>0.1032396311533516</v>
+        <v>0.1074676254030607</v>
       </c>
       <c r="W88">
-        <v>0.2279395422596759</v>
+        <v>0.2179395422596759</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3823690042716726</v>
+        <v>0.3980282422335579</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8680,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2376355835307585</v>
+        <v>0.228789948542805</v>
       </c>
       <c r="C89">
-        <v>-6292.726786616759</v>
+        <v>-6220.233430047434</v>
       </c>
       <c r="D89">
-        <v>1512.47521338324</v>
+        <v>1584.968569952565</v>
       </c>
       <c r="E89">
         <v>2656.302</v>
@@ -8585,37 +8713,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M89">
-        <v>2159.319839004413</v>
+        <v>2074.367819004413</v>
       </c>
       <c r="N89">
-        <v>-1343.153172337747</v>
+        <v>-1258.201152337747</v>
       </c>
       <c r="O89">
-        <v>-362.6513565311916</v>
+        <v>-339.7143111311917</v>
       </c>
       <c r="P89">
-        <v>-980.501815806555</v>
+        <v>-918.4868412065553</v>
       </c>
       <c r="Q89">
-        <v>-461.601815806555</v>
+        <v>-399.5868412065553</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3005058932974775</v>
+        <v>0.299385624159373</v>
       </c>
       <c r="T89">
-        <v>4.663117296657734</v>
+        <v>4.644509762071674</v>
       </c>
       <c r="U89">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V89">
-        <v>0.1020529687263016</v>
+        <v>0.1062323653409565</v>
       </c>
       <c r="W89">
-        <v>0.2282411694276856</v>
+        <v>0.2182411694276856</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3779739582455615</v>
+        <v>0.3934532049665055</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8762,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2397193945895237</v>
+        <v>0.2307737596015701</v>
       </c>
       <c r="C90">
-        <v>-6406.625480590084</v>
+        <v>-6334.877939369187</v>
       </c>
       <c r="D90">
-        <v>1496.222519409914</v>
+        <v>1567.970060630812</v>
       </c>
       <c r="E90">
         <v>2753.947999999999</v>
@@ -8667,37 +8795,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M90">
-        <v>2184.139607268832</v>
+        <v>2098.211127268832</v>
       </c>
       <c r="N90">
-        <v>-1367.972940602165</v>
+        <v>-1282.044460602165</v>
       </c>
       <c r="O90">
-        <v>-369.3526939625846</v>
+        <v>-346.1520043625846</v>
       </c>
       <c r="P90">
-        <v>-998.6202466395805</v>
+        <v>-935.8924562395805</v>
       </c>
       <c r="Q90">
-        <v>-479.7202466395805</v>
+        <v>-416.9924562395805</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3217313844056007</v>
+        <v>0.3205177595059874</v>
       </c>
       <c r="T90">
-        <v>5.051710404712546</v>
+        <v>5.031552242244314</v>
       </c>
       <c r="U90">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V90">
-        <v>0.1008932758998664</v>
+        <v>0.1050251793711729</v>
       </c>
       <c r="W90">
-        <v>0.228535941432786</v>
+        <v>0.218535941432786</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3736787996291346</v>
+        <v>0.3889821458191589</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8844,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2418032056482889</v>
+        <v>0.2327575706603353</v>
       </c>
       <c r="C91">
-        <v>-6520.178593037595</v>
+        <v>-6449.161705548463</v>
       </c>
       <c r="D91">
-        <v>1480.315406962404</v>
+        <v>1551.332294451536</v>
       </c>
       <c r="E91">
         <v>2851.593999999999</v>
@@ -8749,37 +8877,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M91">
-        <v>2208.95937553325</v>
+        <v>2122.05443553325</v>
       </c>
       <c r="N91">
-        <v>-1392.792708866584</v>
+        <v>-1305.887768866584</v>
       </c>
       <c r="O91">
-        <v>-376.0540313939777</v>
+        <v>-352.5896975939777</v>
       </c>
       <c r="P91">
-        <v>-1016.738677472606</v>
+        <v>-953.2980712726062</v>
       </c>
       <c r="Q91">
-        <v>-497.8386774726062</v>
+        <v>-434.3980712726062</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3468160557152007</v>
+        <v>0.3454921012792591</v>
       </c>
       <c r="T91">
-        <v>5.510956805140959</v>
+        <v>5.488966082448343</v>
       </c>
       <c r="U91">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V91">
-        <v>0.09975964358638473</v>
+        <v>0.1038451211759912</v>
       </c>
       <c r="W91">
-        <v>0.2288240893478841</v>
+        <v>0.2188240893478841</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3694801614310544</v>
+        <v>0.3846115599110784</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8926,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2438870167070541</v>
+        <v>0.2347413817191006</v>
       </c>
       <c r="C92">
-        <v>-6633.397030175415</v>
+        <v>-6563.096091573543</v>
       </c>
       <c r="D92">
-        <v>1464.742969824584</v>
+        <v>1535.043908426456</v>
       </c>
       <c r="E92">
         <v>2949.24</v>
@@ -8831,37 +8959,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M92">
-        <v>2233.779143797669</v>
+        <v>2145.897743797669</v>
       </c>
       <c r="N92">
-        <v>-1417.612477131002</v>
+        <v>-1329.731077131003</v>
       </c>
       <c r="O92">
-        <v>-382.7553688253707</v>
+        <v>-359.0273908253707</v>
       </c>
       <c r="P92">
-        <v>-1034.857108305632</v>
+        <v>-970.7036863056319</v>
       </c>
       <c r="Q92">
-        <v>-515.9571083056318</v>
+        <v>-451.8036863056319</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3769176612867208</v>
+        <v>0.375461311407185</v>
       </c>
       <c r="T92">
-        <v>6.062052485655056</v>
+        <v>6.037862690693178</v>
       </c>
       <c r="U92">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V92">
-        <v>0.09865120310209155</v>
+        <v>0.102691286496258</v>
       </c>
       <c r="W92">
-        <v>0.22910583397598</v>
+        <v>0.21910583397598</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3653748263040427</v>
+        <v>0.3803380981342886</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +9008,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2459708277658193</v>
+        <v>0.2367251927778657</v>
       </c>
       <c r="C93">
-        <v>-6746.291244077692</v>
+        <v>-6676.691988163509</v>
       </c>
       <c r="D93">
-        <v>1449.494755922306</v>
+        <v>1519.094011836489</v>
       </c>
       <c r="E93">
         <v>3046.885999999999</v>
@@ -8913,37 +9041,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M93">
-        <v>2258.598912062087</v>
+        <v>2169.741052062087</v>
       </c>
       <c r="N93">
-        <v>-1442.432245395421</v>
+        <v>-1353.574385395421</v>
       </c>
       <c r="O93">
-        <v>-389.4567062567635</v>
+        <v>-365.4650840567637</v>
       </c>
       <c r="P93">
-        <v>-1052.975539138657</v>
+        <v>-988.1093013386572</v>
       </c>
       <c r="Q93">
-        <v>-534.0755391386571</v>
+        <v>-469.2093013386573</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4137085125408009</v>
+        <v>0.4120903460079834</v>
       </c>
       <c r="T93">
-        <v>6.735613872950062</v>
+        <v>6.708736322992421</v>
       </c>
       <c r="U93">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V93">
-        <v>0.09756712394712352</v>
+        <v>0.1015628108204749</v>
       </c>
       <c r="W93">
-        <v>0.2293813864144475</v>
+        <v>0.2193813864144475</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3613597183226797</v>
+        <v>0.3761585585943514</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +9090,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2480546388245845</v>
+        <v>0.2387090038366309</v>
       </c>
       <c r="C94">
-        <v>-6858.871256071518</v>
+        <v>-6789.95983805154</v>
       </c>
       <c r="D94">
-        <v>1434.560743928482</v>
+        <v>1503.472161948459</v>
       </c>
       <c r="E94">
         <v>3144.531999999999</v>
@@ -8995,37 +9123,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M94">
-        <v>2283.418680326506</v>
+        <v>2193.584360326506</v>
       </c>
       <c r="N94">
-        <v>-1467.25201365984</v>
+        <v>-1377.41769365984</v>
       </c>
       <c r="O94">
-        <v>-396.1580436881567</v>
+        <v>-371.9027772881568</v>
       </c>
       <c r="P94">
-        <v>-1071.093969971683</v>
+        <v>-1005.514916371683</v>
       </c>
       <c r="Q94">
-        <v>-552.1939699716828</v>
+        <v>-486.6149163716829</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4596970766084012</v>
+        <v>0.4578766392589814</v>
       </c>
       <c r="T94">
-        <v>7.577565607068823</v>
+        <v>7.547328363366476</v>
       </c>
       <c r="U94">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V94">
-        <v>0.09650661173030695</v>
+        <v>0.1004588672246002</v>
       </c>
       <c r="W94">
-        <v>0.2296509485825135</v>
+        <v>0.2196509485825135</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.357431895297433</v>
+        <v>0.3720698786096303</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9172,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2501384498833497</v>
+        <v>0.2406928148953961</v>
       </c>
       <c r="C95">
-        <v>-6971.146678700372</v>
+        <v>-6902.909658785105</v>
       </c>
       <c r="D95">
-        <v>1419.931321299627</v>
+        <v>1488.168341214894</v>
       </c>
       <c r="E95">
         <v>3242.178</v>
@@ -9077,37 +9205,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M95">
-        <v>2308.238448590925</v>
+        <v>2217.427668590925</v>
       </c>
       <c r="N95">
-        <v>-1492.071781924258</v>
+        <v>-1401.261001924258</v>
       </c>
       <c r="O95">
-        <v>-402.8593811195497</v>
+        <v>-378.3404705195498</v>
       </c>
       <c r="P95">
-        <v>-1089.212400804709</v>
+        <v>-1022.920531404709</v>
       </c>
       <c r="Q95">
-        <v>-570.3124008047085</v>
+        <v>-504.0205314047085</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5188252304096014</v>
+        <v>0.5167447305816931</v>
       </c>
       <c r="T95">
-        <v>8.660074979507227</v>
+        <v>8.625518129561687</v>
       </c>
       <c r="U95">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V95">
-        <v>0.09546890622783052</v>
+        <v>0.09937866435121738</v>
       </c>
       <c r="W95">
-        <v>0.2299147137147071</v>
+        <v>0.2199147137147071</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3535885415845574</v>
+        <v>0.3680691272267309</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9254,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2522222609421149</v>
+        <v>0.2426766259541613</v>
       </c>
       <c r="C96">
-        <v>-7083.126736357268</v>
+        <v>-7015.551064147718</v>
       </c>
       <c r="D96">
-        <v>1405.597263642731</v>
+        <v>1473.172935852281</v>
       </c>
       <c r="E96">
         <v>3339.823999999999</v>
@@ -9159,37 +9287,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M96">
-        <v>2333.058216855343</v>
+        <v>2241.270976855343</v>
       </c>
       <c r="N96">
-        <v>-1516.891550188676</v>
+        <v>-1425.104310188677</v>
       </c>
       <c r="O96">
-        <v>-409.5607185509426</v>
+        <v>-384.7781637509427</v>
       </c>
       <c r="P96">
-        <v>-1107.330831637734</v>
+        <v>-1040.326146437734</v>
       </c>
       <c r="Q96">
-        <v>-588.4308316377338</v>
+        <v>-521.426146437734</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.5976627688112016</v>
+        <v>0.5952355190119754</v>
       </c>
       <c r="T96">
-        <v>10.1034208094251</v>
+        <v>10.06310448448864</v>
       </c>
       <c r="U96">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V96">
-        <v>0.09445327956583234</v>
+        <v>0.0983214445176938</v>
       </c>
       <c r="W96">
-        <v>0.2301728668228114</v>
+        <v>0.2201728668228115</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3498269613549345</v>
+        <v>0.3641534982136807</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9336,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2543060720008801</v>
+        <v>0.2446604370129265</v>
       </c>
       <c r="C97">
-        <v>-7194.820284680641</v>
+        <v>-7127.893284298473</v>
       </c>
       <c r="D97">
-        <v>1391.549715319358</v>
+        <v>1458.476715701526</v>
       </c>
       <c r="E97">
         <v>3437.469999999999</v>
@@ -9241,37 +9369,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M97">
-        <v>2357.877985119761</v>
+        <v>2265.114285119762</v>
       </c>
       <c r="N97">
-        <v>-1541.711318453095</v>
+        <v>-1448.947618453095</v>
       </c>
       <c r="O97">
-        <v>-416.2620559823357</v>
+        <v>-391.2158569823358</v>
       </c>
       <c r="P97">
-        <v>-1125.449262470759</v>
+        <v>-1057.73176147076</v>
       </c>
       <c r="Q97">
-        <v>-606.5492624707593</v>
+        <v>-538.8317614707597</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.7080353225734424</v>
+        <v>0.7051226228143708</v>
       </c>
       <c r="T97">
-        <v>12.12410497131013</v>
+        <v>12.07572538138637</v>
       </c>
       <c r="U97">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V97">
-        <v>0.09345903451777095</v>
+        <v>0.09728648194382333</v>
       </c>
       <c r="W97">
-        <v>0.2304255851286399</v>
+        <v>0.22042558512864</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3461445722880405</v>
+        <v>0.3603203034956419</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9418,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2563898830596452</v>
+        <v>0.2466442480716917</v>
       </c>
       <c r="C98">
-        <v>-7306.235828798684</v>
+        <v>-7239.945184718023</v>
       </c>
       <c r="D98">
-        <v>1377.780171201313</v>
+        <v>1444.070815281975</v>
       </c>
       <c r="E98">
         <v>3535.115999999998</v>
@@ -9323,37 +9451,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M98">
-        <v>2382.69775338418</v>
+        <v>2288.95759338418</v>
       </c>
       <c r="N98">
-        <v>-1566.531086717514</v>
+        <v>-1472.790926717514</v>
       </c>
       <c r="O98">
-        <v>-422.9633934137287</v>
+        <v>-397.6535502137287</v>
       </c>
       <c r="P98">
-        <v>-1143.567693303785</v>
+        <v>-1075.137376503785</v>
       </c>
       <c r="Q98">
-        <v>-624.6676933037849</v>
+        <v>-556.237376503785</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.8735941532168011</v>
+        <v>0.8699532785179617</v>
       </c>
       <c r="T98">
-        <v>15.15513121413762</v>
+        <v>15.09465672673293</v>
       </c>
       <c r="U98">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V98">
-        <v>0.09248550290821082</v>
+        <v>0.09627308109024184</v>
       </c>
       <c r="W98">
-        <v>0.2306730384697637</v>
+        <v>0.2206730384697637</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.34253889966004</v>
+        <v>0.3565669670008956</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9500,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2584736941184104</v>
+        <v>0.2486280591304568</v>
       </c>
       <c r="C99">
-        <v>-7417.381540501151</v>
+        <v>-7351.715284042732</v>
       </c>
       <c r="D99">
-        <v>1364.280459498847</v>
+        <v>1429.946715957267</v>
       </c>
       <c r="E99">
         <v>3632.761999999999</v>
@@ -9405,37 +9533,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M99">
-        <v>2407.517521648599</v>
+        <v>2312.800901648599</v>
       </c>
       <c r="N99">
-        <v>-1591.350854981932</v>
+        <v>-1496.634234981932</v>
       </c>
       <c r="O99">
-        <v>-429.6647308451217</v>
+        <v>-404.0912434451218</v>
       </c>
       <c r="P99">
-        <v>-1161.68612413681</v>
+        <v>-1092.542991536811</v>
       </c>
       <c r="Q99">
-        <v>-642.7861241368104</v>
+        <v>-573.6429915368107</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.149525537622402</v>
+        <v>1.144671038023949</v>
       </c>
       <c r="T99">
-        <v>20.20684161885017</v>
+        <v>20.12620896897724</v>
       </c>
       <c r="U99">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V99">
-        <v>0.09153204411534267</v>
+        <v>0.09528057509962079</v>
       </c>
       <c r="W99">
-        <v>0.2309153896801426</v>
+        <v>0.2209153896801426</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3390075707975654</v>
+        <v>0.3528910188874843</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9582,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2605575051771756</v>
+        <v>0.250611870189222</v>
       </c>
       <c r="C100">
-        <v>-7528.265274411384</v>
+        <v>-7463.211770862369</v>
       </c>
       <c r="D100">
-        <v>1351.042725588615</v>
+        <v>1416.09622913763</v>
       </c>
       <c r="E100">
         <v>3730.407999999999</v>
@@ -9487,37 +9615,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M100">
-        <v>2432.337289913017</v>
+        <v>2336.644209913018</v>
       </c>
       <c r="N100">
-        <v>-1616.170623246351</v>
+        <v>-1520.477543246351</v>
       </c>
       <c r="O100">
-        <v>-436.3660682765147</v>
+        <v>-410.5289366765148</v>
       </c>
       <c r="P100">
-        <v>-1179.804554969836</v>
+        <v>-1109.948606569836</v>
       </c>
       <c r="Q100">
-        <v>-660.9045549698359</v>
+        <v>-591.0486065698364</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.701388306433602</v>
+        <v>1.694106557035923</v>
       </c>
       <c r="T100">
-        <v>30.31026242827525</v>
+        <v>30.18931345346585</v>
       </c>
       <c r="U100">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V100">
-        <v>0.09059804366518612</v>
+        <v>0.09430832433329812</v>
       </c>
       <c r="W100">
-        <v>0.2311527949474526</v>
+        <v>0.2211527949474526</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9653,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3355483098710597</v>
+        <v>0.3492900901233263</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9664,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2626413162359408</v>
+        <v>0.2525956812479871</v>
       </c>
       <c r="C101">
-        <v>-7638.894583225938</v>
+        <v>-7574.442519550954</v>
       </c>
       <c r="D101">
-        <v>1338.05941677406</v>
+        <v>1402.511480449044</v>
       </c>
       <c r="E101">
         <v>3828.053999999998</v>
@@ -9569,37 +9697,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M101">
-        <v>2457.157058177435</v>
+        <v>2360.487518177436</v>
       </c>
       <c r="N101">
-        <v>-1640.990391510769</v>
+        <v>-1544.320851510769</v>
       </c>
       <c r="O101">
-        <v>-443.0674057079076</v>
+        <v>-416.9666299079076</v>
       </c>
       <c r="P101">
-        <v>-1197.922985802861</v>
+        <v>-1127.354221602861</v>
       </c>
       <c r="Q101">
-        <v>-679.0229858028612</v>
+        <v>-608.4542216028614</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.356976612867205</v>
+        <v>3.342413114071846</v>
       </c>
       <c r="T101">
-        <v>60.6205248565505</v>
+        <v>60.37862690693171</v>
       </c>
       <c r="U101">
-        <v>0.2541811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V101">
-        <v>0.08968291191099233</v>
+        <v>0.09335571499659817</v>
       </c>
       <c r="W101">
-        <v>0.2313854041487563</v>
+        <v>0.2213854041487563</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9735,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3321589330036753</v>
+        <v>0.3457619073948079</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/chile/chile_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_paper_forest_products.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08212319963045955</v>
+        <v>0.08199549906435591</v>
       </c>
       <c r="C2">
-        <v>8674.795392704607</v>
+        <v>8605.320378551693</v>
       </c>
       <c r="D2">
-        <v>7984.795392704608</v>
+        <v>8012.966378551692</v>
       </c>
       <c r="E2">
-        <v>-5838.9</v>
+        <v>-5741.254</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>97.64599999999999</v>
       </c>
       <c r="G2">
         <v>690</v>
@@ -1579,28 +1579,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>5.729975264418547</v>
       </c>
       <c r="N2">
-        <v>816.1666666666666</v>
+        <v>810.4366914022481</v>
       </c>
       <c r="O2">
-        <v>220.365</v>
+        <v>218.817906678607</v>
       </c>
       <c r="P2">
-        <v>595.8016666666666</v>
+        <v>591.6187847236411</v>
       </c>
       <c r="Q2">
-        <v>1114.701666666667</v>
+        <v>1110.518784723641</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08212319963045955</v>
+        <v>0.0823910373651084</v>
       </c>
       <c r="T2">
-        <v>0.6652721574126821</v>
+        <v>0.6701776995835029</v>
       </c>
       <c r="U2">
         <v>0.05868110587651873</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>142.4380785262408</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08199549906435591</v>
+        <v>0.08186779849825225</v>
       </c>
       <c r="C3">
-        <v>8605.320378551693</v>
+        <v>8536.044847094714</v>
       </c>
       <c r="D3">
-        <v>8012.966378551692</v>
+        <v>8041.336847094713</v>
       </c>
       <c r="E3">
-        <v>-5741.254</v>
+        <v>-5643.607999999999</v>
       </c>
       <c r="F3">
-        <v>97.64599999999999</v>
+        <v>195.292</v>
       </c>
       <c r="G3">
         <v>690</v>
@@ -1661,28 +1661,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M3">
-        <v>5.729975264418547</v>
+        <v>11.45995052883709</v>
       </c>
       <c r="N3">
-        <v>810.4366914022481</v>
+        <v>804.7067161378295</v>
       </c>
       <c r="O3">
-        <v>218.817906678607</v>
+        <v>217.270813357214</v>
       </c>
       <c r="P3">
-        <v>591.6187847236411</v>
+        <v>587.4359027806155</v>
       </c>
       <c r="Q3">
-        <v>1110.518784723641</v>
+        <v>1106.335902780615</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0823910373651084</v>
+        <v>0.08266434117597457</v>
       </c>
       <c r="T3">
-        <v>0.6701776995835029</v>
+        <v>0.6751833548598507</v>
       </c>
       <c r="U3">
         <v>0.05868110587651873</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>142.4380785262408</v>
+        <v>71.21903926312042</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08186779849825225</v>
+        <v>0.08174009793214859</v>
       </c>
       <c r="C4">
-        <v>8536.044847094714</v>
+        <v>8466.970924709605</v>
       </c>
       <c r="D4">
-        <v>8041.336847094713</v>
+        <v>8069.908924709605</v>
       </c>
       <c r="E4">
-        <v>-5643.607999999999</v>
+        <v>-5545.962</v>
       </c>
       <c r="F4">
-        <v>195.292</v>
+        <v>292.9379999999999</v>
       </c>
       <c r="G4">
         <v>690</v>
@@ -1743,28 +1743,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M4">
-        <v>11.45995052883709</v>
+        <v>17.18992579325564</v>
       </c>
       <c r="N4">
-        <v>804.7067161378295</v>
+        <v>798.976740873411</v>
       </c>
       <c r="O4">
-        <v>217.270813357214</v>
+        <v>215.723720035821</v>
       </c>
       <c r="P4">
-        <v>587.4359027806155</v>
+        <v>583.25302083759</v>
       </c>
       <c r="Q4">
-        <v>1106.335902780615</v>
+        <v>1102.15302083759</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08266434117597457</v>
+        <v>0.08294328011696168</v>
       </c>
       <c r="T4">
-        <v>0.6751833548598507</v>
+        <v>0.6802922195233395</v>
       </c>
       <c r="U4">
         <v>0.05868110587651873</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>71.21903926312042</v>
+        <v>47.47935950874695</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08174009793214859</v>
+        <v>0.08161239736604495</v>
       </c>
       <c r="C5">
-        <v>8466.970924709605</v>
+        <v>8398.100768101407</v>
       </c>
       <c r="D5">
-        <v>8069.908924709605</v>
+        <v>8098.684768101407</v>
       </c>
       <c r="E5">
-        <v>-5545.962</v>
+        <v>-5448.316</v>
       </c>
       <c r="F5">
-        <v>292.9379999999999</v>
+        <v>390.5839999999999</v>
       </c>
       <c r="G5">
         <v>690</v>
@@ -1825,28 +1825,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M5">
-        <v>17.18992579325564</v>
+        <v>22.91990105767419</v>
       </c>
       <c r="N5">
-        <v>798.976740873411</v>
+        <v>793.2467656089924</v>
       </c>
       <c r="O5">
-        <v>215.723720035821</v>
+        <v>214.176626714428</v>
       </c>
       <c r="P5">
-        <v>583.25302083759</v>
+        <v>579.0701388945645</v>
       </c>
       <c r="Q5">
-        <v>1102.15302083759</v>
+        <v>1097.970138894565</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08294328011696168</v>
+        <v>0.08322803028588605</v>
       </c>
       <c r="T5">
-        <v>0.6802922195233395</v>
+        <v>0.6855075188673179</v>
       </c>
       <c r="U5">
         <v>0.05868110587651873</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>47.47935950874695</v>
+        <v>35.60951963156021</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08161239736604495</v>
+        <v>0.08148469679994129</v>
       </c>
       <c r="C6">
-        <v>8398.100768101407</v>
+        <v>8329.436564846932</v>
       </c>
       <c r="D6">
-        <v>8098.684768101407</v>
+        <v>8127.666564846932</v>
       </c>
       <c r="E6">
-        <v>-5448.316</v>
+        <v>-5350.67</v>
       </c>
       <c r="F6">
-        <v>390.5839999999999</v>
+        <v>488.23</v>
       </c>
       <c r="G6">
         <v>690</v>
@@ -1907,28 +1907,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M6">
-        <v>22.91990105767419</v>
+        <v>28.64987632209274</v>
       </c>
       <c r="N6">
-        <v>793.2467656089924</v>
+        <v>787.5167903445739</v>
       </c>
       <c r="O6">
-        <v>214.176626714428</v>
+        <v>212.629533393035</v>
       </c>
       <c r="P6">
-        <v>579.0701388945645</v>
+        <v>574.8872569515389</v>
       </c>
       <c r="Q6">
-        <v>1097.970138894565</v>
+        <v>1093.787256951539</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08322803028588605</v>
+        <v>0.0835187751952088</v>
       </c>
       <c r="T6">
-        <v>0.6855075188673179</v>
+        <v>0.6908326139869588</v>
       </c>
       <c r="U6">
         <v>0.05868110587651873</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.60951963156021</v>
+        <v>28.48761570524817</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08148469679994129</v>
+        <v>0.08135699623383763</v>
       </c>
       <c r="C7">
-        <v>8329.436564846932</v>
+        <v>8260.980533949132</v>
       </c>
       <c r="D7">
-        <v>8127.666564846932</v>
+        <v>8156.856533949132</v>
       </c>
       <c r="E7">
-        <v>-5350.67</v>
+        <v>-5253.023999999999</v>
       </c>
       <c r="F7">
-        <v>488.23</v>
+        <v>585.876</v>
       </c>
       <c r="G7">
         <v>690</v>
@@ -1989,28 +1989,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M7">
-        <v>28.64987632209274</v>
+        <v>34.37985158651129</v>
       </c>
       <c r="N7">
-        <v>787.5167903445739</v>
+        <v>781.7868150801553</v>
       </c>
       <c r="O7">
-        <v>212.629533393035</v>
+        <v>211.0824400716419</v>
       </c>
       <c r="P7">
-        <v>574.8872569515389</v>
+        <v>570.7043750085134</v>
       </c>
       <c r="Q7">
-        <v>1093.787256951539</v>
+        <v>1089.604375008513</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0835187751952088</v>
+        <v>0.08381570616643204</v>
       </c>
       <c r="T7">
-        <v>0.6908326139869588</v>
+        <v>0.6962710090027624</v>
       </c>
       <c r="U7">
         <v>0.05868110587651873</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.48761570524817</v>
+        <v>23.73967975437347</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08135699623383763</v>
+        <v>0.08122929566773399</v>
       </c>
       <c r="C8">
-        <v>8260.980533949132</v>
+        <v>8192.734926403451</v>
       </c>
       <c r="D8">
-        <v>8156.856533949132</v>
+        <v>8186.256926403451</v>
       </c>
       <c r="E8">
-        <v>-5253.023999999999</v>
+        <v>-5155.378</v>
       </c>
       <c r="F8">
-        <v>585.8759999999999</v>
+        <v>683.5219999999998</v>
       </c>
       <c r="G8">
         <v>690</v>
@@ -2071,28 +2071,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M8">
-        <v>34.37985158651128</v>
+        <v>40.10982685092983</v>
       </c>
       <c r="N8">
-        <v>781.7868150801553</v>
+        <v>776.0568398157368</v>
       </c>
       <c r="O8">
-        <v>211.0824400716419</v>
+        <v>209.5353467502489</v>
       </c>
       <c r="P8">
-        <v>570.7043750085134</v>
+        <v>566.5214930654879</v>
       </c>
       <c r="Q8">
-        <v>1089.604375008513</v>
+        <v>1085.421493065488</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08381570616643204</v>
+        <v>0.08411902274993965</v>
       </c>
       <c r="T8">
-        <v>0.6962710090027624</v>
+        <v>0.7018263587500886</v>
       </c>
       <c r="U8">
         <v>0.05868110587651873</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.73967975437347</v>
+        <v>20.34829693232012</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08122929566773397</v>
+        <v>0.08110159510163033</v>
       </c>
       <c r="C9">
-        <v>8192.734926403456</v>
+        <v>8124.702025776502</v>
       </c>
       <c r="D9">
-        <v>8186.256926403456</v>
+        <v>8215.870025776501</v>
       </c>
       <c r="E9">
-        <v>-5155.378</v>
+        <v>-5057.732</v>
       </c>
       <c r="F9">
-        <v>683.5219999999999</v>
+        <v>781.1679999999999</v>
       </c>
       <c r="G9">
         <v>690</v>
@@ -2153,28 +2153,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M9">
-        <v>40.10982685092983</v>
+        <v>45.83980211534838</v>
       </c>
       <c r="N9">
-        <v>776.0568398157368</v>
+        <v>770.3268645513183</v>
       </c>
       <c r="O9">
-        <v>209.5353467502489</v>
+        <v>207.988253428856</v>
       </c>
       <c r="P9">
-        <v>566.5214930654879</v>
+        <v>562.3386111224623</v>
       </c>
       <c r="Q9">
-        <v>1085.421493065488</v>
+        <v>1081.238611122462</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08411902274993965</v>
+        <v>0.08442893317221917</v>
       </c>
       <c r="T9">
-        <v>0.7018263587500886</v>
+        <v>0.7075024769701828</v>
       </c>
       <c r="U9">
         <v>0.05868110587651873</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.34829693232012</v>
+        <v>17.80475981578011</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08110159510163033</v>
+        <v>0.08097389453552667</v>
       </c>
       <c r="C10">
-        <v>8124.702025776502</v>
+        <v>8056.884148797284</v>
       </c>
       <c r="D10">
-        <v>8215.870025776501</v>
+        <v>8245.698148797284</v>
       </c>
       <c r="E10">
-        <v>-5057.732</v>
+        <v>-4960.085999999999</v>
       </c>
       <c r="F10">
-        <v>781.1679999999999</v>
+        <v>878.8139999999999</v>
       </c>
       <c r="G10">
         <v>690</v>
@@ -2235,28 +2235,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M10">
-        <v>45.83980211534838</v>
+        <v>51.56977737976693</v>
       </c>
       <c r="N10">
-        <v>770.3268645513183</v>
+        <v>764.5968892868997</v>
       </c>
       <c r="O10">
-        <v>207.988253428856</v>
+        <v>206.4411601074629</v>
       </c>
       <c r="P10">
-        <v>562.3386111224623</v>
+        <v>558.1557291794368</v>
       </c>
       <c r="Q10">
-        <v>1081.238611122462</v>
+        <v>1077.055729179437</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08442893317221917</v>
+        <v>0.08474565481257076</v>
       </c>
       <c r="T10">
-        <v>0.7075024769701828</v>
+        <v>0.713303345041268</v>
       </c>
       <c r="U10">
         <v>0.05868110587651873</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.80475981578011</v>
+        <v>15.82645316958232</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08097389453552667</v>
+        <v>0.08084619396942301</v>
       </c>
       <c r="C11">
-        <v>8056.884148797284</v>
+        <v>7989.283645961398</v>
       </c>
       <c r="D11">
-        <v>8245.698148797284</v>
+        <v>8275.743645961398</v>
       </c>
       <c r="E11">
-        <v>-4960.085999999999</v>
+        <v>-4862.44</v>
       </c>
       <c r="F11">
-        <v>878.8139999999999</v>
+        <v>976.4599999999998</v>
       </c>
       <c r="G11">
         <v>690</v>
@@ -2317,28 +2317,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M11">
-        <v>51.56977737976693</v>
+        <v>57.29975264418547</v>
       </c>
       <c r="N11">
-        <v>764.5968892868997</v>
+        <v>758.8669140224812</v>
       </c>
       <c r="O11">
-        <v>206.4411601074629</v>
+        <v>204.8940667860699</v>
       </c>
       <c r="P11">
-        <v>558.1557291794368</v>
+        <v>553.9728472364112</v>
       </c>
       <c r="Q11">
-        <v>1077.055729179437</v>
+        <v>1072.872847236411</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08474565481257076</v>
+        <v>0.08506941471159683</v>
       </c>
       <c r="T11">
-        <v>0.713303345041268</v>
+        <v>0.7192331212917108</v>
       </c>
       <c r="U11">
         <v>0.05868110587651873</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.82645316958232</v>
+        <v>14.24380785262409</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08084619396942301</v>
+        <v>0.08071849340331935</v>
       </c>
       <c r="C12">
-        <v>7989.283645961398</v>
+        <v>7921.902902148469</v>
       </c>
       <c r="D12">
-        <v>8275.743645961398</v>
+        <v>8306.008902148469</v>
       </c>
       <c r="E12">
-        <v>-4862.44</v>
+        <v>-4764.794</v>
       </c>
       <c r="F12">
-        <v>976.4599999999999</v>
+        <v>1074.106</v>
       </c>
       <c r="G12">
         <v>690</v>
@@ -2399,28 +2399,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M12">
-        <v>57.29975264418547</v>
+        <v>63.02972790860402</v>
       </c>
       <c r="N12">
-        <v>758.8669140224812</v>
+        <v>753.1369387580626</v>
       </c>
       <c r="O12">
-        <v>204.8940667860699</v>
+        <v>203.3469734646769</v>
       </c>
       <c r="P12">
-        <v>553.9728472364112</v>
+        <v>549.7899652933856</v>
       </c>
       <c r="Q12">
-        <v>1072.872847236411</v>
+        <v>1068.689965293386</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08506941471159683</v>
+        <v>0.08540045011397181</v>
       </c>
       <c r="T12">
-        <v>0.7192331212917108</v>
+        <v>0.7252961509410398</v>
       </c>
       <c r="U12">
         <v>0.05868110587651873</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.24380785262408</v>
+        <v>12.94891622965826</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08071849340331935</v>
+        <v>0.08072219283721571</v>
       </c>
       <c r="C13">
-        <v>7921.902902148469</v>
+        <v>7823.377016655045</v>
       </c>
       <c r="D13">
-        <v>8306.008902148469</v>
+        <v>8305.129016655044</v>
       </c>
       <c r="E13">
-        <v>-4764.794</v>
+        <v>-4667.148</v>
       </c>
       <c r="F13">
-        <v>1074.106</v>
+        <v>1171.752</v>
       </c>
       <c r="G13">
         <v>690</v>
@@ -2481,45 +2481,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M13">
-        <v>63.02972790860402</v>
+        <v>70.51733117302255</v>
       </c>
       <c r="N13">
-        <v>753.1369387580626</v>
+        <v>745.6493354936441</v>
       </c>
       <c r="O13">
-        <v>203.3469734646769</v>
+        <v>201.3253205832839</v>
       </c>
       <c r="P13">
-        <v>549.7899652933856</v>
+        <v>544.3240149103602</v>
       </c>
       <c r="Q13">
-        <v>1068.689965293386</v>
+        <v>1063.22401491036</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08540045011397181</v>
+        <v>0.08573900904821895</v>
       </c>
       <c r="T13">
-        <v>0.7252961509410398</v>
+        <v>0.7314969767187628</v>
       </c>
       <c r="U13">
-        <v>0.05868110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V13">
         <v>0.27</v>
       </c>
       <c r="W13">
-        <v>0.04283720728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>12.94891622965826</v>
+        <v>11.57398689215997</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08072219283721571</v>
+        <v>0.08060544227111206</v>
       </c>
       <c r="C14">
-        <v>7823.377016655045</v>
+        <v>7753.589548280804</v>
       </c>
       <c r="D14">
-        <v>8305.129016655044</v>
+        <v>8332.987548280804</v>
       </c>
       <c r="E14">
-        <v>-4667.148</v>
+        <v>-4569.501999999999</v>
       </c>
       <c r="F14">
-        <v>1171.752</v>
+        <v>1269.398</v>
       </c>
       <c r="G14">
         <v>690</v>
@@ -2563,28 +2563,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M14">
-        <v>70.51733117302255</v>
+        <v>76.39377543744111</v>
       </c>
       <c r="N14">
-        <v>745.6493354936441</v>
+        <v>739.7728912292255</v>
       </c>
       <c r="O14">
-        <v>201.3253205832839</v>
+        <v>199.7386806318909</v>
       </c>
       <c r="P14">
-        <v>544.3240149103602</v>
+        <v>540.0342105973345</v>
       </c>
       <c r="Q14">
-        <v>1063.22401491036</v>
+        <v>1058.934210597335</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08573900904821895</v>
+        <v>0.08608535094647177</v>
       </c>
       <c r="T14">
-        <v>0.7314969767187628</v>
+        <v>0.7378403502155138</v>
       </c>
       <c r="U14">
         <v>0.06018110587651872</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.57398689215997</v>
+        <v>10.68368020814766</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08060544227111206</v>
+        <v>0.0804886917050084</v>
       </c>
       <c r="C15">
-        <v>7753.589548280804</v>
+        <v>7683.989604957427</v>
       </c>
       <c r="D15">
-        <v>8332.987548280804</v>
+        <v>8361.033604957427</v>
       </c>
       <c r="E15">
-        <v>-4569.501999999999</v>
+        <v>-4471.856</v>
       </c>
       <c r="F15">
-        <v>1269.398</v>
+        <v>1367.044</v>
       </c>
       <c r="G15">
         <v>690</v>
@@ -2645,28 +2645,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M15">
-        <v>76.39377543744111</v>
+        <v>82.27021970185966</v>
       </c>
       <c r="N15">
-        <v>739.7728912292255</v>
+        <v>733.896446964807</v>
       </c>
       <c r="O15">
-        <v>199.7386806318909</v>
+        <v>198.1520406804979</v>
       </c>
       <c r="P15">
-        <v>540.0342105973345</v>
+        <v>535.7444062843091</v>
       </c>
       <c r="Q15">
-        <v>1058.934210597335</v>
+        <v>1054.644406284309</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08608535094647177</v>
+        <v>0.08643974730747464</v>
       </c>
       <c r="T15">
-        <v>0.7378403502155138</v>
+        <v>0.7443312440261427</v>
       </c>
       <c r="U15">
         <v>0.06018110587651872</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.68368020814766</v>
+        <v>9.920560193279972</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0804886917050084</v>
+        <v>0.08055809113890475</v>
       </c>
       <c r="C16">
-        <v>7683.989604957427</v>
+        <v>7569.649621485965</v>
       </c>
       <c r="D16">
-        <v>8361.033604957427</v>
+        <v>8344.339621485966</v>
       </c>
       <c r="E16">
-        <v>-4471.856</v>
+        <v>-4374.209999999999</v>
       </c>
       <c r="F16">
-        <v>1367.044</v>
+        <v>1464.69</v>
       </c>
       <c r="G16">
         <v>690</v>
@@ -2727,45 +2727,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M16">
-        <v>82.27021970185966</v>
+        <v>90.63663696627822</v>
       </c>
       <c r="N16">
-        <v>733.896446964807</v>
+        <v>725.5300297003885</v>
       </c>
       <c r="O16">
-        <v>198.1520406804979</v>
+        <v>195.8931080191049</v>
       </c>
       <c r="P16">
-        <v>535.7444062843091</v>
+        <v>529.6369216812836</v>
       </c>
       <c r="Q16">
-        <v>1054.644406284309</v>
+        <v>1048.536921681284</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08643974730747464</v>
+        <v>0.08680248240638347</v>
       </c>
       <c r="T16">
-        <v>0.7443312440261427</v>
+        <v>0.750974864749963</v>
       </c>
       <c r="U16">
-        <v>0.06018110587651872</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V16">
         <v>0.27</v>
       </c>
       <c r="W16">
-        <v>0.04393220728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>9.920560193279972</v>
+        <v>9.004820721341694</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08055809113890475</v>
+        <v>0.08045375057280109</v>
       </c>
       <c r="C17">
-        <v>7569.649621485966</v>
+        <v>7497.127976151069</v>
       </c>
       <c r="D17">
-        <v>8344.339621485966</v>
+        <v>8369.463976151068</v>
       </c>
       <c r="E17">
-        <v>-4374.21</v>
+        <v>-4276.564</v>
       </c>
       <c r="F17">
-        <v>1464.69</v>
+        <v>1562.336</v>
       </c>
       <c r="G17">
         <v>690</v>
@@ -2809,28 +2809,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M17">
-        <v>90.6366369662782</v>
+        <v>96.67907943069675</v>
       </c>
       <c r="N17">
-        <v>725.5300297003885</v>
+        <v>719.4875872359698</v>
       </c>
       <c r="O17">
-        <v>195.8931080191049</v>
+        <v>194.2616485537119</v>
       </c>
       <c r="P17">
-        <v>529.6369216812836</v>
+        <v>525.2259386822579</v>
       </c>
       <c r="Q17">
-        <v>1048.536921681284</v>
+        <v>1044.125938682258</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08680248240638347</v>
+        <v>0.08717385405526631</v>
       </c>
       <c r="T17">
-        <v>0.750974864749963</v>
+        <v>0.7577766669195883</v>
       </c>
       <c r="U17">
         <v>0.06188110587651872</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.004820721341696</v>
+        <v>8.44201942625784</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08045375057280109</v>
+        <v>0.08034941000669742</v>
       </c>
       <c r="C18">
-        <v>7497.127976151069</v>
+        <v>7424.758083878714</v>
       </c>
       <c r="D18">
-        <v>8369.463976151068</v>
+        <v>8394.740083878714</v>
       </c>
       <c r="E18">
-        <v>-4276.564</v>
+        <v>-4178.918</v>
       </c>
       <c r="F18">
-        <v>1562.336</v>
+        <v>1659.982</v>
       </c>
       <c r="G18">
         <v>690</v>
@@ -2891,28 +2891,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M18">
-        <v>96.67907943069675</v>
+        <v>102.7215218951153</v>
       </c>
       <c r="N18">
-        <v>719.4875872359698</v>
+        <v>713.4451447715513</v>
       </c>
       <c r="O18">
-        <v>194.2616485537119</v>
+        <v>192.6301890883189</v>
       </c>
       <c r="P18">
-        <v>525.2259386822579</v>
+        <v>520.8149556832325</v>
       </c>
       <c r="Q18">
-        <v>1044.125938682258</v>
+        <v>1039.714955683232</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08717385405526631</v>
+        <v>0.08755417441858007</v>
       </c>
       <c r="T18">
-        <v>0.7577766669195883</v>
+        <v>0.7647423679366747</v>
       </c>
       <c r="U18">
         <v>0.06188110587651872</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.44201942625784</v>
+        <v>7.945430048242672</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08034941000669742</v>
+        <v>0.08035018944059379</v>
       </c>
       <c r="C19">
-        <v>7424.758083878714</v>
+        <v>7326.922703007624</v>
       </c>
       <c r="D19">
-        <v>8394.740083878714</v>
+        <v>8394.550703007624</v>
       </c>
       <c r="E19">
-        <v>-4178.918</v>
+        <v>-4081.272</v>
       </c>
       <c r="F19">
-        <v>1659.982</v>
+        <v>1757.628</v>
       </c>
       <c r="G19">
         <v>690</v>
@@ -2973,45 +2973,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M19">
-        <v>102.7215218951153</v>
+        <v>110.1700667595339</v>
       </c>
       <c r="N19">
-        <v>713.4451447715513</v>
+        <v>705.9965999071328</v>
       </c>
       <c r="O19">
-        <v>192.6301890883189</v>
+        <v>190.6190819749259</v>
       </c>
       <c r="P19">
-        <v>520.8149556832325</v>
+        <v>515.377517932207</v>
       </c>
       <c r="Q19">
-        <v>1039.714955683232</v>
+        <v>1034.277517932207</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08755417441858007</v>
+        <v>0.08794377088831612</v>
       </c>
       <c r="T19">
-        <v>0.7647423679366747</v>
+        <v>0.7718779641005191</v>
       </c>
       <c r="U19">
-        <v>0.06188110587651872</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V19">
         <v>0.27</v>
       </c>
       <c r="W19">
-        <v>0.04517320728985866</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.945430048242672</v>
+        <v>7.408243370207792</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08035018944059377</v>
+        <v>0.08025168887449013</v>
       </c>
       <c r="C20">
-        <v>7326.922703007628</v>
+        <v>7253.277500165766</v>
       </c>
       <c r="D20">
-        <v>8394.550703007628</v>
+        <v>8418.551500165766</v>
       </c>
       <c r="E20">
-        <v>-4081.272</v>
+        <v>-3983.626</v>
       </c>
       <c r="F20">
-        <v>1757.628</v>
+        <v>1855.274</v>
       </c>
       <c r="G20">
         <v>690</v>
@@ -3055,28 +3055,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M20">
-        <v>110.1700667595339</v>
+        <v>116.2906260239524</v>
       </c>
       <c r="N20">
-        <v>705.9965999071328</v>
+        <v>699.8760406427142</v>
       </c>
       <c r="O20">
-        <v>190.6190819749259</v>
+        <v>188.9665309735329</v>
       </c>
       <c r="P20">
-        <v>515.377517932207</v>
+        <v>510.9095096691814</v>
       </c>
       <c r="Q20">
-        <v>1034.277517932207</v>
+        <v>1029.809509669181</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08794377088831612</v>
+        <v>0.08834298702397159</v>
       </c>
       <c r="T20">
-        <v>0.7718779641005191</v>
+        <v>0.7791897478239648</v>
       </c>
       <c r="U20">
         <v>0.06268110587651873</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.408243370207793</v>
+        <v>7.018335824407383</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08025168887449013</v>
+        <v>0.08015318830838648</v>
       </c>
       <c r="C21">
-        <v>7253.277500165766</v>
+        <v>7179.769931833158</v>
       </c>
       <c r="D21">
-        <v>8418.551500165766</v>
+        <v>8442.689931833158</v>
       </c>
       <c r="E21">
-        <v>-3983.626</v>
+        <v>-3885.98</v>
       </c>
       <c r="F21">
-        <v>1855.274</v>
+        <v>1952.92</v>
       </c>
       <c r="G21">
         <v>690</v>
@@ -3137,28 +3137,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M21">
-        <v>116.2906260239524</v>
+        <v>122.411185288371</v>
       </c>
       <c r="N21">
-        <v>699.8760406427142</v>
+        <v>693.7554813782957</v>
       </c>
       <c r="O21">
-        <v>188.9665309735329</v>
+        <v>187.3139799721399</v>
       </c>
       <c r="P21">
-        <v>510.9095096691814</v>
+        <v>506.4415014061559</v>
       </c>
       <c r="Q21">
-        <v>1029.809509669181</v>
+        <v>1025.341501406156</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08834298702397159</v>
+        <v>0.08875218356301842</v>
       </c>
       <c r="T21">
-        <v>0.7791897478239648</v>
+        <v>0.7866843261404967</v>
       </c>
       <c r="U21">
         <v>0.06268110587651873</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.018335824407383</v>
+        <v>6.667419033187014</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08015318830838648</v>
+        <v>0.08005468774228282</v>
       </c>
       <c r="C22">
-        <v>7179.769931833158</v>
+        <v>7106.401185328504</v>
       </c>
       <c r="D22">
-        <v>8442.689931833158</v>
+        <v>8466.967185328504</v>
       </c>
       <c r="E22">
-        <v>-3885.98</v>
+        <v>-3788.334</v>
       </c>
       <c r="F22">
-        <v>1952.92</v>
+        <v>2050.566</v>
       </c>
       <c r="G22">
         <v>690</v>
@@ -3219,28 +3219,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M22">
-        <v>122.411185288371</v>
+        <v>128.5317445527895</v>
       </c>
       <c r="N22">
-        <v>693.7554813782957</v>
+        <v>687.6349221138771</v>
       </c>
       <c r="O22">
-        <v>187.3139799721399</v>
+        <v>185.6614289707468</v>
       </c>
       <c r="P22">
-        <v>506.4415014061559</v>
+        <v>501.9734931431303</v>
       </c>
       <c r="Q22">
-        <v>1025.341501406156</v>
+        <v>1020.87349314313</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08875218356301842</v>
+        <v>0.08917173950811709</v>
       </c>
       <c r="T22">
-        <v>0.7866843261404967</v>
+        <v>0.7943686406169406</v>
       </c>
       <c r="U22">
         <v>0.06268110587651873</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.667419033187014</v>
+        <v>6.349922888749537</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08005468774228282</v>
+        <v>0.08011678717617916</v>
       </c>
       <c r="C23">
-        <v>7106.401185328504</v>
+        <v>6993.433416821201</v>
       </c>
       <c r="D23">
-        <v>8466.967185328504</v>
+        <v>8451.6454168212</v>
       </c>
       <c r="E23">
-        <v>-3788.334</v>
+        <v>-3690.688</v>
       </c>
       <c r="F23">
-        <v>2050.566</v>
+        <v>2148.212</v>
       </c>
       <c r="G23">
         <v>690</v>
@@ -3301,45 +3301,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M23">
-        <v>128.5317445527895</v>
+        <v>136.800515817208</v>
       </c>
       <c r="N23">
-        <v>687.6349221138771</v>
+        <v>679.3661508494586</v>
       </c>
       <c r="O23">
-        <v>185.6614289707468</v>
+        <v>183.4288607293538</v>
       </c>
       <c r="P23">
-        <v>501.9734931431303</v>
+        <v>495.9372901201048</v>
       </c>
       <c r="Q23">
-        <v>1020.87349314313</v>
+        <v>1014.837290120105</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08917173950811709</v>
+        <v>0.08960205329796186</v>
       </c>
       <c r="T23">
-        <v>0.7943686406169406</v>
+        <v>0.8022499887979087</v>
       </c>
       <c r="U23">
-        <v>0.06268110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V23">
         <v>0.27</v>
       </c>
       <c r="W23">
-        <v>0.04575720728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.349922888749537</v>
+        <v>5.966108108519292</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08011678717617916</v>
+        <v>0.08002558661007551</v>
       </c>
       <c r="C24">
-        <v>6993.433416821201</v>
+        <v>6918.308428814447</v>
       </c>
       <c r="D24">
-        <v>8451.6454168212</v>
+        <v>8474.166428814447</v>
       </c>
       <c r="E24">
-        <v>-3690.688</v>
+        <v>-3593.042</v>
       </c>
       <c r="F24">
-        <v>2148.212</v>
+        <v>2245.858</v>
       </c>
       <c r="G24">
         <v>690</v>
@@ -3383,28 +3383,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M24">
-        <v>136.800515817208</v>
+        <v>143.0187210816266</v>
       </c>
       <c r="N24">
-        <v>679.3661508494586</v>
+        <v>673.14794558504</v>
       </c>
       <c r="O24">
-        <v>183.4288607293538</v>
+        <v>181.7499453079608</v>
       </c>
       <c r="P24">
-        <v>495.9372901201048</v>
+        <v>491.3980002770792</v>
       </c>
       <c r="Q24">
-        <v>1014.837290120105</v>
+        <v>1010.298000277079</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08960205329796186</v>
+        <v>0.09004354406936106</v>
       </c>
       <c r="T24">
-        <v>0.8022499887979087</v>
+        <v>0.8103360473212396</v>
       </c>
       <c r="U24">
         <v>0.06368110587651873</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.966108108519292</v>
+        <v>5.706712103801062</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08002558661007551</v>
+        <v>0.07993438604397186</v>
       </c>
       <c r="C25">
-        <v>6918.308428814447</v>
+        <v>6843.303784501021</v>
       </c>
       <c r="D25">
-        <v>8474.166428814447</v>
+        <v>8496.807784501021</v>
       </c>
       <c r="E25">
-        <v>-3593.042</v>
+        <v>-3495.396</v>
       </c>
       <c r="F25">
-        <v>2245.858</v>
+        <v>2343.504</v>
       </c>
       <c r="G25">
         <v>690</v>
@@ -3465,28 +3465,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M25">
-        <v>143.0187210816266</v>
+        <v>149.2369263460452</v>
       </c>
       <c r="N25">
-        <v>673.14794558504</v>
+        <v>666.9297403206215</v>
       </c>
       <c r="O25">
-        <v>181.7499453079608</v>
+        <v>180.0710298865678</v>
       </c>
       <c r="P25">
-        <v>491.3980002770792</v>
+        <v>486.8587104340537</v>
       </c>
       <c r="Q25">
-        <v>1010.298000277079</v>
+        <v>1005.758710434054</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09004354406936106</v>
+        <v>0.09049665301895497</v>
       </c>
       <c r="T25">
-        <v>0.8103360473212396</v>
+        <v>0.8186348968583425</v>
       </c>
       <c r="U25">
         <v>0.06368110587651873</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.706712103801062</v>
+        <v>5.468932432809351</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07993438604397186</v>
+        <v>0.0798431854778682</v>
       </c>
       <c r="C26">
-        <v>6843.303784501022</v>
+        <v>6768.420451071232</v>
       </c>
       <c r="D26">
-        <v>8496.807784501021</v>
+        <v>8519.570451071231</v>
       </c>
       <c r="E26">
-        <v>-3495.396</v>
+        <v>-3397.75</v>
       </c>
       <c r="F26">
-        <v>2343.503999999999</v>
+        <v>2441.15</v>
       </c>
       <c r="G26">
         <v>690</v>
@@ -3547,28 +3547,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M26">
-        <v>149.2369263460451</v>
+        <v>155.4551316104637</v>
       </c>
       <c r="N26">
-        <v>666.9297403206215</v>
+        <v>660.7115350562029</v>
       </c>
       <c r="O26">
-        <v>180.0710298865678</v>
+        <v>178.3921144651748</v>
       </c>
       <c r="P26">
-        <v>486.8587104340537</v>
+        <v>482.3194205910281</v>
       </c>
       <c r="Q26">
-        <v>1005.758710434054</v>
+        <v>1001.219420591028</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09049665301895497</v>
+        <v>0.09096184487387138</v>
       </c>
       <c r="T26">
-        <v>0.8186348968583425</v>
+        <v>0.8271550490497681</v>
       </c>
       <c r="U26">
         <v>0.06368110587651873</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.468932432809352</v>
+        <v>5.250175135496977</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0798431854778682</v>
+        <v>0.07975198491176455</v>
       </c>
       <c r="C27">
-        <v>6768.420451071232</v>
+        <v>6693.659406107494</v>
       </c>
       <c r="D27">
-        <v>8519.570451071231</v>
+        <v>8542.455406107494</v>
       </c>
       <c r="E27">
-        <v>-3397.75</v>
+        <v>-3300.104</v>
       </c>
       <c r="F27">
-        <v>2441.15</v>
+        <v>2538.796</v>
       </c>
       <c r="G27">
         <v>690</v>
@@ -3629,28 +3629,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M27">
-        <v>155.4551316104637</v>
+        <v>161.6733368748822</v>
       </c>
       <c r="N27">
-        <v>660.7115350562029</v>
+        <v>654.4933297917844</v>
       </c>
       <c r="O27">
-        <v>178.3921144651748</v>
+        <v>176.7131990437818</v>
       </c>
       <c r="P27">
-        <v>482.3194205910281</v>
+        <v>477.7801307480026</v>
       </c>
       <c r="Q27">
-        <v>1001.219420591028</v>
+        <v>996.6801307480025</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09096184487387138</v>
+        <v>0.09143960948162337</v>
       </c>
       <c r="T27">
-        <v>0.8271550490497681</v>
+        <v>0.8359054756247456</v>
       </c>
       <c r="U27">
         <v>0.06368110587651873</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.250175135496977</v>
+        <v>5.048245322593247</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07975198491176455</v>
+        <v>0.0796607843456609</v>
       </c>
       <c r="C28">
-        <v>6693.659406107494</v>
+        <v>6619.021637724315</v>
       </c>
       <c r="D28">
-        <v>8542.455406107494</v>
+        <v>8565.463637724315</v>
       </c>
       <c r="E28">
-        <v>-3300.104</v>
+        <v>-3202.458</v>
       </c>
       <c r="F28">
-        <v>2538.796</v>
+        <v>2636.442</v>
       </c>
       <c r="G28">
         <v>690</v>
@@ -3711,28 +3711,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M28">
-        <v>161.6733368748822</v>
+        <v>167.8915421393008</v>
       </c>
       <c r="N28">
-        <v>654.4933297917844</v>
+        <v>648.2751245273658</v>
       </c>
       <c r="O28">
-        <v>176.7131990437818</v>
+        <v>175.0342836223888</v>
       </c>
       <c r="P28">
-        <v>477.7801307480026</v>
+        <v>473.2408409049771</v>
       </c>
       <c r="Q28">
-        <v>996.6801307480025</v>
+        <v>992.140840904977</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09143960948162337</v>
+        <v>0.09193046353068364</v>
       </c>
       <c r="T28">
-        <v>0.8359054756247456</v>
+        <v>0.8448956399141062</v>
       </c>
       <c r="U28">
         <v>0.06368110587651873</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.048245322593247</v>
+        <v>4.861273273608312</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0796607843456609</v>
+        <v>0.07956958377955724</v>
       </c>
       <c r="C29">
-        <v>6619.021637724315</v>
+        <v>6544.508144710489</v>
       </c>
       <c r="D29">
-        <v>8565.463637724315</v>
+        <v>8588.596144710489</v>
       </c>
       <c r="E29">
-        <v>-3202.458</v>
+        <v>-3104.812</v>
       </c>
       <c r="F29">
-        <v>2636.442</v>
+        <v>2734.088</v>
       </c>
       <c r="G29">
         <v>690</v>
@@ -3793,28 +3793,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M29">
-        <v>167.8915421393008</v>
+        <v>174.1097474037193</v>
       </c>
       <c r="N29">
-        <v>648.2751245273658</v>
+        <v>642.0569192629473</v>
       </c>
       <c r="O29">
-        <v>175.0342836223888</v>
+        <v>173.3553682009958</v>
       </c>
       <c r="P29">
-        <v>473.2408409049771</v>
+        <v>468.7015510619515</v>
       </c>
       <c r="Q29">
-        <v>992.140840904977</v>
+        <v>987.6015510619516</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09193046353068364</v>
+        <v>0.09243495241444002</v>
       </c>
       <c r="T29">
-        <v>0.8448956399141062</v>
+        <v>0.8541355309892824</v>
       </c>
       <c r="U29">
         <v>0.06368110587651873</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.861273273608312</v>
+        <v>4.687656370979444</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07956958377955724</v>
+        <v>0.07947838321345359</v>
       </c>
       <c r="C30">
-        <v>6544.508144710489</v>
+        <v>6470.119936673624</v>
       </c>
       <c r="D30">
-        <v>8588.596144710489</v>
+        <v>8611.853936673624</v>
       </c>
       <c r="E30">
-        <v>-3104.812</v>
+        <v>-3007.166</v>
       </c>
       <c r="F30">
-        <v>2734.088</v>
+        <v>2831.734</v>
       </c>
       <c r="G30">
         <v>690</v>
@@ -3875,28 +3875,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M30">
-        <v>174.1097474037193</v>
+        <v>180.3279526681379</v>
       </c>
       <c r="N30">
-        <v>642.0569192629473</v>
+        <v>635.8387139985288</v>
       </c>
       <c r="O30">
-        <v>173.3553682009958</v>
+        <v>171.6764527796028</v>
       </c>
       <c r="P30">
-        <v>468.7015510619515</v>
+        <v>464.162261218926</v>
       </c>
       <c r="Q30">
-        <v>987.6015510619516</v>
+        <v>983.062261218926</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09243495241444002</v>
+        <v>0.09295365225266841</v>
       </c>
       <c r="T30">
-        <v>0.8541355309892824</v>
+        <v>0.8636357006862945</v>
       </c>
       <c r="U30">
         <v>0.06368110587651873</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.687656370979444</v>
+        <v>4.526013047842222</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07947838321345359</v>
+        <v>0.07993468264734993</v>
       </c>
       <c r="C31">
-        <v>6470.119936673625</v>
+        <v>6257.353953965736</v>
       </c>
       <c r="D31">
-        <v>8611.853936673624</v>
+        <v>8496.733953965735</v>
       </c>
       <c r="E31">
-        <v>-3007.166</v>
+        <v>-2909.52</v>
       </c>
       <c r="F31">
-        <v>2831.733999999999</v>
+        <v>2929.38</v>
       </c>
       <c r="G31">
         <v>690</v>
@@ -3957,45 +3957,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M31">
-        <v>180.3279526681379</v>
+        <v>193.8696079325564</v>
       </c>
       <c r="N31">
-        <v>635.8387139985288</v>
+        <v>622.2970587341102</v>
       </c>
       <c r="O31">
-        <v>171.6764527796028</v>
+        <v>168.0202058582098</v>
       </c>
       <c r="P31">
-        <v>464.162261218926</v>
+        <v>454.2768528759004</v>
       </c>
       <c r="Q31">
-        <v>983.062261218926</v>
+        <v>973.1768528759004</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09295365225266841</v>
+        <v>0.09348717208627477</v>
       </c>
       <c r="T31">
-        <v>0.8636357006862945</v>
+        <v>0.8734073038032213</v>
       </c>
       <c r="U31">
-        <v>0.06368110587651873</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V31">
         <v>0.27</v>
       </c>
       <c r="W31">
-        <v>0.04648720728985867</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.526013047842222</v>
+        <v>4.209874231295685</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07993468264734993</v>
+        <v>0.07986173208124628</v>
       </c>
       <c r="C32">
-        <v>6257.353953965736</v>
+        <v>6177.905547396846</v>
       </c>
       <c r="D32">
-        <v>8496.733953965735</v>
+        <v>8514.931547396845</v>
       </c>
       <c r="E32">
-        <v>-2909.52</v>
+        <v>-2811.874</v>
       </c>
       <c r="F32">
-        <v>2929.38</v>
+        <v>3027.025999999999</v>
       </c>
       <c r="G32">
         <v>690</v>
@@ -4039,28 +4039,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M32">
-        <v>193.8696079325564</v>
+        <v>200.3319281969749</v>
       </c>
       <c r="N32">
-        <v>622.2970587341102</v>
+        <v>615.8347384696917</v>
       </c>
       <c r="O32">
-        <v>168.0202058582098</v>
+        <v>166.2753793868168</v>
       </c>
       <c r="P32">
-        <v>454.2768528759004</v>
+        <v>449.5593590828749</v>
       </c>
       <c r="Q32">
-        <v>973.1768528759004</v>
+        <v>968.4593590828749</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09348717208627477</v>
+        <v>0.0940361562628842</v>
       </c>
       <c r="T32">
-        <v>0.8734073038032213</v>
+        <v>0.8834621417931023</v>
       </c>
       <c r="U32">
         <v>0.06618110587651872</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.209874231295685</v>
+        <v>4.07407183673776</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07986173208124628</v>
+        <v>0.08060638151514263</v>
       </c>
       <c r="C33">
-        <v>6177.905547396846</v>
+        <v>5898.090684090078</v>
       </c>
       <c r="D33">
-        <v>8514.931547396845</v>
+        <v>8332.762684090078</v>
       </c>
       <c r="E33">
-        <v>-2811.874</v>
+        <v>-2714.228</v>
       </c>
       <c r="F33">
-        <v>3027.025999999999</v>
+        <v>3124.672</v>
       </c>
       <c r="G33">
         <v>690</v>
@@ -4121,45 +4121,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M33">
-        <v>200.3319281969749</v>
+        <v>217.7306004613935</v>
       </c>
       <c r="N33">
-        <v>615.8347384696917</v>
+        <v>598.4360662052732</v>
       </c>
       <c r="O33">
-        <v>166.2753793868168</v>
+        <v>161.5777378754238</v>
       </c>
       <c r="P33">
-        <v>449.5593590828749</v>
+        <v>436.8583283298494</v>
       </c>
       <c r="Q33">
-        <v>968.4593590828749</v>
+        <v>955.7583283298494</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0940361562628842</v>
+        <v>0.09460128703292331</v>
       </c>
       <c r="T33">
-        <v>0.8834621417931023</v>
+        <v>0.8938127103120975</v>
       </c>
       <c r="U33">
-        <v>0.06618110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V33">
         <v>0.27</v>
       </c>
       <c r="W33">
-        <v>0.04831220728985867</v>
+        <v>0.05086720728985867</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.07407183673776</v>
+        <v>3.748516124684016</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08060638151514263</v>
+        <v>0.08055898094903896</v>
       </c>
       <c r="C34">
-        <v>5898.090684090078</v>
+        <v>5811.808011139639</v>
       </c>
       <c r="D34">
-        <v>8332.762684090078</v>
+        <v>8344.126011139639</v>
       </c>
       <c r="E34">
-        <v>-2714.228</v>
+        <v>-2616.582</v>
       </c>
       <c r="F34">
-        <v>3124.672</v>
+        <v>3222.318</v>
       </c>
       <c r="G34">
         <v>690</v>
@@ -4203,28 +4203,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M34">
-        <v>217.7306004613935</v>
+        <v>224.534681725812</v>
       </c>
       <c r="N34">
-        <v>598.4360662052732</v>
+        <v>591.6319849408546</v>
       </c>
       <c r="O34">
-        <v>161.5777378754238</v>
+        <v>159.7406359340308</v>
       </c>
       <c r="P34">
-        <v>436.8583283298494</v>
+        <v>431.8913490068239</v>
       </c>
       <c r="Q34">
-        <v>955.7583283298494</v>
+        <v>950.7913490068238</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09460128703292331</v>
+        <v>0.09518328737818749</v>
       </c>
       <c r="T34">
-        <v>0.8938127103120975</v>
+        <v>0.9044722510256897</v>
       </c>
       <c r="U34">
         <v>0.06968110587651873</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.748516124684016</v>
+        <v>3.634924726966319</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08055898094903896</v>
+        <v>0.08051158038293531</v>
       </c>
       <c r="C35">
-        <v>5811.808011139639</v>
+        <v>5725.556372681376</v>
       </c>
       <c r="D35">
-        <v>8344.126011139639</v>
+        <v>8355.520372681376</v>
       </c>
       <c r="E35">
-        <v>-2616.582</v>
+        <v>-2518.936</v>
       </c>
       <c r="F35">
-        <v>3222.318</v>
+        <v>3319.964</v>
       </c>
       <c r="G35">
         <v>690</v>
@@ -4285,28 +4285,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M35">
-        <v>224.534681725812</v>
+        <v>231.3387629902306</v>
       </c>
       <c r="N35">
-        <v>591.6319849408546</v>
+        <v>584.827903676436</v>
       </c>
       <c r="O35">
-        <v>159.7406359340308</v>
+        <v>157.9035339926377</v>
       </c>
       <c r="P35">
-        <v>431.8913490068239</v>
+        <v>426.9243696837983</v>
       </c>
       <c r="Q35">
-        <v>950.7913490068238</v>
+        <v>945.8243696837983</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09518328737818749</v>
+        <v>0.09578292409755056</v>
       </c>
       <c r="T35">
-        <v>0.9044722510256897</v>
+        <v>0.9154548081245422</v>
       </c>
       <c r="U35">
         <v>0.06968110587651873</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.634924726966319</v>
+        <v>3.528015176173191</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08051158038293531</v>
+        <v>0.08117957981683166</v>
       </c>
       <c r="C36">
-        <v>5725.556372681376</v>
+        <v>5470.150362309369</v>
       </c>
       <c r="D36">
-        <v>8355.520372681376</v>
+        <v>8197.760362309369</v>
       </c>
       <c r="E36">
-        <v>-2518.936</v>
+        <v>-2421.29</v>
       </c>
       <c r="F36">
-        <v>3319.964</v>
+        <v>3417.61</v>
       </c>
       <c r="G36">
         <v>690</v>
@@ -4367,45 +4367,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M36">
-        <v>231.3387629902306</v>
+        <v>247.7121522546491</v>
       </c>
       <c r="N36">
-        <v>584.827903676436</v>
+        <v>568.4545144120175</v>
       </c>
       <c r="O36">
-        <v>157.9035339926377</v>
+        <v>153.4827188912447</v>
       </c>
       <c r="P36">
-        <v>426.9243696837983</v>
+        <v>414.9717955207727</v>
       </c>
       <c r="Q36">
-        <v>945.8243696837983</v>
+        <v>933.8717955207727</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09578292409755056</v>
+        <v>0.09640101117750943</v>
       </c>
       <c r="T36">
-        <v>0.9154548081245422</v>
+        <v>0.9267752900572056</v>
       </c>
       <c r="U36">
-        <v>0.06968110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V36">
         <v>0.27</v>
       </c>
       <c r="W36">
-        <v>0.05086720728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.528015176173191</v>
+        <v>3.294818842103652</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08117957981683166</v>
+        <v>0.081152619250728</v>
       </c>
       <c r="C37">
-        <v>5470.150362309369</v>
+        <v>5378.756127096089</v>
       </c>
       <c r="D37">
-        <v>8197.760362309369</v>
+        <v>8204.012127096088</v>
       </c>
       <c r="E37">
-        <v>-2421.29</v>
+        <v>-2323.644</v>
       </c>
       <c r="F37">
-        <v>3417.61</v>
+        <v>3515.256</v>
       </c>
       <c r="G37">
         <v>690</v>
@@ -4449,28 +4449,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M37">
-        <v>247.7121522546491</v>
+        <v>254.7896423190677</v>
       </c>
       <c r="N37">
-        <v>568.4545144120175</v>
+        <v>561.377024347599</v>
       </c>
       <c r="O37">
-        <v>153.4827188912447</v>
+        <v>151.5717965738517</v>
       </c>
       <c r="P37">
-        <v>414.9717955207727</v>
+        <v>409.8052277737472</v>
       </c>
       <c r="Q37">
-        <v>933.8717955207727</v>
+        <v>928.7052277737472</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09640101117750943</v>
+        <v>0.09703841347871701</v>
       </c>
       <c r="T37">
-        <v>0.9267752900572056</v>
+        <v>0.9384495370502647</v>
       </c>
       <c r="U37">
         <v>0.07248110587651872</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.294818842103652</v>
+        <v>3.203296096489662</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.081152619250728</v>
+        <v>0.08112565868462435</v>
       </c>
       <c r="C38">
-        <v>5378.756127096089</v>
+        <v>5287.371434584858</v>
       </c>
       <c r="D38">
-        <v>8204.012127096088</v>
+        <v>8210.273434584858</v>
       </c>
       <c r="E38">
-        <v>-2323.644</v>
+        <v>-2225.998</v>
       </c>
       <c r="F38">
-        <v>3515.255999999999</v>
+        <v>3612.902</v>
       </c>
       <c r="G38">
         <v>690</v>
@@ -4531,28 +4531,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M38">
-        <v>254.7896423190677</v>
+        <v>261.8671323834862</v>
       </c>
       <c r="N38">
-        <v>561.377024347599</v>
+        <v>554.2995342831805</v>
       </c>
       <c r="O38">
-        <v>151.5717965738517</v>
+        <v>149.6608742564588</v>
       </c>
       <c r="P38">
-        <v>409.8052277737472</v>
+        <v>404.6386600267217</v>
       </c>
       <c r="Q38">
-        <v>928.7052277737472</v>
+        <v>923.5386600267217</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09703841347871701</v>
+        <v>0.09769605077361372</v>
       </c>
       <c r="T38">
-        <v>0.9384495370502647</v>
+        <v>0.9504943950589764</v>
       </c>
       <c r="U38">
         <v>0.07248110587651872</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.203296096489662</v>
+        <v>3.116720526314266</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08112565868462435</v>
+        <v>0.08109869811852069</v>
       </c>
       <c r="C39">
-        <v>5287.371434584858</v>
+        <v>5195.996306641358</v>
       </c>
       <c r="D39">
-        <v>8210.273434584858</v>
+        <v>8216.544306641357</v>
       </c>
       <c r="E39">
-        <v>-2225.998</v>
+        <v>-2128.352</v>
       </c>
       <c r="F39">
-        <v>3612.902</v>
+        <v>3710.547999999999</v>
       </c>
       <c r="G39">
         <v>690</v>
@@ -4613,28 +4613,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M39">
-        <v>261.8671323834862</v>
+        <v>268.9446224479047</v>
       </c>
       <c r="N39">
-        <v>554.2995342831805</v>
+        <v>547.2220442187619</v>
       </c>
       <c r="O39">
-        <v>149.6608742564588</v>
+        <v>147.7499519390657</v>
       </c>
       <c r="P39">
-        <v>404.6386600267217</v>
+        <v>399.4720922796962</v>
       </c>
       <c r="Q39">
-        <v>923.5386600267217</v>
+        <v>918.3720922796962</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09769605077361372</v>
+        <v>0.09837490217479743</v>
       </c>
       <c r="T39">
-        <v>0.9504943950589764</v>
+        <v>0.9629277968744208</v>
       </c>
       <c r="U39">
         <v>0.07248110587651872</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.116720526314266</v>
+        <v>3.034701565095469</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08109869811852069</v>
+        <v>0.08329239755241705</v>
       </c>
       <c r="C40">
-        <v>5195.996306641358</v>
+        <v>4617.596079898089</v>
       </c>
       <c r="D40">
-        <v>8216.544306641357</v>
+        <v>7735.790079898088</v>
       </c>
       <c r="E40">
-        <v>-2128.352</v>
+        <v>-2030.706</v>
       </c>
       <c r="F40">
-        <v>3710.547999999999</v>
+        <v>3808.194</v>
       </c>
       <c r="G40">
         <v>690</v>
@@ -4695,45 +4695,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M40">
-        <v>268.9446224479047</v>
+        <v>305.7260257123233</v>
       </c>
       <c r="N40">
-        <v>547.2220442187619</v>
+        <v>510.4406409543433</v>
       </c>
       <c r="O40">
-        <v>147.7499519390657</v>
+        <v>137.8189730576727</v>
       </c>
       <c r="P40">
-        <v>399.4720922796962</v>
+        <v>372.6216678966706</v>
       </c>
       <c r="Q40">
-        <v>918.3720922796962</v>
+        <v>891.5216678966706</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09837490217479743</v>
+        <v>0.09907601099897076</v>
       </c>
       <c r="T40">
-        <v>0.9629277968744208</v>
+        <v>0.9757688512084044</v>
       </c>
       <c r="U40">
-        <v>0.07248110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V40">
         <v>0.27</v>
       </c>
       <c r="W40">
-        <v>0.05291120728985867</v>
+        <v>0.05860520728985868</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.034701565095469</v>
+        <v>2.669601532172628</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08329239755241705</v>
+        <v>0.0833223769863134</v>
       </c>
       <c r="C41">
-        <v>4617.596079898089</v>
+        <v>4513.769378514993</v>
       </c>
       <c r="D41">
-        <v>7735.790079898088</v>
+        <v>7729.609378514993</v>
       </c>
       <c r="E41">
-        <v>-2030.706</v>
+        <v>-1933.06</v>
       </c>
       <c r="F41">
-        <v>3808.194</v>
+        <v>3905.84</v>
       </c>
       <c r="G41">
         <v>690</v>
@@ -4777,28 +4777,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M41">
-        <v>305.7260257123233</v>
+        <v>313.5651545767419</v>
       </c>
       <c r="N41">
-        <v>510.4406409543433</v>
+        <v>502.6015120899247</v>
       </c>
       <c r="O41">
-        <v>137.8189730576727</v>
+        <v>135.7024082642797</v>
       </c>
       <c r="P41">
-        <v>372.6216678966706</v>
+        <v>366.8991038256451</v>
       </c>
       <c r="Q41">
-        <v>891.5216678966706</v>
+        <v>885.799103825645</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09907601099897076</v>
+        <v>0.09980049011728322</v>
       </c>
       <c r="T41">
-        <v>0.9757688512084044</v>
+        <v>0.9890379406868541</v>
       </c>
       <c r="U41">
         <v>0.08028110587651874</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.669601532172628</v>
+        <v>2.602861493868312</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0833223769863134</v>
+        <v>0.08335235642020974</v>
       </c>
       <c r="C42">
-        <v>4513.769378514993</v>
+        <v>4409.952545696547</v>
       </c>
       <c r="D42">
-        <v>7729.609378514993</v>
+        <v>7723.438545696547</v>
       </c>
       <c r="E42">
-        <v>-1933.06</v>
+        <v>-1835.414</v>
       </c>
       <c r="F42">
-        <v>3905.84</v>
+        <v>4003.486</v>
       </c>
       <c r="G42">
         <v>690</v>
@@ -4859,28 +4859,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M42">
-        <v>313.5651545767419</v>
+        <v>321.4042834411605</v>
       </c>
       <c r="N42">
-        <v>502.6015120899247</v>
+        <v>494.7623832255061</v>
       </c>
       <c r="O42">
-        <v>135.7024082642797</v>
+        <v>133.5858434708867</v>
       </c>
       <c r="P42">
-        <v>366.8991038256451</v>
+        <v>361.1765397546195</v>
       </c>
       <c r="Q42">
-        <v>885.799103825645</v>
+        <v>880.0765397546195</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09980049011728322</v>
+        <v>0.1005495278497757</v>
       </c>
       <c r="T42">
-        <v>0.9890379406868541</v>
+        <v>1.002756829808641</v>
       </c>
       <c r="U42">
         <v>0.08028110587651874</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.602861493868312</v>
+        <v>2.539377067188597</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08335235642020974</v>
+        <v>0.08457807585410609</v>
       </c>
       <c r="C43">
-        <v>4409.952545696547</v>
+        <v>4068.179715949218</v>
       </c>
       <c r="D43">
-        <v>7723.438545696547</v>
+        <v>7479.311715949218</v>
       </c>
       <c r="E43">
-        <v>-1835.414</v>
+        <v>-1737.768</v>
       </c>
       <c r="F43">
-        <v>4003.486</v>
+        <v>4101.132</v>
       </c>
       <c r="G43">
         <v>690</v>
@@ -4941,45 +4941,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M43">
-        <v>321.4042834411605</v>
+        <v>345.237827105579</v>
       </c>
       <c r="N43">
-        <v>494.7623832255061</v>
+        <v>470.9288395610877</v>
       </c>
       <c r="O43">
-        <v>133.5858434708867</v>
+        <v>127.1507866814937</v>
       </c>
       <c r="P43">
-        <v>361.1765397546195</v>
+        <v>343.778052879594</v>
       </c>
       <c r="Q43">
-        <v>880.0765397546195</v>
+        <v>862.6780528795939</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1005495278497757</v>
+        <v>0.1013243944695956</v>
       </c>
       <c r="T43">
-        <v>1.002756829808641</v>
+        <v>1.016948784072559</v>
       </c>
       <c r="U43">
-        <v>0.08028110587651874</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V43">
         <v>0.27</v>
       </c>
       <c r="W43">
-        <v>0.05860520728985868</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.539377067188597</v>
+        <v>2.364070801595767</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08457807585410609</v>
+        <v>0.08463652528800245</v>
       </c>
       <c r="C44">
-        <v>4068.179715949218</v>
+        <v>3959.277262585028</v>
       </c>
       <c r="D44">
-        <v>7479.311715949218</v>
+        <v>7468.055262585027</v>
       </c>
       <c r="E44">
-        <v>-1737.768</v>
+        <v>-1640.122</v>
       </c>
       <c r="F44">
-        <v>4101.132</v>
+        <v>4198.777999999999</v>
       </c>
       <c r="G44">
         <v>690</v>
@@ -5023,28 +5023,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M44">
-        <v>345.237827105579</v>
+        <v>353.4577753699975</v>
       </c>
       <c r="N44">
-        <v>470.9288395610877</v>
+        <v>462.7088912966692</v>
       </c>
       <c r="O44">
-        <v>127.1507866814937</v>
+        <v>124.9314006501007</v>
       </c>
       <c r="P44">
-        <v>343.778052879594</v>
+        <v>337.7774906465685</v>
       </c>
       <c r="Q44">
-        <v>862.6780528795939</v>
+        <v>856.6774906465685</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1013243944695956</v>
+        <v>0.1021264493918653</v>
       </c>
       <c r="T44">
-        <v>1.016948784072558</v>
+        <v>1.031638701643982</v>
       </c>
       <c r="U44">
         <v>0.08418110587651872</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.364070801595767</v>
+        <v>2.309092410860981</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08463652528800245</v>
+        <v>0.08469497472189877</v>
       </c>
       <c r="C45">
-        <v>3959.277262585028</v>
+        <v>3850.408640497584</v>
       </c>
       <c r="D45">
-        <v>7468.055262585027</v>
+        <v>7456.832640497583</v>
       </c>
       <c r="E45">
-        <v>-1640.122</v>
+        <v>-1542.476000000001</v>
       </c>
       <c r="F45">
-        <v>4198.777999999999</v>
+        <v>4296.423999999999</v>
       </c>
       <c r="G45">
         <v>690</v>
@@ -5105,28 +5105,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M45">
-        <v>353.4577753699975</v>
+        <v>361.677723634416</v>
       </c>
       <c r="N45">
-        <v>462.7088912966692</v>
+        <v>454.4889430322506</v>
       </c>
       <c r="O45">
-        <v>124.9314006501007</v>
+        <v>122.7120146187077</v>
       </c>
       <c r="P45">
-        <v>337.7774906465685</v>
+        <v>331.7769284135429</v>
       </c>
       <c r="Q45">
-        <v>856.6774906465685</v>
+        <v>850.6769284135429</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1021264493918653</v>
+        <v>0.1029571491327874</v>
       </c>
       <c r="T45">
-        <v>1.031638701643982</v>
+        <v>1.04685325912867</v>
       </c>
       <c r="U45">
         <v>0.08418110587651872</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.309092410860981</v>
+        <v>2.256613037886869</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08469497472189877</v>
+        <v>0.08475342415579513</v>
       </c>
       <c r="C46">
-        <v>3850.408640497584</v>
+        <v>3741.573697395846</v>
       </c>
       <c r="D46">
-        <v>7456.832640497583</v>
+        <v>7445.643697395846</v>
       </c>
       <c r="E46">
-        <v>-1542.476000000001</v>
+        <v>-1444.83</v>
       </c>
       <c r="F46">
-        <v>4296.423999999999</v>
+        <v>4394.07</v>
       </c>
       <c r="G46">
         <v>690</v>
@@ -5187,28 +5187,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M46">
-        <v>361.677723634416</v>
+        <v>369.8976718988346</v>
       </c>
       <c r="N46">
-        <v>454.4889430322506</v>
+        <v>446.268994767832</v>
       </c>
       <c r="O46">
-        <v>122.7120146187077</v>
+        <v>120.4926285873146</v>
       </c>
       <c r="P46">
-        <v>331.7769284135429</v>
+        <v>325.7763661805174</v>
       </c>
       <c r="Q46">
-        <v>850.6769284135429</v>
+        <v>844.6763661805173</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1029571491327874</v>
+        <v>0.1038180561370159</v>
       </c>
       <c r="T46">
-        <v>1.04685325912867</v>
+        <v>1.062621073249166</v>
       </c>
       <c r="U46">
         <v>0.08418110587651872</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.256613037886869</v>
+        <v>2.206466081489382</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08475342415579513</v>
+        <v>0.08481187358969147</v>
       </c>
       <c r="C47">
-        <v>3741.573697395846</v>
+        <v>3632.772281901483</v>
       </c>
       <c r="D47">
-        <v>7445.643697395846</v>
+        <v>7434.488281901482</v>
       </c>
       <c r="E47">
-        <v>-1444.83</v>
+        <v>-1347.184</v>
       </c>
       <c r="F47">
-        <v>4394.07</v>
+        <v>4491.715999999999</v>
       </c>
       <c r="G47">
         <v>690</v>
@@ -5269,28 +5269,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M47">
-        <v>369.8976718988346</v>
+        <v>378.1176201632532</v>
       </c>
       <c r="N47">
-        <v>446.268994767832</v>
+        <v>438.0490465034135</v>
       </c>
       <c r="O47">
-        <v>120.4926285873146</v>
+        <v>118.2732425559216</v>
       </c>
       <c r="P47">
-        <v>325.7763661805174</v>
+        <v>319.7758039474919</v>
       </c>
       <c r="Q47">
-        <v>844.6763661805173</v>
+        <v>838.6758039474919</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1038180561370159</v>
+        <v>0.1047108485858453</v>
       </c>
       <c r="T47">
-        <v>1.062621073249166</v>
+        <v>1.078972880485235</v>
       </c>
       <c r="U47">
         <v>0.08418110587651872</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.206466081489382</v>
+        <v>2.158499427543961</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08481187358969147</v>
+        <v>0.08487032302358782</v>
       </c>
       <c r="C48">
-        <v>3632.772281901483</v>
+        <v>3524.004243541988</v>
       </c>
       <c r="D48">
-        <v>7434.488281901482</v>
+        <v>7423.366243541987</v>
       </c>
       <c r="E48">
-        <v>-1347.184</v>
+        <v>-1249.538</v>
       </c>
       <c r="F48">
-        <v>4491.715999999999</v>
+        <v>4589.361999999999</v>
       </c>
       <c r="G48">
         <v>690</v>
@@ -5351,28 +5351,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M48">
-        <v>378.1176201632532</v>
+        <v>386.3375684276717</v>
       </c>
       <c r="N48">
-        <v>438.0490465034135</v>
+        <v>429.829098238995</v>
       </c>
       <c r="O48">
-        <v>118.2732425559216</v>
+        <v>116.0538565245286</v>
       </c>
       <c r="P48">
-        <v>319.7758039474919</v>
+        <v>313.7752417144663</v>
       </c>
       <c r="Q48">
-        <v>838.6758039474919</v>
+        <v>832.6752417144663</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1047108485858453</v>
+        <v>0.1056373313157627</v>
       </c>
       <c r="T48">
-        <v>1.078972880485235</v>
+        <v>1.095941737050967</v>
       </c>
       <c r="U48">
         <v>0.08418110587651872</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.158499427543961</v>
+        <v>2.112573907808983</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08487032302358782</v>
+        <v>0.08492877245748416</v>
       </c>
       <c r="C49">
-        <v>3524.004243541988</v>
+        <v>3415.269432743958</v>
       </c>
       <c r="D49">
-        <v>7423.366243541987</v>
+        <v>7412.277432743957</v>
       </c>
       <c r="E49">
-        <v>-1249.538</v>
+        <v>-1151.892</v>
       </c>
       <c r="F49">
-        <v>4589.361999999999</v>
+        <v>4687.008</v>
       </c>
       <c r="G49">
         <v>690</v>
@@ -5433,28 +5433,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M49">
-        <v>386.3375684276717</v>
+        <v>394.5575166920902</v>
       </c>
       <c r="N49">
-        <v>429.829098238995</v>
+        <v>421.6091499745764</v>
       </c>
       <c r="O49">
-        <v>116.0538565245286</v>
+        <v>113.8344704931356</v>
       </c>
       <c r="P49">
-        <v>313.7752417144663</v>
+        <v>307.7746794814408</v>
       </c>
       <c r="Q49">
-        <v>832.6752417144663</v>
+        <v>826.6746794814408</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1056373313157627</v>
+        <v>0.1065994479968308</v>
       </c>
       <c r="T49">
-        <v>1.095941737050967</v>
+        <v>1.113563241946151</v>
       </c>
       <c r="U49">
         <v>0.08418110587651872</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.112573907808983</v>
+        <v>2.068561951396295</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08492877245748416</v>
+        <v>0.0849872218913805</v>
       </c>
       <c r="C50">
-        <v>3415.269432743959</v>
+        <v>3306.567700826361</v>
       </c>
       <c r="D50">
-        <v>7412.277432743957</v>
+        <v>7401.221700826361</v>
       </c>
       <c r="E50">
-        <v>-1151.892000000001</v>
+        <v>-1054.246</v>
       </c>
       <c r="F50">
-        <v>4687.007999999999</v>
+        <v>4784.654</v>
       </c>
       <c r="G50">
         <v>690</v>
@@ -5515,28 +5515,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M50">
-        <v>394.5575166920902</v>
+        <v>402.7774649565088</v>
       </c>
       <c r="N50">
-        <v>421.6091499745764</v>
+        <v>413.3892017101579</v>
       </c>
       <c r="O50">
-        <v>113.8344704931356</v>
+        <v>111.6150844617426</v>
       </c>
       <c r="P50">
-        <v>307.7746794814408</v>
+        <v>301.7741172484152</v>
       </c>
       <c r="Q50">
-        <v>826.6746794814408</v>
+        <v>820.6741172484152</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1065994479968308</v>
+        <v>0.107599294743823</v>
       </c>
       <c r="T50">
-        <v>1.113563241946151</v>
+        <v>1.131875786248989</v>
       </c>
       <c r="U50">
         <v>0.08418110587651872</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.068561951396296</v>
+        <v>2.0263464013678</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0849872218913805</v>
+        <v>0.09022867132527684</v>
       </c>
       <c r="C51">
-        <v>3306.567700826361</v>
+        <v>2335.766413108651</v>
       </c>
       <c r="D51">
-        <v>7401.221700826361</v>
+        <v>6528.066413108651</v>
       </c>
       <c r="E51">
-        <v>-1054.246</v>
+        <v>-956.6000000000004</v>
       </c>
       <c r="F51">
-        <v>4784.654</v>
+        <v>4882.299999999999</v>
       </c>
       <c r="G51">
         <v>690</v>
@@ -5597,45 +5597,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M51">
-        <v>402.7774649565088</v>
+        <v>480.3260732209273</v>
       </c>
       <c r="N51">
-        <v>413.3892017101579</v>
+        <v>335.8405934457393</v>
       </c>
       <c r="O51">
-        <v>111.6150844617426</v>
+        <v>90.67696023034962</v>
       </c>
       <c r="P51">
-        <v>301.7741172484152</v>
+        <v>245.1636332153897</v>
       </c>
       <c r="Q51">
-        <v>820.6741172484152</v>
+        <v>764.0636332153897</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.107599294743823</v>
+        <v>0.108639135360695</v>
       </c>
       <c r="T51">
-        <v>1.131875786248989</v>
+        <v>1.15092083232394</v>
       </c>
       <c r="U51">
-        <v>0.08418110587651872</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V51">
         <v>0.27</v>
       </c>
       <c r="W51">
-        <v>0.06145220728985867</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.0263464013678</v>
+        <v>1.699192927824404</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09022867132527684</v>
+        <v>0.0903907807591732</v>
       </c>
       <c r="C52">
-        <v>2335.766413108651</v>
+        <v>2214.387678838257</v>
       </c>
       <c r="D52">
-        <v>6528.066413108651</v>
+        <v>6504.333678838256</v>
       </c>
       <c r="E52">
-        <v>-956.6000000000004</v>
+        <v>-858.9540000000006</v>
       </c>
       <c r="F52">
-        <v>4882.299999999999</v>
+        <v>4979.945999999999</v>
       </c>
       <c r="G52">
         <v>690</v>
@@ -5679,28 +5679,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M52">
-        <v>480.3260732209273</v>
+        <v>489.9325946853459</v>
       </c>
       <c r="N52">
-        <v>335.8405934457393</v>
+        <v>326.2340719813208</v>
       </c>
       <c r="O52">
-        <v>90.67696023034962</v>
+        <v>88.08319943495661</v>
       </c>
       <c r="P52">
-        <v>245.1636332153897</v>
+        <v>238.1508725463642</v>
       </c>
       <c r="Q52">
-        <v>764.0636332153897</v>
+        <v>757.0508725463642</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.108639135360695</v>
+        <v>0.1097214184517251</v>
       </c>
       <c r="T52">
-        <v>1.15092083232394</v>
+        <v>1.170743227218277</v>
       </c>
       <c r="U52">
         <v>0.09838110587651873</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.699192927824404</v>
+        <v>1.66587541943569</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0903907807591732</v>
+        <v>0.09055289019306956</v>
       </c>
       <c r="C53">
-        <v>2214.387678838257</v>
+        <v>2093.180879837329</v>
       </c>
       <c r="D53">
-        <v>6504.333678838256</v>
+        <v>6480.772879837329</v>
       </c>
       <c r="E53">
-        <v>-858.9540000000006</v>
+        <v>-761.308</v>
       </c>
       <c r="F53">
-        <v>4979.945999999999</v>
+        <v>5077.592</v>
       </c>
       <c r="G53">
         <v>690</v>
@@ -5761,28 +5761,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M53">
-        <v>489.9325946853459</v>
+        <v>499.5391161497644</v>
       </c>
       <c r="N53">
-        <v>326.2340719813208</v>
+        <v>316.6275505169022</v>
       </c>
       <c r="O53">
-        <v>88.08319943495661</v>
+        <v>85.4894386395636</v>
       </c>
       <c r="P53">
-        <v>238.1508725463642</v>
+        <v>231.1381118773386</v>
       </c>
       <c r="Q53">
-        <v>757.0508725463642</v>
+        <v>750.0381118773386</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1097214184517251</v>
+        <v>0.110848796671548</v>
       </c>
       <c r="T53">
-        <v>1.170743227218277</v>
+        <v>1.191391555233212</v>
       </c>
       <c r="U53">
         <v>0.09838110587651873</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.66587541943569</v>
+        <v>1.633839353677312</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09055289019306956</v>
+        <v>0.09071499962696589</v>
       </c>
       <c r="C54">
-        <v>2093.180879837329</v>
+        <v>1972.144154434087</v>
       </c>
       <c r="D54">
-        <v>6480.772879837329</v>
+        <v>6457.382154434086</v>
       </c>
       <c r="E54">
-        <v>-761.308</v>
+        <v>-663.6620000000003</v>
       </c>
       <c r="F54">
-        <v>5077.592</v>
+        <v>5175.237999999999</v>
       </c>
       <c r="G54">
         <v>690</v>
@@ -5843,28 +5843,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M54">
-        <v>499.5391161497644</v>
+        <v>509.145637614183</v>
       </c>
       <c r="N54">
-        <v>316.6275505169022</v>
+        <v>307.0210290524836</v>
       </c>
       <c r="O54">
-        <v>85.4894386395636</v>
+        <v>82.89567784417059</v>
       </c>
       <c r="P54">
-        <v>231.1381118773386</v>
+        <v>224.125351208313</v>
       </c>
       <c r="Q54">
-        <v>750.0381118773386</v>
+        <v>743.0253512083131</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.110848796671548</v>
+        <v>0.11202414843264</v>
       </c>
       <c r="T54">
-        <v>1.191391555233212</v>
+        <v>1.212918535504101</v>
       </c>
       <c r="U54">
         <v>0.09838110587651873</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.633839353677312</v>
+        <v>1.603012196060758</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09071499962696589</v>
+        <v>0.09087710906086224</v>
       </c>
       <c r="C55">
-        <v>1972.144154434087</v>
+        <v>1851.275667737027</v>
       </c>
       <c r="D55">
-        <v>6457.382154434086</v>
+        <v>6434.159667737027</v>
       </c>
       <c r="E55">
-        <v>-663.6620000000003</v>
+        <v>-566.0159999999996</v>
       </c>
       <c r="F55">
-        <v>5175.237999999999</v>
+        <v>5272.884</v>
       </c>
       <c r="G55">
         <v>690</v>
@@ -5925,28 +5925,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M55">
-        <v>509.145637614183</v>
+        <v>518.7521590786016</v>
       </c>
       <c r="N55">
-        <v>307.0210290524836</v>
+        <v>297.414507588065</v>
       </c>
       <c r="O55">
-        <v>82.89567784417059</v>
+        <v>80.30191704877755</v>
       </c>
       <c r="P55">
-        <v>224.125351208313</v>
+        <v>217.1125905392875</v>
       </c>
       <c r="Q55">
-        <v>743.0253512083131</v>
+        <v>736.0125905392874</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.11202414843264</v>
+        <v>0.1132506024442143</v>
       </c>
       <c r="T55">
-        <v>1.212918535504101</v>
+        <v>1.235381471438941</v>
       </c>
       <c r="U55">
         <v>0.09838110587651873</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.603012196060758</v>
+        <v>1.573326785022596</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09087710906086224</v>
+        <v>0.09103921849475859</v>
       </c>
       <c r="C56">
-        <v>1851.275667737027</v>
+        <v>1730.57361115514</v>
       </c>
       <c r="D56">
-        <v>6434.159667737027</v>
+        <v>6411.103611155139</v>
       </c>
       <c r="E56">
-        <v>-566.0159999999996</v>
+        <v>-468.3699999999999</v>
       </c>
       <c r="F56">
-        <v>5272.884</v>
+        <v>5370.53</v>
       </c>
       <c r="G56">
         <v>690</v>
@@ -6007,28 +6007,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M56">
-        <v>518.7521590786016</v>
+        <v>528.3586805430201</v>
       </c>
       <c r="N56">
-        <v>297.414507588065</v>
+        <v>287.8079861236465</v>
       </c>
       <c r="O56">
-        <v>80.30191704877755</v>
+        <v>77.70815625338456</v>
       </c>
       <c r="P56">
-        <v>217.1125905392875</v>
+        <v>210.0998298702619</v>
       </c>
       <c r="Q56">
-        <v>736.0125905392874</v>
+        <v>728.9998298702619</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1132506024442143</v>
+        <v>0.1145315655229696</v>
       </c>
       <c r="T56">
-        <v>1.235381471438941</v>
+        <v>1.258842760081998</v>
       </c>
       <c r="U56">
         <v>0.09838110587651873</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.573326785022596</v>
+        <v>1.544720843476731</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09103921849475859</v>
+        <v>0.09120132792865493</v>
       </c>
       <c r="C57">
-        <v>1730.57361115514</v>
+        <v>1610.036201928336</v>
       </c>
       <c r="D57">
-        <v>6411.103611155139</v>
+        <v>6388.212201928335</v>
       </c>
       <c r="E57">
-        <v>-468.3699999999999</v>
+        <v>-370.7240000000002</v>
       </c>
       <c r="F57">
-        <v>5370.53</v>
+        <v>5468.175999999999</v>
       </c>
       <c r="G57">
         <v>690</v>
@@ -6089,28 +6089,28 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M57">
-        <v>528.3586805430201</v>
+        <v>537.9652020074386</v>
       </c>
       <c r="N57">
-        <v>287.8079861236465</v>
+        <v>278.201464659228</v>
       </c>
       <c r="O57">
-        <v>77.70815625338456</v>
+        <v>75.11439545799156</v>
       </c>
       <c r="P57">
-        <v>210.0998298702619</v>
+        <v>203.0870692012364</v>
       </c>
       <c r="Q57">
-        <v>728.9998298702619</v>
+        <v>721.9870692012364</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1145315655229696</v>
+        <v>0.1158707541962138</v>
       </c>
       <c r="T57">
-        <v>1.258842760081998</v>
+        <v>1.283370470936101</v>
       </c>
       <c r="U57">
         <v>0.09838110587651873</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.544720843476731</v>
+        <v>1.517136542700361</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09120132792865493</v>
+        <v>0.1166202593473234</v>
       </c>
       <c r="C58">
-        <v>1610.036201928336</v>
+        <v>-780.4781008033824</v>
       </c>
       <c r="D58">
-        <v>6388.212201928335</v>
+        <v>4095.343899196618</v>
       </c>
       <c r="E58">
-        <v>-370.7240000000002</v>
+        <v>-273.0779999999995</v>
       </c>
       <c r="F58">
-        <v>5468.175999999999</v>
+        <v>5565.822</v>
       </c>
       <c r="G58">
         <v>690</v>
@@ -6171,45 +6171,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M58">
-        <v>537.9652020074386</v>
+        <v>863.7104130718573</v>
       </c>
       <c r="N58">
-        <v>278.201464659228</v>
+        <v>-47.54374640519063</v>
       </c>
       <c r="O58">
-        <v>75.11439545799156</v>
+        <v>-12.83681152940147</v>
       </c>
       <c r="P58">
-        <v>203.0870692012364</v>
+        <v>-34.70693487578916</v>
       </c>
       <c r="Q58">
-        <v>721.9870692012364</v>
+        <v>484.1930651242108</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1158707541962138</v>
+        <v>0.1179878458330059</v>
       </c>
       <c r="T58">
-        <v>1.283370470936101</v>
+        <v>1.322145747755821</v>
       </c>
       <c r="U58">
-        <v>0.09838110587651873</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V58">
-        <v>0.27</v>
+        <v>0.2551375978162099</v>
       </c>
       <c r="W58">
-        <v>0.07181820728985867</v>
+        <v>0.1155885712967208</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.517136542700361</v>
+        <v>0.9449540659859623</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1166202593473234</v>
+        <v>0.1177140704060886</v>
       </c>
       <c r="C59">
-        <v>-780.4781008033824</v>
+        <v>-940.4141703418254</v>
       </c>
       <c r="D59">
-        <v>4095.343899196618</v>
+        <v>4033.053829658174</v>
       </c>
       <c r="E59">
-        <v>-273.0779999999995</v>
+        <v>-175.4319999999998</v>
       </c>
       <c r="F59">
-        <v>5565.822</v>
+        <v>5663.468</v>
       </c>
       <c r="G59">
         <v>690</v>
@@ -6253,37 +6253,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M59">
-        <v>863.7104130718573</v>
+        <v>878.8632273362757</v>
       </c>
       <c r="N59">
-        <v>-47.54374640519063</v>
+        <v>-62.69656066960908</v>
       </c>
       <c r="O59">
-        <v>-12.83681152940147</v>
+        <v>-16.92807138079445</v>
       </c>
       <c r="P59">
-        <v>-34.70693487578916</v>
+        <v>-45.76848928881464</v>
       </c>
       <c r="Q59">
-        <v>484.1930651242108</v>
+        <v>473.1315107111853</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1179878458330059</v>
+        <v>0.1197066040671251</v>
       </c>
       <c r="T59">
-        <v>1.322145747755821</v>
+        <v>1.353625408416674</v>
       </c>
       <c r="U59">
         <v>0.1551811058765187</v>
       </c>
       <c r="V59">
-        <v>0.2551375978162099</v>
+        <v>0.2507386737159304</v>
       </c>
       <c r="W59">
-        <v>0.1155885712967208</v>
+        <v>0.1162712012032691</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9449540659859623</v>
+        <v>0.9286617545034459</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1177140704060886</v>
+        <v>0.1188078814648537</v>
       </c>
       <c r="C60">
-        <v>-940.4141703418236</v>
+        <v>-1098.483768328282</v>
       </c>
       <c r="D60">
-        <v>4033.053829658175</v>
+        <v>3972.630231671717</v>
       </c>
       <c r="E60">
-        <v>-175.4320000000007</v>
+        <v>-77.78600000000097</v>
       </c>
       <c r="F60">
-        <v>5663.467999999999</v>
+        <v>5761.113999999999</v>
       </c>
       <c r="G60">
         <v>690</v>
@@ -6335,37 +6335,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M60">
-        <v>878.8632273362756</v>
+        <v>894.0160416006942</v>
       </c>
       <c r="N60">
-        <v>-62.69656066960897</v>
+        <v>-77.84937493402754</v>
       </c>
       <c r="O60">
-        <v>-16.92807138079442</v>
+        <v>-21.01933123218744</v>
       </c>
       <c r="P60">
-        <v>-45.76848928881455</v>
+        <v>-56.8300437018401</v>
       </c>
       <c r="Q60">
-        <v>473.1315107111855</v>
+        <v>462.0699562981599</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.119706604067125</v>
+        <v>0.1215092041663232</v>
       </c>
       <c r="T60">
-        <v>1.353625408416674</v>
+        <v>1.386640662280495</v>
       </c>
       <c r="U60">
         <v>0.1551811058765187</v>
       </c>
       <c r="V60">
-        <v>0.2507386737159304</v>
+        <v>0.2464888656868469</v>
       </c>
       <c r="W60">
-        <v>0.116271201203269</v>
+        <v>0.1169306911129851</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.928661754503446</v>
+        <v>0.9129217247660995</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1188078814648537</v>
+        <v>0.119901692523619</v>
       </c>
       <c r="C61">
-        <v>-1098.483768328282</v>
+        <v>-1254.769547418383</v>
       </c>
       <c r="D61">
-        <v>3972.630231671717</v>
+        <v>3913.990452581616</v>
       </c>
       <c r="E61">
-        <v>-77.78600000000097</v>
+        <v>19.85999999999967</v>
       </c>
       <c r="F61">
-        <v>5761.113999999999</v>
+        <v>5858.759999999999</v>
       </c>
       <c r="G61">
         <v>690</v>
@@ -6417,37 +6417,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M61">
-        <v>894.0160416006942</v>
+        <v>909.1688558651127</v>
       </c>
       <c r="N61">
-        <v>-77.84937493402754</v>
+        <v>-93.0021891984461</v>
       </c>
       <c r="O61">
-        <v>-21.01933123218744</v>
+        <v>-25.11059108358045</v>
       </c>
       <c r="P61">
-        <v>-56.8300437018401</v>
+        <v>-67.89159811486566</v>
       </c>
       <c r="Q61">
-        <v>462.0699562981599</v>
+        <v>451.0084018851343</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1215092041663232</v>
+        <v>0.1234019342704813</v>
       </c>
       <c r="T61">
-        <v>1.386640662280495</v>
+        <v>1.421306678837507</v>
       </c>
       <c r="U61">
         <v>0.1551811058765187</v>
       </c>
       <c r="V61">
-        <v>0.2464888656868469</v>
+        <v>0.2423807179253994</v>
       </c>
       <c r="W61">
-        <v>0.1169306911129851</v>
+        <v>0.1175681980257107</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.9129217247660995</v>
+        <v>0.8977063626866644</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.119901692523619</v>
+        <v>0.1209955035823841</v>
       </c>
       <c r="C62">
-        <v>-1254.769547418383</v>
+        <v>-1409.349351129726</v>
       </c>
       <c r="D62">
-        <v>3913.990452581616</v>
+        <v>3857.056648870273</v>
       </c>
       <c r="E62">
-        <v>19.85999999999967</v>
+        <v>117.5059999999994</v>
       </c>
       <c r="F62">
-        <v>5858.759999999999</v>
+        <v>5956.405999999999</v>
       </c>
       <c r="G62">
         <v>690</v>
@@ -6499,37 +6499,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M62">
-        <v>909.1688558651127</v>
+        <v>924.3216701295313</v>
       </c>
       <c r="N62">
-        <v>-93.0021891984461</v>
+        <v>-108.1550034628647</v>
       </c>
       <c r="O62">
-        <v>-25.11059108358045</v>
+        <v>-29.20185093497346</v>
       </c>
       <c r="P62">
-        <v>-67.89159811486566</v>
+        <v>-78.95315252789121</v>
       </c>
       <c r="Q62">
-        <v>451.0084018851343</v>
+        <v>439.9468474721087</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1234019342704813</v>
+        <v>0.1253917274569039</v>
       </c>
       <c r="T62">
-        <v>1.421306678837507</v>
+        <v>1.457750439833341</v>
       </c>
       <c r="U62">
         <v>0.1551811058765187</v>
       </c>
       <c r="V62">
-        <v>0.2423807179253994</v>
+        <v>0.2384072635331798</v>
       </c>
       <c r="W62">
-        <v>0.1175681980257107</v>
+        <v>0.1181848030724453</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8977063626866644</v>
+        <v>0.8829898649377027</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1209955035823841</v>
+        <v>0.1220893146411493</v>
       </c>
       <c r="C63">
-        <v>-1409.349351129726</v>
+        <v>-1562.296558601086</v>
       </c>
       <c r="D63">
-        <v>3857.056648870273</v>
+        <v>3801.755441398913</v>
       </c>
       <c r="E63">
-        <v>117.5059999999994</v>
+        <v>215.1519999999991</v>
       </c>
       <c r="F63">
-        <v>5956.405999999999</v>
+        <v>6054.051999999999</v>
       </c>
       <c r="G63">
         <v>690</v>
@@ -6581,37 +6581,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M63">
-        <v>924.3216701295313</v>
+        <v>939.4744843939498</v>
       </c>
       <c r="N63">
-        <v>-108.1550034628647</v>
+        <v>-123.3078177272831</v>
       </c>
       <c r="O63">
-        <v>-29.20185093497346</v>
+        <v>-33.29311078636645</v>
       </c>
       <c r="P63">
-        <v>-78.95315252789121</v>
+        <v>-90.01470694091668</v>
       </c>
       <c r="Q63">
-        <v>439.9468474721087</v>
+        <v>428.8852930590833</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1253917274569039</v>
+        <v>0.1274862466005066</v>
       </c>
       <c r="T63">
-        <v>1.457750439833341</v>
+        <v>1.496112293513165</v>
       </c>
       <c r="U63">
         <v>0.1551811058765187</v>
       </c>
       <c r="V63">
-        <v>0.2384072635331798</v>
+        <v>0.2345619850890962</v>
       </c>
       <c r="W63">
-        <v>0.1181848030724453</v>
+        <v>0.1187815176338013</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8829898649377027</v>
+        <v>0.8687480929225786</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1220893146411493</v>
+        <v>0.1231831256999145</v>
       </c>
       <c r="C64">
-        <v>-1562.296558601086</v>
+        <v>-1713.680400112539</v>
       </c>
       <c r="D64">
-        <v>3801.755441398913</v>
+        <v>3748.01759988746</v>
       </c>
       <c r="E64">
-        <v>215.1519999999991</v>
+        <v>312.7979999999998</v>
       </c>
       <c r="F64">
-        <v>6054.051999999999</v>
+        <v>6151.697999999999</v>
       </c>
       <c r="G64">
         <v>690</v>
@@ -6663,37 +6663,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M64">
-        <v>939.4744843939498</v>
+        <v>954.6272986583684</v>
       </c>
       <c r="N64">
-        <v>-123.3078177272831</v>
+        <v>-138.4606319917018</v>
       </c>
       <c r="O64">
-        <v>-33.29311078636645</v>
+        <v>-37.38437063775949</v>
       </c>
       <c r="P64">
-        <v>-90.01470694091668</v>
+        <v>-101.0762613539423</v>
       </c>
       <c r="Q64">
-        <v>428.8852930590833</v>
+        <v>417.8237386460577</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1274862466005066</v>
+        <v>0.1296939829951149</v>
       </c>
       <c r="T64">
-        <v>1.496112293513165</v>
+        <v>1.536547760905413</v>
       </c>
       <c r="U64">
         <v>0.1551811058765187</v>
       </c>
       <c r="V64">
-        <v>0.2345619850890962</v>
+        <v>0.2308387789765708</v>
       </c>
       <c r="W64">
-        <v>0.1187815176338013</v>
+        <v>0.1193592888757492</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8687480929225786</v>
+        <v>0.8549584406539661</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1231831256999145</v>
+        <v>0.1242769367586797</v>
       </c>
       <c r="C65">
-        <v>-1713.680400112539</v>
+        <v>-1863.566246219301</v>
       </c>
       <c r="D65">
-        <v>3748.01759988746</v>
+        <v>3695.777753780697</v>
       </c>
       <c r="E65">
-        <v>312.7979999999998</v>
+        <v>410.4439999999995</v>
       </c>
       <c r="F65">
-        <v>6151.697999999999</v>
+        <v>6249.343999999999</v>
       </c>
       <c r="G65">
         <v>690</v>
@@ -6745,37 +6745,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M65">
-        <v>954.6272986583684</v>
+        <v>969.780112922787</v>
       </c>
       <c r="N65">
-        <v>-138.4606319917018</v>
+        <v>-153.6134462561204</v>
       </c>
       <c r="O65">
-        <v>-37.38437063775949</v>
+        <v>-41.4756304891525</v>
       </c>
       <c r="P65">
-        <v>-101.0762613539423</v>
+        <v>-112.1378157669679</v>
       </c>
       <c r="Q65">
-        <v>417.8237386460577</v>
+        <v>406.7621842330321</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1296939829951149</v>
+        <v>0.1320243714116459</v>
       </c>
       <c r="T65">
-        <v>1.536547760905413</v>
+        <v>1.579229643152786</v>
       </c>
       <c r="U65">
         <v>0.1551811058765187</v>
       </c>
       <c r="V65">
-        <v>0.2308387789765708</v>
+        <v>0.2272319230550619</v>
       </c>
       <c r="W65">
-        <v>0.1193592888757492</v>
+        <v>0.1199190047663862</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8549584406539661</v>
+        <v>0.8415997150187479</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1242769367586797</v>
+        <v>0.1253707478174449</v>
       </c>
       <c r="C66">
-        <v>-1863.566246219301</v>
+        <v>-2012.01587303827</v>
       </c>
       <c r="D66">
-        <v>3695.777753780697</v>
+        <v>3644.974126961729</v>
       </c>
       <c r="E66">
-        <v>410.4439999999995</v>
+        <v>508.0899999999992</v>
       </c>
       <c r="F66">
-        <v>6249.343999999999</v>
+        <v>6346.989999999999</v>
       </c>
       <c r="G66">
         <v>690</v>
@@ -6827,37 +6827,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M66">
-        <v>969.780112922787</v>
+        <v>984.9329271872055</v>
       </c>
       <c r="N66">
-        <v>-153.6134462561204</v>
+        <v>-168.7662605205388</v>
       </c>
       <c r="O66">
-        <v>-41.4756304891525</v>
+        <v>-45.56689034054548</v>
       </c>
       <c r="P66">
-        <v>-112.1378157669679</v>
+        <v>-123.1993701799933</v>
       </c>
       <c r="Q66">
-        <v>406.7621842330321</v>
+        <v>395.7006298200066</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1320243714116459</v>
+        <v>0.1344879248805501</v>
       </c>
       <c r="T66">
-        <v>1.579229643152786</v>
+        <v>1.624350490100009</v>
       </c>
       <c r="U66">
         <v>0.1551811058765187</v>
       </c>
       <c r="V66">
-        <v>0.2272319230550619</v>
+        <v>0.2237360473157533</v>
       </c>
       <c r="W66">
-        <v>0.1199190047663862</v>
+        <v>0.120461498629619</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8415997150187479</v>
+        <v>0.8286520270953825</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1253707478174449</v>
+        <v>0.1264645588762101</v>
       </c>
       <c r="C67">
-        <v>-2012.01587303827</v>
+        <v>-2159.087705950865</v>
       </c>
       <c r="D67">
-        <v>3644.974126961729</v>
+        <v>3595.548294049135</v>
       </c>
       <c r="E67">
-        <v>508.0899999999992</v>
+        <v>605.7359999999999</v>
       </c>
       <c r="F67">
-        <v>6346.989999999999</v>
+        <v>6444.636</v>
       </c>
       <c r="G67">
         <v>690</v>
@@ -6909,37 +6909,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M67">
-        <v>984.9329271872055</v>
+        <v>1000.085741451624</v>
       </c>
       <c r="N67">
-        <v>-168.7662605205388</v>
+        <v>-183.9190747849575</v>
       </c>
       <c r="O67">
-        <v>-45.56689034054548</v>
+        <v>-49.65815019193853</v>
       </c>
       <c r="P67">
-        <v>-123.1993701799933</v>
+        <v>-134.260924593019</v>
       </c>
       <c r="Q67">
-        <v>395.7006298200066</v>
+        <v>384.639075406981</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1344879248805501</v>
+        <v>0.1370963932593898</v>
       </c>
       <c r="T67">
-        <v>1.624350490100009</v>
+        <v>1.672125504514715</v>
       </c>
       <c r="U67">
         <v>0.1551811058765187</v>
       </c>
       <c r="V67">
-        <v>0.2237360473157533</v>
+        <v>0.2203461072049085</v>
       </c>
       <c r="W67">
-        <v>0.120461498629619</v>
+        <v>0.1209875532848751</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8286520270953825</v>
+        <v>0.816096693351513</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1264645588762101</v>
+        <v>0.1275583699349753</v>
       </c>
       <c r="C68">
-        <v>-2159.087705950865</v>
+        <v>-2304.837043743475</v>
       </c>
       <c r="D68">
-        <v>3595.548294049135</v>
+        <v>3547.444956256525</v>
       </c>
       <c r="E68">
-        <v>605.7359999999999</v>
+        <v>703.3819999999996</v>
       </c>
       <c r="F68">
-        <v>6444.636</v>
+        <v>6542.281999999999</v>
       </c>
       <c r="G68">
         <v>690</v>
@@ -6991,37 +6991,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M68">
-        <v>1000.085741451624</v>
+        <v>1015.238555716043</v>
       </c>
       <c r="N68">
-        <v>-183.9190747849575</v>
+        <v>-199.071889049376</v>
       </c>
       <c r="O68">
-        <v>-49.65815019193853</v>
+        <v>-53.74941004333151</v>
       </c>
       <c r="P68">
-        <v>-134.260924593019</v>
+        <v>-145.3224790060444</v>
       </c>
       <c r="Q68">
-        <v>384.639075406981</v>
+        <v>373.5775209939555</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1370963932593898</v>
+        <v>0.1398629506308865</v>
       </c>
       <c r="T68">
-        <v>1.672125504514715</v>
+        <v>1.722795974348494</v>
       </c>
       <c r="U68">
         <v>0.1551811058765187</v>
       </c>
       <c r="V68">
-        <v>0.2203461072049085</v>
+        <v>0.2170573593361786</v>
       </c>
       <c r="W68">
-        <v>0.1209875532848751</v>
+        <v>0.1214979048160936</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.816096693351513</v>
+        <v>0.8039161456895503</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1275583699349753</v>
+        <v>0.1667358366576072</v>
       </c>
       <c r="C69">
-        <v>-2304.837043743475</v>
+        <v>-3551.686708804209</v>
       </c>
       <c r="D69">
-        <v>3547.444956256525</v>
+        <v>2398.241291195791</v>
       </c>
       <c r="E69">
-        <v>703.3819999999996</v>
+        <v>801.0280000000002</v>
       </c>
       <c r="F69">
-        <v>6542.281999999999</v>
+        <v>6639.928</v>
       </c>
       <c r="G69">
         <v>690</v>
@@ -7073,45 +7073,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M69">
-        <v>1015.238555716043</v>
+        <v>1388.947481980461</v>
       </c>
       <c r="N69">
-        <v>-199.071889049376</v>
+        <v>-572.7808153137945</v>
       </c>
       <c r="O69">
-        <v>-53.74941004333151</v>
+        <v>-154.6508201347245</v>
       </c>
       <c r="P69">
-        <v>-145.3224790060444</v>
+        <v>-418.12999517907</v>
       </c>
       <c r="Q69">
-        <v>373.5775209939555</v>
+        <v>100.77000482093</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1398629506308865</v>
+        <v>0.1470638417876852</v>
       </c>
       <c r="T69">
-        <v>1.722795974348494</v>
+        <v>1.854682824733783</v>
       </c>
       <c r="U69">
-        <v>0.1551811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V69">
-        <v>0.2170573593361786</v>
+        <v>0.1586561067707094</v>
       </c>
       <c r="W69">
-        <v>0.1214979048160936</v>
+        <v>0.1759932460081587</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.8039161456895503</v>
+        <v>0.5876152102618866</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1667358366576072</v>
+        <v>0.1683696477163724</v>
       </c>
       <c r="C70">
-        <v>-3551.686708804209</v>
+        <v>-3681.300436672775</v>
       </c>
       <c r="D70">
-        <v>2398.241291195791</v>
+        <v>2366.273563327225</v>
       </c>
       <c r="E70">
-        <v>801.0280000000002</v>
+        <v>898.674</v>
       </c>
       <c r="F70">
-        <v>6639.928</v>
+        <v>6737.574</v>
       </c>
       <c r="G70">
         <v>690</v>
@@ -7155,37 +7155,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M70">
-        <v>1388.947481980461</v>
+        <v>1409.37318024488</v>
       </c>
       <c r="N70">
-        <v>-572.7808153137945</v>
+        <v>-593.206513578213</v>
       </c>
       <c r="O70">
-        <v>-154.6508201347245</v>
+        <v>-160.1657586661175</v>
       </c>
       <c r="P70">
-        <v>-418.12999517907</v>
+        <v>-433.0407549120955</v>
       </c>
       <c r="Q70">
-        <v>100.77000482093</v>
+        <v>85.85924508790447</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1470638417876852</v>
+        <v>0.1503304173292234</v>
       </c>
       <c r="T70">
-        <v>1.854682824733783</v>
+        <v>1.914511302951002</v>
       </c>
       <c r="U70">
         <v>0.2091811058765187</v>
       </c>
       <c r="V70">
-        <v>0.1586561067707094</v>
+        <v>0.1563567429044672</v>
       </c>
       <c r="W70">
-        <v>0.1759932460081587</v>
+        <v>0.1764742294845117</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5876152102618866</v>
+        <v>0.579099047794323</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1683696477163724</v>
+        <v>0.1700034587751376</v>
       </c>
       <c r="C71">
-        <v>-3681.300436672775</v>
+        <v>-3810.073137603278</v>
       </c>
       <c r="D71">
-        <v>2366.273563327225</v>
+        <v>2335.146862396722</v>
       </c>
       <c r="E71">
-        <v>898.674</v>
+        <v>996.3199999999997</v>
       </c>
       <c r="F71">
-        <v>6737.574</v>
+        <v>6835.219999999999</v>
       </c>
       <c r="G71">
         <v>690</v>
@@ -7237,37 +7237,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M71">
-        <v>1409.37318024488</v>
+        <v>1429.798878509298</v>
       </c>
       <c r="N71">
-        <v>-593.206513578213</v>
+        <v>-613.6322118426316</v>
       </c>
       <c r="O71">
-        <v>-160.1657586661175</v>
+        <v>-165.6806971975105</v>
       </c>
       <c r="P71">
-        <v>-433.0407549120955</v>
+        <v>-447.9515146451211</v>
       </c>
       <c r="Q71">
-        <v>85.85924508790447</v>
+        <v>70.94848535487893</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1503304173292234</v>
+        <v>0.1538147645735309</v>
       </c>
       <c r="T71">
-        <v>1.914511302951002</v>
+        <v>1.978328346382702</v>
       </c>
       <c r="U71">
         <v>0.2091811058765187</v>
       </c>
       <c r="V71">
-        <v>0.1563567429044672</v>
+        <v>0.1541230751486891</v>
       </c>
       <c r="W71">
-        <v>0.1764742294845117</v>
+        <v>0.1769414705758262</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.579099047794323</v>
+        <v>0.5708262042544041</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1700034587751376</v>
+        <v>0.1716372698339027</v>
       </c>
       <c r="C72">
-        <v>-3810.073137603278</v>
+        <v>-3938.037570072929</v>
       </c>
       <c r="D72">
-        <v>2335.146862396722</v>
+        <v>2304.828429927071</v>
       </c>
       <c r="E72">
-        <v>996.3199999999997</v>
+        <v>1093.966</v>
       </c>
       <c r="F72">
-        <v>6835.219999999999</v>
+        <v>6932.866</v>
       </c>
       <c r="G72">
         <v>690</v>
@@ -7319,37 +7319,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M72">
-        <v>1429.798878509298</v>
+        <v>1450.224576773717</v>
       </c>
       <c r="N72">
-        <v>-613.6322118426316</v>
+        <v>-634.0579101070501</v>
       </c>
       <c r="O72">
-        <v>-165.6806971975105</v>
+        <v>-171.1956357289035</v>
       </c>
       <c r="P72">
-        <v>-447.9515146451211</v>
+        <v>-462.8622743781466</v>
       </c>
       <c r="Q72">
-        <v>70.94848535487893</v>
+        <v>56.03772562185338</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1538147645735309</v>
+        <v>0.1575394116277906</v>
       </c>
       <c r="T72">
-        <v>1.978328346382702</v>
+        <v>2.046546565223485</v>
       </c>
       <c r="U72">
         <v>0.2091811058765187</v>
       </c>
       <c r="V72">
-        <v>0.1541230751486891</v>
+        <v>0.1519523276113836</v>
       </c>
       <c r="W72">
-        <v>0.1769414705758262</v>
+        <v>0.1773955499462584</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5708262042544041</v>
+        <v>0.5627863985606801</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1716372698339027</v>
+        <v>0.1732710808926679</v>
       </c>
       <c r="C73">
-        <v>-3938.037570072927</v>
+        <v>-4065.224813082721</v>
       </c>
       <c r="D73">
-        <v>2304.828429927071</v>
+        <v>2275.287186917278</v>
       </c>
       <c r="E73">
-        <v>1093.965999999999</v>
+        <v>1191.611999999999</v>
       </c>
       <c r="F73">
-        <v>6932.865999999998</v>
+        <v>7030.511999999999</v>
       </c>
       <c r="G73">
         <v>690</v>
@@ -7401,37 +7401,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M73">
-        <v>1450.224576773717</v>
+        <v>1470.650275038135</v>
       </c>
       <c r="N73">
-        <v>-634.0579101070499</v>
+        <v>-654.4836083714684</v>
       </c>
       <c r="O73">
-        <v>-171.1956357289035</v>
+        <v>-176.7105742602965</v>
       </c>
       <c r="P73">
-        <v>-462.8622743781464</v>
+        <v>-477.773034111172</v>
       </c>
       <c r="Q73">
-        <v>56.03772562185355</v>
+        <v>41.12696588882801</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1575394116277905</v>
+        <v>0.1615301049002116</v>
       </c>
       <c r="T73">
-        <v>2.046546565223484</v>
+        <v>2.119637513981465</v>
       </c>
       <c r="U73">
         <v>0.2091811058765187</v>
       </c>
       <c r="V73">
-        <v>0.1519523276113837</v>
+        <v>0.1498418786167811</v>
       </c>
       <c r="W73">
-        <v>0.1773955499462584</v>
+        <v>0.1778370160008454</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5627863985606802</v>
+        <v>0.554969920802893</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1732710808926679</v>
+        <v>0.1749048919514331</v>
       </c>
       <c r="C74">
-        <v>-4065.224813082721</v>
+        <v>-4191.664372425543</v>
       </c>
       <c r="D74">
-        <v>2275.287186917278</v>
+        <v>2246.493627574456</v>
       </c>
       <c r="E74">
-        <v>1191.611999999999</v>
+        <v>1289.257999999999</v>
       </c>
       <c r="F74">
-        <v>7030.511999999999</v>
+        <v>7128.157999999999</v>
       </c>
       <c r="G74">
         <v>690</v>
@@ -7483,37 +7483,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M74">
-        <v>1470.650275038135</v>
+        <v>1491.075973302554</v>
       </c>
       <c r="N74">
-        <v>-654.4836083714684</v>
+        <v>-674.909306635887</v>
       </c>
       <c r="O74">
-        <v>-176.7105742602965</v>
+        <v>-182.2255127916895</v>
       </c>
       <c r="P74">
-        <v>-477.773034111172</v>
+        <v>-492.6837938441975</v>
       </c>
       <c r="Q74">
-        <v>41.12696588882801</v>
+        <v>26.21620615580252</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1615301049002116</v>
+        <v>0.1658164050817009</v>
       </c>
       <c r="T74">
-        <v>2.119637513981465</v>
+        <v>2.19814260709189</v>
       </c>
       <c r="U74">
         <v>0.2091811058765187</v>
       </c>
       <c r="V74">
-        <v>0.1498418786167811</v>
+        <v>0.1477892501425787</v>
       </c>
       <c r="W74">
-        <v>0.1778370160008454</v>
+        <v>0.1782663870950327</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.554969920802893</v>
+        <v>0.5473675931206616</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1749048919514331</v>
+        <v>0.1765387030101983</v>
       </c>
       <c r="C75">
-        <v>-4191.664372425543</v>
+        <v>-4317.384278986254</v>
       </c>
       <c r="D75">
-        <v>2246.493627574456</v>
+        <v>2218.419721013746</v>
       </c>
       <c r="E75">
-        <v>1289.257999999999</v>
+        <v>1386.904</v>
       </c>
       <c r="F75">
-        <v>7128.157999999999</v>
+        <v>7225.803999999999</v>
       </c>
       <c r="G75">
         <v>690</v>
@@ -7565,37 +7565,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M75">
-        <v>1491.075973302554</v>
+        <v>1511.501671566972</v>
       </c>
       <c r="N75">
-        <v>-674.909306635887</v>
+        <v>-695.3350049003058</v>
       </c>
       <c r="O75">
-        <v>-182.2255127916895</v>
+        <v>-187.7404513230826</v>
       </c>
       <c r="P75">
-        <v>-492.6837938441975</v>
+        <v>-507.5945535772232</v>
       </c>
       <c r="Q75">
-        <v>26.21620615580252</v>
+        <v>11.30544642277675</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1658164050817009</v>
+        <v>0.1704324206617663</v>
       </c>
       <c r="T75">
-        <v>2.19814260709189</v>
+        <v>2.282686553518501</v>
       </c>
       <c r="U75">
         <v>0.2091811058765187</v>
       </c>
       <c r="V75">
-        <v>0.1477892501425787</v>
+        <v>0.1457920981136248</v>
       </c>
       <c r="W75">
-        <v>0.1782663870950327</v>
+        <v>0.1786841535650528</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5473675931206616</v>
+        <v>0.5399707337541662</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1765387030101983</v>
+        <v>0.1781725140689635</v>
       </c>
       <c r="C76">
-        <v>-4317.384278986254</v>
+        <v>-4442.411179762125</v>
       </c>
       <c r="D76">
-        <v>2218.419721013746</v>
+        <v>2191.038820237874</v>
       </c>
       <c r="E76">
-        <v>1386.904</v>
+        <v>1484.549999999999</v>
       </c>
       <c r="F76">
-        <v>7225.803999999999</v>
+        <v>7323.449999999999</v>
       </c>
       <c r="G76">
         <v>690</v>
@@ -7647,37 +7647,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M76">
-        <v>1511.501671566972</v>
+        <v>1531.927369831391</v>
       </c>
       <c r="N76">
-        <v>-695.3350049003058</v>
+        <v>-715.7607031647243</v>
       </c>
       <c r="O76">
-        <v>-187.7404513230826</v>
+        <v>-193.2553898544756</v>
       </c>
       <c r="P76">
-        <v>-507.5945535772232</v>
+        <v>-522.5053133102488</v>
       </c>
       <c r="Q76">
-        <v>11.30544642277675</v>
+        <v>-3.605313310248789</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1704324206617663</v>
+        <v>0.175417717488237</v>
       </c>
       <c r="T76">
-        <v>2.282686553518501</v>
+        <v>2.373994015659241</v>
       </c>
       <c r="U76">
         <v>0.2091811058765187</v>
       </c>
       <c r="V76">
-        <v>0.1457920981136248</v>
+        <v>0.1438482034721099</v>
       </c>
       <c r="W76">
-        <v>0.1786841535650528</v>
+        <v>0.1790907795958723</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5399707337541662</v>
+        <v>0.5327711239707772</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1781725140689635</v>
+        <v>0.1798063251277287</v>
       </c>
       <c r="C77">
-        <v>-4442.411179762125</v>
+        <v>-4566.770422224945</v>
       </c>
       <c r="D77">
-        <v>2191.038820237874</v>
+        <v>2164.325577775054</v>
       </c>
       <c r="E77">
-        <v>1484.549999999999</v>
+        <v>1582.195999999999</v>
       </c>
       <c r="F77">
-        <v>7323.449999999999</v>
+        <v>7421.095999999999</v>
       </c>
       <c r="G77">
         <v>690</v>
@@ -7729,37 +7729,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M77">
-        <v>1531.927369831391</v>
+        <v>1552.353068095809</v>
       </c>
       <c r="N77">
-        <v>-715.7607031647243</v>
+        <v>-736.1864014291426</v>
       </c>
       <c r="O77">
-        <v>-193.2553898544756</v>
+        <v>-198.7703283858685</v>
       </c>
       <c r="P77">
-        <v>-522.5053133102488</v>
+        <v>-537.4160730432741</v>
       </c>
       <c r="Q77">
-        <v>-3.605313310248789</v>
+        <v>-18.5160730432741</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.175417717488237</v>
+        <v>0.1808184557169135</v>
       </c>
       <c r="T77">
-        <v>2.373994015659241</v>
+        <v>2.472910432978376</v>
       </c>
       <c r="U77">
         <v>0.2091811058765187</v>
       </c>
       <c r="V77">
-        <v>0.1438482034721099</v>
+        <v>0.14195546395274</v>
       </c>
       <c r="W77">
-        <v>0.1790907795958723</v>
+        <v>0.1794867049416703</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5327711239707772</v>
+        <v>0.5257609776027408</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1798063251277287</v>
+        <v>0.1814401361864939</v>
       </c>
       <c r="C78">
-        <v>-4566.770422224945</v>
+        <v>-4690.486132586157</v>
       </c>
       <c r="D78">
-        <v>2164.325577775054</v>
+        <v>2138.255867413842</v>
       </c>
       <c r="E78">
-        <v>1582.195999999999</v>
+        <v>1679.842</v>
       </c>
       <c r="F78">
-        <v>7421.095999999999</v>
+        <v>7518.741999999999</v>
       </c>
       <c r="G78">
         <v>690</v>
@@ -7811,37 +7811,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M78">
-        <v>1552.353068095809</v>
+        <v>1572.778766360228</v>
       </c>
       <c r="N78">
-        <v>-736.1864014291426</v>
+        <v>-756.6120996935614</v>
       </c>
       <c r="O78">
-        <v>-198.7703283858685</v>
+        <v>-204.2852669172616</v>
       </c>
       <c r="P78">
-        <v>-537.4160730432741</v>
+        <v>-552.3268327762999</v>
       </c>
       <c r="Q78">
-        <v>-18.5160730432741</v>
+        <v>-33.42683277629988</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1808184557169135</v>
+        <v>0.1866888233567794</v>
       </c>
       <c r="T78">
-        <v>2.472910432978376</v>
+        <v>2.58042827789048</v>
       </c>
       <c r="U78">
         <v>0.2091811058765187</v>
       </c>
       <c r="V78">
-        <v>0.14195546395274</v>
+        <v>0.1401118864988083</v>
       </c>
       <c r="W78">
-        <v>0.1794867049416703</v>
+        <v>0.1798723465122527</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5257609776027408</v>
+        <v>0.5189329129585492</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1814401361864939</v>
+        <v>0.183073947245259</v>
       </c>
       <c r="C79">
-        <v>-4690.486132586157</v>
+        <v>-4813.581288473025</v>
       </c>
       <c r="D79">
-        <v>2138.255867413842</v>
+        <v>2112.806711526974</v>
       </c>
       <c r="E79">
-        <v>1679.842</v>
+        <v>1777.487999999999</v>
       </c>
       <c r="F79">
-        <v>7518.741999999999</v>
+        <v>7616.387999999999</v>
       </c>
       <c r="G79">
         <v>690</v>
@@ -7893,37 +7893,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M79">
-        <v>1572.778766360228</v>
+        <v>1593.204464624647</v>
       </c>
       <c r="N79">
-        <v>-756.6120996935614</v>
+        <v>-777.0377979579799</v>
       </c>
       <c r="O79">
-        <v>-204.2852669172616</v>
+        <v>-209.8002054486546</v>
       </c>
       <c r="P79">
-        <v>-552.3268327762999</v>
+        <v>-567.2375925093254</v>
       </c>
       <c r="Q79">
-        <v>-33.42683277629988</v>
+        <v>-48.33759250932542</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1866888233567794</v>
+        <v>0.1930928607820875</v>
       </c>
       <c r="T79">
-        <v>2.58042827789048</v>
+        <v>2.697720472340047</v>
       </c>
       <c r="U79">
         <v>0.2091811058765187</v>
       </c>
       <c r="V79">
-        <v>0.1401118864988083</v>
+        <v>0.1383155802616441</v>
       </c>
       <c r="W79">
-        <v>0.1798723465122527</v>
+        <v>0.1802480998374356</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5189329129585492</v>
+        <v>0.512279926894978</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.183073947245259</v>
+        <v>0.1847077583040242</v>
       </c>
       <c r="C80">
-        <v>-4813.581288473025</v>
+        <v>-4936.077786475958</v>
       </c>
       <c r="D80">
-        <v>2112.806711526974</v>
+        <v>2087.956213524041</v>
       </c>
       <c r="E80">
-        <v>1777.487999999999</v>
+        <v>1875.134</v>
       </c>
       <c r="F80">
-        <v>7616.387999999999</v>
+        <v>7714.034</v>
       </c>
       <c r="G80">
         <v>690</v>
@@ -7975,37 +7975,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M80">
-        <v>1593.204464624647</v>
+        <v>1613.630162889065</v>
       </c>
       <c r="N80">
-        <v>-777.0377979579799</v>
+        <v>-797.4634962223985</v>
       </c>
       <c r="O80">
-        <v>-209.8002054486546</v>
+        <v>-215.3151439800476</v>
       </c>
       <c r="P80">
-        <v>-567.2375925093254</v>
+        <v>-582.1483522423509</v>
       </c>
       <c r="Q80">
-        <v>-48.33759250932542</v>
+        <v>-63.24835224235096</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1930928607820875</v>
+        <v>0.2001068065336155</v>
       </c>
       <c r="T80">
-        <v>2.697720472340047</v>
+        <v>2.826183351975288</v>
       </c>
       <c r="U80">
         <v>0.2091811058765187</v>
       </c>
       <c r="V80">
-        <v>0.1383155802616441</v>
+        <v>0.1365647501317499</v>
       </c>
       <c r="W80">
-        <v>0.1802480998374356</v>
+        <v>0.1806143404202088</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.512279926894978</v>
+        <v>0.5057953708583327</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1847077583040242</v>
+        <v>0.2149032711314487</v>
       </c>
       <c r="C81">
-        <v>-4936.077786475958</v>
+        <v>-5406.554591029453</v>
       </c>
       <c r="D81">
-        <v>2087.956213524041</v>
+        <v>1715.125408970546</v>
       </c>
       <c r="E81">
-        <v>1875.134</v>
+        <v>1972.78</v>
       </c>
       <c r="F81">
-        <v>7714.034</v>
+        <v>7811.679999999999</v>
       </c>
       <c r="G81">
         <v>690</v>
@@ -8057,45 +8057,45 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M81">
-        <v>1613.630162889065</v>
+        <v>1907.464661153484</v>
       </c>
       <c r="N81">
-        <v>-797.4634962223985</v>
+        <v>-1091.297994486817</v>
       </c>
       <c r="O81">
-        <v>-215.3151439800476</v>
+        <v>-294.6504585114406</v>
       </c>
       <c r="P81">
-        <v>-582.1483522423509</v>
+        <v>-796.6475359753765</v>
       </c>
       <c r="Q81">
-        <v>-63.24835224235096</v>
+        <v>-277.7475359753765</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2001068065336155</v>
+        <v>0.2106306557035925</v>
       </c>
       <c r="T81">
-        <v>2.826183351975288</v>
+        <v>3.018931345346589</v>
       </c>
       <c r="U81">
-        <v>0.2091811058765187</v>
+        <v>0.2441811058765187</v>
       </c>
       <c r="V81">
-        <v>0.1365647501317499</v>
+        <v>0.1155276973082902</v>
       </c>
       <c r="W81">
-        <v>0.1806143404202088</v>
+        <v>0.2159714249884127</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.5057953708583327</v>
+        <v>0.4278803604010748</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2149032711314487</v>
+        <v>0.2168870821902139</v>
       </c>
       <c r="C82">
-        <v>-5406.554591029453</v>
+        <v>-5524.088034955243</v>
       </c>
       <c r="D82">
-        <v>1715.125408970546</v>
+        <v>1695.237965044756</v>
       </c>
       <c r="E82">
-        <v>1972.78</v>
+        <v>2070.425999999999</v>
       </c>
       <c r="F82">
-        <v>7811.679999999999</v>
+        <v>7909.325999999999</v>
       </c>
       <c r="G82">
         <v>690</v>
@@ -8139,37 +8139,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M82">
-        <v>1907.464661153484</v>
+        <v>1931.307969417902</v>
       </c>
       <c r="N82">
-        <v>-1091.297994486817</v>
+        <v>-1115.141302751235</v>
       </c>
       <c r="O82">
-        <v>-294.6504585114406</v>
+        <v>-301.0881517428336</v>
       </c>
       <c r="P82">
-        <v>-796.6475359753765</v>
+        <v>-814.0531510084018</v>
       </c>
       <c r="Q82">
-        <v>-277.7475359753765</v>
+        <v>-295.1531510084018</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2106306557035925</v>
+        <v>0.2193059533722026</v>
       </c>
       <c r="T82">
-        <v>3.018931345346589</v>
+        <v>3.177822468785883</v>
       </c>
       <c r="U82">
         <v>0.2441811058765187</v>
       </c>
       <c r="V82">
-        <v>0.1155276973082902</v>
+        <v>0.1141014294402866</v>
       </c>
       <c r="W82">
-        <v>0.2159714249884127</v>
+        <v>0.216319692653698</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4278803604010748</v>
+        <v>0.4225978868158764</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2168870821902139</v>
+        <v>0.2188708932489791</v>
       </c>
       <c r="C83">
-        <v>-5524.088034955243</v>
+        <v>-5641.165562459157</v>
       </c>
       <c r="D83">
-        <v>1695.237965044756</v>
+        <v>1675.806437540843</v>
       </c>
       <c r="E83">
-        <v>2070.425999999999</v>
+        <v>2168.072</v>
       </c>
       <c r="F83">
-        <v>7909.325999999999</v>
+        <v>8006.972</v>
       </c>
       <c r="G83">
         <v>690</v>
@@ -8221,37 +8221,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M83">
-        <v>1931.307969417902</v>
+        <v>1955.151277682321</v>
       </c>
       <c r="N83">
-        <v>-1115.141302751235</v>
+        <v>-1138.984611015654</v>
       </c>
       <c r="O83">
-        <v>-301.0881517428336</v>
+        <v>-307.5258449742266</v>
       </c>
       <c r="P83">
-        <v>-814.0531510084018</v>
+        <v>-831.4587660414275</v>
       </c>
       <c r="Q83">
-        <v>-295.1531510084018</v>
+        <v>-312.5587660414275</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2193059533722026</v>
+        <v>0.2289451730039917</v>
       </c>
       <c r="T83">
-        <v>3.177822468785883</v>
+        <v>3.354368161496211</v>
       </c>
       <c r="U83">
         <v>0.2441811058765187</v>
       </c>
       <c r="V83">
-        <v>0.1141014294402866</v>
+        <v>0.1127099485934538</v>
       </c>
       <c r="W83">
-        <v>0.216319692653698</v>
+        <v>0.2166594659856836</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4225978868158764</v>
+        <v>0.4174442540498291</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2188708932489791</v>
+        <v>0.2208547043077442</v>
       </c>
       <c r="C84">
-        <v>-5641.165562459157</v>
+        <v>-5757.802673588047</v>
       </c>
       <c r="D84">
-        <v>1675.806437540843</v>
+        <v>1656.815326411953</v>
       </c>
       <c r="E84">
-        <v>2168.072</v>
+        <v>2265.718</v>
       </c>
       <c r="F84">
-        <v>8006.972</v>
+        <v>8104.617999999999</v>
       </c>
       <c r="G84">
         <v>690</v>
@@ -8303,37 +8303,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M84">
-        <v>1955.151277682321</v>
+        <v>1978.994585946739</v>
       </c>
       <c r="N84">
-        <v>-1138.984611015654</v>
+        <v>-1162.827919280073</v>
       </c>
       <c r="O84">
-        <v>-307.5258449742266</v>
+        <v>-313.9635382056197</v>
       </c>
       <c r="P84">
-        <v>-831.4587660414275</v>
+        <v>-848.8643810744531</v>
       </c>
       <c r="Q84">
-        <v>-312.5587660414275</v>
+        <v>-329.9643810744532</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2289451730039917</v>
+        <v>0.2397184184748147</v>
       </c>
       <c r="T84">
-        <v>3.354368161496211</v>
+        <v>3.55168393570187</v>
       </c>
       <c r="U84">
         <v>0.2441811058765187</v>
       </c>
       <c r="V84">
-        <v>0.1127099485934538</v>
+        <v>0.1113519974055809</v>
       </c>
       <c r="W84">
-        <v>0.2166594659856836</v>
+        <v>0.2169910520084647</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4174442540498291</v>
+        <v>0.4124148052058552</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2208547043077442</v>
+        <v>0.2228385153665094</v>
       </c>
       <c r="C85">
-        <v>-5757.802673588047</v>
+        <v>-5874.014173643575</v>
       </c>
       <c r="D85">
-        <v>1656.815326411953</v>
+        <v>1638.249826356424</v>
       </c>
       <c r="E85">
-        <v>2265.718</v>
+        <v>2363.364</v>
       </c>
       <c r="F85">
-        <v>8104.617999999999</v>
+        <v>8202.263999999999</v>
       </c>
       <c r="G85">
         <v>690</v>
@@ -8385,37 +8385,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M85">
-        <v>1978.994585946739</v>
+        <v>2002.837894211158</v>
       </c>
       <c r="N85">
-        <v>-1162.827919280073</v>
+        <v>-1186.671227544491</v>
       </c>
       <c r="O85">
-        <v>-313.9635382056197</v>
+        <v>-320.4012314370126</v>
       </c>
       <c r="P85">
-        <v>-848.8643810744531</v>
+        <v>-866.2699961074785</v>
       </c>
       <c r="Q85">
-        <v>-329.9643810744532</v>
+        <v>-347.3699961074785</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2397184184748147</v>
+        <v>0.2518383196294907</v>
       </c>
       <c r="T85">
-        <v>3.55168393570187</v>
+        <v>3.773664181683238</v>
       </c>
       <c r="U85">
         <v>0.2441811058765187</v>
       </c>
       <c r="V85">
-        <v>0.1113519974055809</v>
+        <v>0.1100263783888478</v>
       </c>
       <c r="W85">
-        <v>0.2169910520084647</v>
+        <v>0.2173147431259416</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4124148052058552</v>
+        <v>0.4075051051438808</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2228385153665094</v>
+        <v>0.2248223264252746</v>
       </c>
       <c r="C86">
-        <v>-5874.014173643575</v>
+        <v>-5989.814211675823</v>
       </c>
       <c r="D86">
-        <v>1638.249826356424</v>
+        <v>1620.095788324175</v>
       </c>
       <c r="E86">
-        <v>2363.364</v>
+        <v>2461.009999999998</v>
       </c>
       <c r="F86">
-        <v>8202.263999999999</v>
+        <v>8299.909999999998</v>
       </c>
       <c r="G86">
         <v>690</v>
@@ -8467,37 +8467,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M86">
-        <v>2002.837894211158</v>
+        <v>2026.681202475576</v>
       </c>
       <c r="N86">
-        <v>-1186.671227544491</v>
+        <v>-1210.514535808909</v>
       </c>
       <c r="O86">
-        <v>-320.4012314370126</v>
+        <v>-326.8389246684056</v>
       </c>
       <c r="P86">
-        <v>-866.2699961074785</v>
+        <v>-883.6756111405039</v>
       </c>
       <c r="Q86">
-        <v>-347.3699961074785</v>
+        <v>-364.7756111405039</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2518383196294905</v>
+        <v>0.2655742076047899</v>
       </c>
       <c r="T86">
-        <v>3.773664181683235</v>
+        <v>4.02524179379545</v>
       </c>
       <c r="U86">
         <v>0.2441811058765187</v>
       </c>
       <c r="V86">
-        <v>0.1100263783888478</v>
+        <v>0.1087319504078026</v>
       </c>
       <c r="W86">
-        <v>0.2173147431259416</v>
+        <v>0.2176308179818307</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4075051051438808</v>
+        <v>0.4027109274363058</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2248223264252746</v>
+        <v>0.2268061374840398</v>
       </c>
       <c r="C87">
-        <v>-5989.814211675823</v>
+        <v>-6105.216316445584</v>
       </c>
       <c r="D87">
-        <v>1620.095788324175</v>
+        <v>1602.339683554414</v>
       </c>
       <c r="E87">
-        <v>2461.009999999998</v>
+        <v>2558.655999999999</v>
       </c>
       <c r="F87">
-        <v>8299.909999999998</v>
+        <v>8397.555999999999</v>
       </c>
       <c r="G87">
         <v>690</v>
@@ -8549,37 +8549,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M87">
-        <v>2026.681202475576</v>
+        <v>2050.524510739995</v>
       </c>
       <c r="N87">
-        <v>-1210.514535808909</v>
+        <v>-1234.357844073328</v>
       </c>
       <c r="O87">
-        <v>-326.8389246684056</v>
+        <v>-333.2766178997986</v>
       </c>
       <c r="P87">
-        <v>-883.6756111405039</v>
+        <v>-901.0812261735296</v>
       </c>
       <c r="Q87">
-        <v>-364.7756111405039</v>
+        <v>-382.1812261735296</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2655742076047899</v>
+        <v>0.2812723652908464</v>
       </c>
       <c r="T87">
-        <v>4.02524179379545</v>
+        <v>4.31275906478084</v>
       </c>
       <c r="U87">
         <v>0.2441811058765187</v>
       </c>
       <c r="V87">
-        <v>0.1087319504078026</v>
+        <v>0.1074676254030607</v>
       </c>
       <c r="W87">
-        <v>0.2176308179818307</v>
+        <v>0.2179395422596759</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4027109274363058</v>
+        <v>0.3980282422335579</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2268061374840398</v>
+        <v>0.228789948542805</v>
       </c>
       <c r="C88">
-        <v>-6105.216316445584</v>
+        <v>-6220.233430047434</v>
       </c>
       <c r="D88">
-        <v>1602.339683554414</v>
+        <v>1584.968569952565</v>
       </c>
       <c r="E88">
-        <v>2558.655999999999</v>
+        <v>2656.302</v>
       </c>
       <c r="F88">
-        <v>8397.555999999999</v>
+        <v>8495.201999999999</v>
       </c>
       <c r="G88">
         <v>690</v>
@@ -8631,37 +8631,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M88">
-        <v>2050.524510739995</v>
+        <v>2074.367819004413</v>
       </c>
       <c r="N88">
-        <v>-1234.357844073328</v>
+        <v>-1258.201152337747</v>
       </c>
       <c r="O88">
-        <v>-333.2766178997986</v>
+        <v>-339.7143111311917</v>
       </c>
       <c r="P88">
-        <v>-901.0812261735296</v>
+        <v>-918.4868412065553</v>
       </c>
       <c r="Q88">
-        <v>-382.1812261735296</v>
+        <v>-399.5868412065553</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2812723652908464</v>
+        <v>0.299385624159373</v>
       </c>
       <c r="T88">
-        <v>4.31275906478084</v>
+        <v>4.644509762071674</v>
       </c>
       <c r="U88">
         <v>0.2441811058765187</v>
       </c>
       <c r="V88">
-        <v>0.1074676254030607</v>
+        <v>0.1062323653409565</v>
       </c>
       <c r="W88">
-        <v>0.2179395422596759</v>
+        <v>0.2182411694276856</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3980282422335579</v>
+        <v>0.3934532049665055</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.228789948542805</v>
+        <v>0.2307737596015701</v>
       </c>
       <c r="C89">
-        <v>-6220.233430047434</v>
+        <v>-6334.877939369187</v>
       </c>
       <c r="D89">
-        <v>1584.968569952565</v>
+        <v>1567.970060630812</v>
       </c>
       <c r="E89">
-        <v>2656.302</v>
+        <v>2753.947999999999</v>
       </c>
       <c r="F89">
-        <v>8495.201999999999</v>
+        <v>8592.847999999998</v>
       </c>
       <c r="G89">
         <v>690</v>
@@ -8713,37 +8713,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M89">
-        <v>2074.367819004413</v>
+        <v>2098.211127268832</v>
       </c>
       <c r="N89">
-        <v>-1258.201152337747</v>
+        <v>-1282.044460602165</v>
       </c>
       <c r="O89">
-        <v>-339.7143111311917</v>
+        <v>-346.1520043625846</v>
       </c>
       <c r="P89">
-        <v>-918.4868412065553</v>
+        <v>-935.8924562395805</v>
       </c>
       <c r="Q89">
-        <v>-399.5868412065553</v>
+        <v>-416.9924562395805</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.299385624159373</v>
+        <v>0.3205177595059874</v>
       </c>
       <c r="T89">
-        <v>4.644509762071674</v>
+        <v>5.031552242244314</v>
       </c>
       <c r="U89">
         <v>0.2441811058765187</v>
       </c>
       <c r="V89">
-        <v>0.1062323653409565</v>
+        <v>0.1050251793711729</v>
       </c>
       <c r="W89">
-        <v>0.2182411694276856</v>
+        <v>0.218535941432786</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3934532049665055</v>
+        <v>0.3889821458191589</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2307737596015701</v>
+        <v>0.2327575706603353</v>
       </c>
       <c r="C90">
-        <v>-6334.877939369187</v>
+        <v>-6449.161705548463</v>
       </c>
       <c r="D90">
-        <v>1567.970060630812</v>
+        <v>1551.332294451536</v>
       </c>
       <c r="E90">
-        <v>2753.947999999999</v>
+        <v>2851.593999999999</v>
       </c>
       <c r="F90">
-        <v>8592.847999999998</v>
+        <v>8690.493999999999</v>
       </c>
       <c r="G90">
         <v>690</v>
@@ -8795,37 +8795,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M90">
-        <v>2098.211127268832</v>
+        <v>2122.05443553325</v>
       </c>
       <c r="N90">
-        <v>-1282.044460602165</v>
+        <v>-1305.887768866584</v>
       </c>
       <c r="O90">
-        <v>-346.1520043625846</v>
+        <v>-352.5896975939777</v>
       </c>
       <c r="P90">
-        <v>-935.8924562395805</v>
+        <v>-953.2980712726062</v>
       </c>
       <c r="Q90">
-        <v>-416.9924562395805</v>
+        <v>-434.3980712726062</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3205177595059874</v>
+        <v>0.3454921012792591</v>
       </c>
       <c r="T90">
-        <v>5.031552242244314</v>
+        <v>5.488966082448343</v>
       </c>
       <c r="U90">
         <v>0.2441811058765187</v>
       </c>
       <c r="V90">
-        <v>0.1050251793711729</v>
+        <v>0.1038451211759912</v>
       </c>
       <c r="W90">
-        <v>0.218535941432786</v>
+        <v>0.2188240893478841</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3889821458191589</v>
+        <v>0.3846115599110784</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2327575706603353</v>
+        <v>0.2347413817191006</v>
       </c>
       <c r="C91">
-        <v>-6449.161705548463</v>
+        <v>-6563.096091573543</v>
       </c>
       <c r="D91">
-        <v>1551.332294451536</v>
+        <v>1535.043908426456</v>
       </c>
       <c r="E91">
-        <v>2851.593999999999</v>
+        <v>2949.24</v>
       </c>
       <c r="F91">
-        <v>8690.493999999999</v>
+        <v>8788.139999999999</v>
       </c>
       <c r="G91">
         <v>690</v>
@@ -8877,37 +8877,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M91">
-        <v>2122.05443553325</v>
+        <v>2145.897743797669</v>
       </c>
       <c r="N91">
-        <v>-1305.887768866584</v>
+        <v>-1329.731077131003</v>
       </c>
       <c r="O91">
-        <v>-352.5896975939777</v>
+        <v>-359.0273908253707</v>
       </c>
       <c r="P91">
-        <v>-953.2980712726062</v>
+        <v>-970.7036863056319</v>
       </c>
       <c r="Q91">
-        <v>-434.3980712726062</v>
+        <v>-451.8036863056319</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3454921012792591</v>
+        <v>0.375461311407185</v>
       </c>
       <c r="T91">
-        <v>5.488966082448343</v>
+        <v>6.037862690693178</v>
       </c>
       <c r="U91">
         <v>0.2441811058765187</v>
       </c>
       <c r="V91">
-        <v>0.1038451211759912</v>
+        <v>0.102691286496258</v>
       </c>
       <c r="W91">
-        <v>0.2188240893478841</v>
+        <v>0.21910583397598</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3846115599110784</v>
+        <v>0.3803380981342886</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2347413817191006</v>
+        <v>0.2367251927778657</v>
       </c>
       <c r="C92">
-        <v>-6563.096091573543</v>
+        <v>-6676.691988163509</v>
       </c>
       <c r="D92">
-        <v>1535.043908426456</v>
+        <v>1519.094011836489</v>
       </c>
       <c r="E92">
-        <v>2949.24</v>
+        <v>3046.885999999999</v>
       </c>
       <c r="F92">
-        <v>8788.139999999999</v>
+        <v>8885.785999999998</v>
       </c>
       <c r="G92">
         <v>690</v>
@@ -8959,37 +8959,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M92">
-        <v>2145.897743797669</v>
+        <v>2169.741052062087</v>
       </c>
       <c r="N92">
-        <v>-1329.731077131003</v>
+        <v>-1353.574385395421</v>
       </c>
       <c r="O92">
-        <v>-359.0273908253707</v>
+        <v>-365.4650840567637</v>
       </c>
       <c r="P92">
-        <v>-970.7036863056319</v>
+        <v>-988.1093013386572</v>
       </c>
       <c r="Q92">
-        <v>-451.8036863056319</v>
+        <v>-469.2093013386573</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.375461311407185</v>
+        <v>0.4120903460079834</v>
       </c>
       <c r="T92">
-        <v>6.037862690693178</v>
+        <v>6.708736322992421</v>
       </c>
       <c r="U92">
         <v>0.2441811058765187</v>
       </c>
       <c r="V92">
-        <v>0.102691286496258</v>
+        <v>0.1015628108204749</v>
       </c>
       <c r="W92">
-        <v>0.21910583397598</v>
+        <v>0.2193813864144475</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3803380981342886</v>
+        <v>0.3761585585943514</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2367251927778657</v>
+        <v>0.2387090038366309</v>
       </c>
       <c r="C93">
-        <v>-6676.691988163509</v>
+        <v>-6789.95983805154</v>
       </c>
       <c r="D93">
-        <v>1519.094011836489</v>
+        <v>1503.472161948459</v>
       </c>
       <c r="E93">
-        <v>3046.885999999999</v>
+        <v>3144.531999999999</v>
       </c>
       <c r="F93">
-        <v>8885.785999999998</v>
+        <v>8983.431999999999</v>
       </c>
       <c r="G93">
         <v>690</v>
@@ -9041,37 +9041,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M93">
-        <v>2169.741052062087</v>
+        <v>2193.584360326506</v>
       </c>
       <c r="N93">
-        <v>-1353.574385395421</v>
+        <v>-1377.41769365984</v>
       </c>
       <c r="O93">
-        <v>-365.4650840567637</v>
+        <v>-371.9027772881568</v>
       </c>
       <c r="P93">
-        <v>-988.1093013386572</v>
+        <v>-1005.514916371683</v>
       </c>
       <c r="Q93">
-        <v>-469.2093013386573</v>
+        <v>-486.6149163716829</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4120903460079834</v>
+        <v>0.4578766392589814</v>
       </c>
       <c r="T93">
-        <v>6.708736322992421</v>
+        <v>7.547328363366476</v>
       </c>
       <c r="U93">
         <v>0.2441811058765187</v>
       </c>
       <c r="V93">
-        <v>0.1015628108204749</v>
+        <v>0.1004588672246002</v>
       </c>
       <c r="W93">
-        <v>0.2193813864144475</v>
+        <v>0.2196509485825135</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3761585585943514</v>
+        <v>0.3720698786096303</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2387090038366309</v>
+        <v>0.2406928148953961</v>
       </c>
       <c r="C94">
-        <v>-6789.95983805154</v>
+        <v>-6902.909658785105</v>
       </c>
       <c r="D94">
-        <v>1503.472161948459</v>
+        <v>1488.168341214894</v>
       </c>
       <c r="E94">
-        <v>3144.531999999999</v>
+        <v>3242.178</v>
       </c>
       <c r="F94">
-        <v>8983.431999999999</v>
+        <v>9081.078</v>
       </c>
       <c r="G94">
         <v>690</v>
@@ -9123,37 +9123,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M94">
-        <v>2193.584360326506</v>
+        <v>2217.427668590925</v>
       </c>
       <c r="N94">
-        <v>-1377.41769365984</v>
+        <v>-1401.261001924258</v>
       </c>
       <c r="O94">
-        <v>-371.9027772881568</v>
+        <v>-378.3404705195498</v>
       </c>
       <c r="P94">
-        <v>-1005.514916371683</v>
+        <v>-1022.920531404709</v>
       </c>
       <c r="Q94">
-        <v>-486.6149163716829</v>
+        <v>-504.0205314047085</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4578766392589814</v>
+        <v>0.5167447305816931</v>
       </c>
       <c r="T94">
-        <v>7.547328363366476</v>
+        <v>8.625518129561687</v>
       </c>
       <c r="U94">
         <v>0.2441811058765187</v>
       </c>
       <c r="V94">
-        <v>0.1004588672246002</v>
+        <v>0.09937866435121738</v>
       </c>
       <c r="W94">
-        <v>0.2196509485825135</v>
+        <v>0.2199147137147071</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3720698786096303</v>
+        <v>0.3680691272267309</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2406928148953961</v>
+        <v>0.2426766259541613</v>
       </c>
       <c r="C95">
-        <v>-6902.909658785105</v>
+        <v>-7015.551064147718</v>
       </c>
       <c r="D95">
-        <v>1488.168341214894</v>
+        <v>1473.172935852281</v>
       </c>
       <c r="E95">
-        <v>3242.178</v>
+        <v>3339.823999999999</v>
       </c>
       <c r="F95">
-        <v>9081.078</v>
+        <v>9178.723999999998</v>
       </c>
       <c r="G95">
         <v>690</v>
@@ -9205,37 +9205,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M95">
-        <v>2217.427668590925</v>
+        <v>2241.270976855343</v>
       </c>
       <c r="N95">
-        <v>-1401.261001924258</v>
+        <v>-1425.104310188677</v>
       </c>
       <c r="O95">
-        <v>-378.3404705195498</v>
+        <v>-384.7781637509427</v>
       </c>
       <c r="P95">
-        <v>-1022.920531404709</v>
+        <v>-1040.326146437734</v>
       </c>
       <c r="Q95">
-        <v>-504.0205314047085</v>
+        <v>-521.426146437734</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5167447305816931</v>
+        <v>0.5952355190119754</v>
       </c>
       <c r="T95">
-        <v>8.625518129561687</v>
+        <v>10.06310448448864</v>
       </c>
       <c r="U95">
         <v>0.2441811058765187</v>
       </c>
       <c r="V95">
-        <v>0.09937866435121738</v>
+        <v>0.0983214445176938</v>
       </c>
       <c r="W95">
-        <v>0.2199147137147071</v>
+        <v>0.2201728668228115</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3680691272267309</v>
+        <v>0.3641534982136807</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2426766259541613</v>
+        <v>0.2446604370129265</v>
       </c>
       <c r="C96">
-        <v>-7015.551064147718</v>
+        <v>-7127.893284298473</v>
       </c>
       <c r="D96">
-        <v>1473.172935852281</v>
+        <v>1458.476715701526</v>
       </c>
       <c r="E96">
-        <v>3339.823999999999</v>
+        <v>3437.469999999999</v>
       </c>
       <c r="F96">
-        <v>9178.723999999998</v>
+        <v>9276.369999999999</v>
       </c>
       <c r="G96">
         <v>690</v>
@@ -9287,37 +9287,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M96">
-        <v>2241.270976855343</v>
+        <v>2265.114285119762</v>
       </c>
       <c r="N96">
-        <v>-1425.104310188677</v>
+        <v>-1448.947618453095</v>
       </c>
       <c r="O96">
-        <v>-384.7781637509427</v>
+        <v>-391.2158569823358</v>
       </c>
       <c r="P96">
-        <v>-1040.326146437734</v>
+        <v>-1057.73176147076</v>
       </c>
       <c r="Q96">
-        <v>-521.426146437734</v>
+        <v>-538.8317614707597</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5952355190119754</v>
+        <v>0.7051226228143708</v>
       </c>
       <c r="T96">
-        <v>10.06310448448864</v>
+        <v>12.07572538138637</v>
       </c>
       <c r="U96">
         <v>0.2441811058765187</v>
       </c>
       <c r="V96">
-        <v>0.0983214445176938</v>
+        <v>0.09728648194382333</v>
       </c>
       <c r="W96">
-        <v>0.2201728668228115</v>
+        <v>0.22042558512864</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3641534982136807</v>
+        <v>0.3603203034956419</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2446604370129265</v>
+        <v>0.2466442480716917</v>
       </c>
       <c r="C97">
-        <v>-7127.893284298473</v>
+        <v>-7239.945184718024</v>
       </c>
       <c r="D97">
-        <v>1458.476715701526</v>
+        <v>1444.070815281975</v>
       </c>
       <c r="E97">
-        <v>3437.469999999999</v>
+        <v>3535.116</v>
       </c>
       <c r="F97">
-        <v>9276.369999999999</v>
+        <v>9374.016</v>
       </c>
       <c r="G97">
         <v>690</v>
@@ -9369,37 +9369,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M97">
-        <v>2265.114285119762</v>
+        <v>2288.957593384181</v>
       </c>
       <c r="N97">
-        <v>-1448.947618453095</v>
+        <v>-1472.790926717514</v>
       </c>
       <c r="O97">
-        <v>-391.2158569823358</v>
+        <v>-397.6535502137289</v>
       </c>
       <c r="P97">
-        <v>-1057.73176147076</v>
+        <v>-1075.137376503785</v>
       </c>
       <c r="Q97">
-        <v>-538.8317614707597</v>
+        <v>-556.2373765037852</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7051226228143708</v>
+        <v>0.8699532785179638</v>
       </c>
       <c r="T97">
-        <v>12.07572538138637</v>
+        <v>15.09465672673297</v>
       </c>
       <c r="U97">
         <v>0.2441811058765187</v>
       </c>
       <c r="V97">
-        <v>0.09728648194382333</v>
+        <v>0.09627308109024182</v>
       </c>
       <c r="W97">
-        <v>0.22042558512864</v>
+        <v>0.2206730384697637</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3603203034956419</v>
+        <v>0.3565669670008956</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2466442480716917</v>
+        <v>0.2486280591304568</v>
       </c>
       <c r="C98">
-        <v>-7239.945184718023</v>
+        <v>-7351.715284042732</v>
       </c>
       <c r="D98">
-        <v>1444.070815281975</v>
+        <v>1429.946715957267</v>
       </c>
       <c r="E98">
-        <v>3535.115999999998</v>
+        <v>3632.761999999999</v>
       </c>
       <c r="F98">
-        <v>9374.015999999998</v>
+        <v>9471.661999999998</v>
       </c>
       <c r="G98">
         <v>690</v>
@@ -9451,37 +9451,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M98">
-        <v>2288.95759338418</v>
+        <v>2312.800901648599</v>
       </c>
       <c r="N98">
-        <v>-1472.790926717514</v>
+        <v>-1496.634234981932</v>
       </c>
       <c r="O98">
-        <v>-397.6535502137287</v>
+        <v>-404.0912434451218</v>
       </c>
       <c r="P98">
-        <v>-1075.137376503785</v>
+        <v>-1092.542991536811</v>
       </c>
       <c r="Q98">
-        <v>-556.237376503785</v>
+        <v>-573.6429915368107</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8699532785179617</v>
+        <v>1.144671038023949</v>
       </c>
       <c r="T98">
-        <v>15.09465672673293</v>
+        <v>20.12620896897724</v>
       </c>
       <c r="U98">
         <v>0.2441811058765187</v>
       </c>
       <c r="V98">
-        <v>0.09627308109024184</v>
+        <v>0.09528057509962079</v>
       </c>
       <c r="W98">
-        <v>0.2206730384697637</v>
+        <v>0.2209153896801426</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3565669670008956</v>
+        <v>0.3528910188874843</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2486280591304568</v>
+        <v>0.250611870189222</v>
       </c>
       <c r="C99">
-        <v>-7351.715284042732</v>
+        <v>-7463.211770862369</v>
       </c>
       <c r="D99">
-        <v>1429.946715957267</v>
+        <v>1416.09622913763</v>
       </c>
       <c r="E99">
-        <v>3632.761999999999</v>
+        <v>3730.407999999999</v>
       </c>
       <c r="F99">
-        <v>9471.661999999998</v>
+        <v>9569.307999999999</v>
       </c>
       <c r="G99">
         <v>690</v>
@@ -9533,37 +9533,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M99">
-        <v>2312.800901648599</v>
+        <v>2336.644209913018</v>
       </c>
       <c r="N99">
-        <v>-1496.634234981932</v>
+        <v>-1520.477543246351</v>
       </c>
       <c r="O99">
-        <v>-404.0912434451218</v>
+        <v>-410.5289366765148</v>
       </c>
       <c r="P99">
-        <v>-1092.542991536811</v>
+        <v>-1109.948606569836</v>
       </c>
       <c r="Q99">
-        <v>-573.6429915368107</v>
+        <v>-591.0486065698364</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.144671038023949</v>
+        <v>1.694106557035923</v>
       </c>
       <c r="T99">
-        <v>20.12620896897724</v>
+        <v>30.18931345346585</v>
       </c>
       <c r="U99">
         <v>0.2441811058765187</v>
       </c>
       <c r="V99">
-        <v>0.09528057509962079</v>
+        <v>0.09430832433329812</v>
       </c>
       <c r="W99">
-        <v>0.2209153896801426</v>
+        <v>0.2211527949474526</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3528910188874843</v>
+        <v>0.3492900901233263</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.250611870189222</v>
+        <v>0.2525956812479871</v>
       </c>
       <c r="C100">
-        <v>-7463.211770862369</v>
+        <v>-7574.442519550954</v>
       </c>
       <c r="D100">
-        <v>1416.09622913763</v>
+        <v>1402.511480449044</v>
       </c>
       <c r="E100">
-        <v>3730.407999999999</v>
+        <v>3828.053999999998</v>
       </c>
       <c r="F100">
-        <v>9569.307999999999</v>
+        <v>9666.953999999998</v>
       </c>
       <c r="G100">
         <v>690</v>
@@ -9615,37 +9615,37 @@
         <v>816.1666666666666</v>
       </c>
       <c r="M100">
-        <v>2336.644209913018</v>
+        <v>2360.487518177436</v>
       </c>
       <c r="N100">
-        <v>-1520.477543246351</v>
+        <v>-1544.320851510769</v>
       </c>
       <c r="O100">
-        <v>-410.5289366765148</v>
+        <v>-416.9666299079076</v>
       </c>
       <c r="P100">
-        <v>-1109.948606569836</v>
+        <v>-1127.354221602861</v>
       </c>
       <c r="Q100">
-        <v>-591.0486065698364</v>
+        <v>-608.4542216028614</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.694106557035923</v>
+        <v>3.342413114071846</v>
       </c>
       <c r="T100">
-        <v>30.18931345346585</v>
+        <v>60.37862690693171</v>
       </c>
       <c r="U100">
         <v>0.2441811058765187</v>
       </c>
       <c r="V100">
-        <v>0.09430832433329812</v>
+        <v>0.09335571499659817</v>
       </c>
       <c r="W100">
-        <v>0.2211527949474526</v>
+        <v>0.2213854041487563</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3492900901233263</v>
+        <v>0.3457619073948079</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2525956812479871</v>
-      </c>
-      <c r="C101">
-        <v>-7574.442519550954</v>
-      </c>
-      <c r="D101">
-        <v>1402.511480449044</v>
-      </c>
-      <c r="E101">
-        <v>3828.053999999998</v>
-      </c>
-      <c r="F101">
-        <v>9666.953999999998</v>
-      </c>
-      <c r="G101">
-        <v>690</v>
-      </c>
-      <c r="H101">
-        <v>3925.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1335.066666666667</v>
-      </c>
-      <c r="K101">
-        <v>518.9</v>
-      </c>
-      <c r="L101">
-        <v>816.1666666666666</v>
-      </c>
-      <c r="M101">
-        <v>2360.487518177436</v>
-      </c>
-      <c r="N101">
-        <v>-1544.320851510769</v>
-      </c>
-      <c r="O101">
-        <v>-416.9666299079076</v>
-      </c>
-      <c r="P101">
-        <v>-1127.354221602861</v>
-      </c>
-      <c r="Q101">
-        <v>-608.4542216028614</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.342413114071846</v>
-      </c>
-      <c r="T101">
-        <v>60.37862690693171</v>
-      </c>
-      <c r="U101">
-        <v>0.2441811058765187</v>
-      </c>
-      <c r="V101">
-        <v>0.09335571499659817</v>
-      </c>
-      <c r="W101">
-        <v>0.2213854041487563</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3457619073948079</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
